--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -44,6 +44,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="003498DB"/>
         <bgColor rgb="003498DB"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
@@ -71,7 +77,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -80,6 +86,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -447,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -459,7 +468,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="30" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -523,43 +532,268 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>17-MAR-26</t>
+          <t>07-APR-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>SM-496</t>
+          <t>SM-494</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1877</v>
+        <v>699</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>1711</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>166</v>
+        <v>-1012</v>
       </c>
       <c r="G2" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>699</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>1711</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>-1012</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>25</v>
+      </c>
+      <c r="J3" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>799</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>1711</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>-912</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>HIGH THREAT ALERT - NEED ACTION</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>07-APR-26</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>1452</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>1711</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>-259</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G6" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H2" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="H6" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW THREAT</t>
         </is>
       </c>
-      <c r="K2" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>16-APR-26</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>483</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>445</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>38</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>LOW THREAT</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -477,7 +477,7 @@
     <col width="13" customWidth="1" min="7" max="7"/>
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="30" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="10" max="10"/>
     <col width="10" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1024,7 +1024,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1069,7 +1069,7 @@
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1114,7 +1114,7 @@
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1249,7 +1249,7 @@
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1294,7 +1294,7 @@
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1519,7 +1519,7 @@
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1564,7 +1564,7 @@
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1654,7 +1654,7 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1789,7 +1789,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1834,7 +1834,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1879,7 +1879,7 @@
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1924,7 +1924,7 @@
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1969,7 +1969,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2149,7 +2149,7 @@
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2194,7 +2194,7 @@
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2239,7 +2239,7 @@
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2284,7 +2284,7 @@
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2374,7 +2374,7 @@
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2419,7 +2419,7 @@
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2509,7 +2509,7 @@
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2689,7 +2689,7 @@
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2734,7 +2734,7 @@
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2779,7 +2779,7 @@
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2869,7 +2869,7 @@
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2959,7 +2959,7 @@
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -3004,7 +3004,7 @@
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3139,7 +3139,7 @@
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3184,7 +3184,7 @@
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3229,7 +3229,7 @@
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3319,7 +3319,7 @@
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3409,7 +3409,7 @@
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3589,7 +3589,7 @@
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3634,7 +3634,7 @@
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3769,7 +3769,7 @@
       </c>
       <c r="J73" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="J74" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3859,7 +3859,7 @@
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3949,7 +3949,7 @@
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3994,7 +3994,7 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4039,7 +4039,7 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4084,7 +4084,7 @@
       </c>
       <c r="J80" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4129,7 +4129,7 @@
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4174,7 +4174,7 @@
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4309,7 +4309,7 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4399,7 +4399,7 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4489,7 +4489,7 @@
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4534,7 +4534,7 @@
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4579,7 +4579,7 @@
       </c>
       <c r="J91" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4624,7 +4624,7 @@
       </c>
       <c r="J92" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4759,7 +4759,7 @@
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4804,7 +4804,7 @@
       </c>
       <c r="J96" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="J97" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4894,7 +4894,7 @@
       </c>
       <c r="J98" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="J99" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="J100" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -5029,7 +5029,7 @@
       </c>
       <c r="J101" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5074,7 +5074,7 @@
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5119,7 +5119,7 @@
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5164,7 +5164,7 @@
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K104" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5254,7 +5254,7 @@
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5299,7 +5299,7 @@
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5344,7 +5344,7 @@
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5389,7 +5389,7 @@
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5434,7 +5434,7 @@
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5569,7 +5569,7 @@
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5659,7 +5659,7 @@
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K115" s="2" t="inlineStr">
@@ -5704,7 +5704,7 @@
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K116" s="2" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
@@ -5794,7 +5794,7 @@
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5839,7 +5839,7 @@
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5884,7 +5884,7 @@
       </c>
       <c r="J120" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5929,7 +5929,7 @@
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="J123" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6064,7 +6064,7 @@
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K124" s="2" t="inlineStr">
@@ -6109,7 +6109,7 @@
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K125" s="2" t="inlineStr">
@@ -6154,7 +6154,7 @@
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K126" s="2" t="inlineStr">
@@ -6199,7 +6199,7 @@
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6289,7 +6289,7 @@
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -6334,7 +6334,7 @@
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K130" s="2" t="inlineStr">
@@ -6379,7 +6379,7 @@
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6424,7 +6424,7 @@
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6469,7 +6469,7 @@
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6514,7 +6514,7 @@
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K134" s="2" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="J135" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6649,7 +6649,7 @@
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -6694,7 +6694,7 @@
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6739,7 +6739,7 @@
       </c>
       <c r="J139" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -6784,7 +6784,7 @@
       </c>
       <c r="J140" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="J141" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="J142" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6919,7 +6919,7 @@
       </c>
       <c r="J143" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -6964,7 +6964,7 @@
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K144" s="2" t="inlineStr">
@@ -7009,7 +7009,7 @@
       </c>
       <c r="J145" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -7054,7 +7054,7 @@
       </c>
       <c r="J146" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="J147" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -7189,7 +7189,7 @@
       </c>
       <c r="J149" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7234,7 +7234,7 @@
       </c>
       <c r="J150" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7279,7 +7279,7 @@
       </c>
       <c r="J151" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -7369,7 +7369,7 @@
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7414,7 +7414,7 @@
       </c>
       <c r="J154" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7459,7 +7459,7 @@
       </c>
       <c r="J155" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="J156" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -7549,7 +7549,7 @@
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K157" s="2" t="inlineStr">
@@ -7594,7 +7594,7 @@
       </c>
       <c r="J158" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -7639,7 +7639,7 @@
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K159" s="2" t="inlineStr">
@@ -7684,7 +7684,7 @@
       </c>
       <c r="J160" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -7729,7 +7729,7 @@
       </c>
       <c r="J161" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7774,7 +7774,7 @@
       </c>
       <c r="J162" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="J163" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K163" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="J164" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -7909,7 +7909,7 @@
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K165" s="2" t="inlineStr">
@@ -7954,7 +7954,7 @@
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K166" s="2" t="inlineStr">
@@ -7999,7 +7999,7 @@
       </c>
       <c r="J167" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K168" s="2" t="inlineStr">
@@ -8089,7 +8089,7 @@
       </c>
       <c r="J169" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K170" s="2" t="inlineStr">
@@ -8179,7 +8179,7 @@
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K171" s="2" t="inlineStr">
@@ -8224,7 +8224,7 @@
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K172" s="2" t="inlineStr">
@@ -8269,7 +8269,7 @@
       </c>
       <c r="J173" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -8314,7 +8314,7 @@
       </c>
       <c r="J174" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -8359,7 +8359,7 @@
       </c>
       <c r="J175" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8404,7 +8404,7 @@
       </c>
       <c r="J176" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8494,7 +8494,7 @@
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K178" s="2" t="inlineStr">
@@ -8539,7 +8539,7 @@
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K179" s="2" t="inlineStr">
@@ -8584,7 +8584,7 @@
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K180" s="2" t="inlineStr">
@@ -8629,7 +8629,7 @@
       </c>
       <c r="J181" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8674,7 +8674,7 @@
       </c>
       <c r="J182" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -8719,7 +8719,7 @@
       </c>
       <c r="J183" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="J184" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -8809,7 +8809,7 @@
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K185" s="2" t="inlineStr">
@@ -8854,7 +8854,7 @@
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K186" s="2" t="inlineStr">
@@ -8899,7 +8899,7 @@
       </c>
       <c r="J187" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K187" s="2" t="inlineStr">
@@ -8944,7 +8944,7 @@
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K188" s="2" t="inlineStr">
@@ -8989,7 +8989,7 @@
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K189" s="2" t="inlineStr">
@@ -9034,7 +9034,7 @@
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K190" s="2" t="inlineStr">
@@ -9079,7 +9079,7 @@
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K191" s="2" t="inlineStr">
@@ -9124,7 +9124,7 @@
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K192" s="2" t="inlineStr">
@@ -9169,7 +9169,7 @@
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K193" s="2" t="inlineStr">
@@ -9214,7 +9214,7 @@
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K194" s="2" t="inlineStr">
@@ -9259,7 +9259,7 @@
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K195" s="2" t="inlineStr">
@@ -9304,7 +9304,7 @@
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K196" s="2" t="inlineStr">
@@ -9349,7 +9349,7 @@
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K197" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K198" s="2" t="inlineStr">
@@ -9439,7 +9439,7 @@
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K199" s="2" t="inlineStr">
@@ -9484,7 +9484,7 @@
       </c>
       <c r="J200" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K200" s="2" t="inlineStr">
@@ -9529,7 +9529,7 @@
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K201" s="2" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K202" s="2" t="inlineStr">
@@ -9619,7 +9619,7 @@
       </c>
       <c r="J203" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K203" s="2" t="inlineStr">
@@ -9664,7 +9664,7 @@
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K204" s="2" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K205" s="2" t="inlineStr">
@@ -9754,7 +9754,7 @@
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K206" s="2" t="inlineStr">
@@ -9799,7 +9799,7 @@
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K207" s="2" t="inlineStr">
@@ -9844,7 +9844,7 @@
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K208" s="2" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="J209" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K209" s="2" t="inlineStr">
@@ -9934,7 +9934,7 @@
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K210" s="2" t="inlineStr">
@@ -9979,7 +9979,7 @@
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K211" s="2" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K212" s="2" t="inlineStr">
@@ -10069,7 +10069,7 @@
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K213" s="2" t="inlineStr">
@@ -10114,7 +10114,7 @@
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K214" s="2" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K215" s="2" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K216" s="2" t="inlineStr">
@@ -10249,7 +10249,7 @@
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K217" s="2" t="inlineStr">
@@ -10294,7 +10294,7 @@
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K218" s="2" t="inlineStr">
@@ -10339,7 +10339,7 @@
       </c>
       <c r="J219" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K219" s="2" t="inlineStr">
@@ -10384,7 +10384,7 @@
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K220" s="2" t="inlineStr">
@@ -10429,7 +10429,7 @@
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K221" s="2" t="inlineStr">
@@ -10474,7 +10474,7 @@
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K222" s="2" t="inlineStr">
@@ -10519,7 +10519,7 @@
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K223" s="2" t="inlineStr">
@@ -10564,7 +10564,7 @@
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K224" s="2" t="inlineStr">
@@ -10609,7 +10609,7 @@
       </c>
       <c r="J225" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K226" s="2" t="inlineStr">
@@ -10699,7 +10699,7 @@
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K227" s="2" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="J228" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K228" s="2" t="inlineStr">
@@ -10789,7 +10789,7 @@
       </c>
       <c r="J229" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K229" s="2" t="inlineStr">
@@ -10834,7 +10834,7 @@
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K230" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K231" s="2" t="inlineStr">
@@ -10924,7 +10924,7 @@
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K232" s="2" t="inlineStr">
@@ -10969,7 +10969,7 @@
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K233" s="2" t="inlineStr">
@@ -11014,7 +11014,7 @@
       </c>
       <c r="J234" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K234" s="2" t="inlineStr">
@@ -11059,7 +11059,7 @@
       </c>
       <c r="J235" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K235" s="2" t="inlineStr">
@@ -11104,7 +11104,7 @@
       </c>
       <c r="J236" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -11149,7 +11149,7 @@
       </c>
       <c r="J237" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="J238" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -11239,7 +11239,7 @@
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K239" s="2" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="J240" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="J241" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11374,7 +11374,7 @@
       </c>
       <c r="J242" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="J243" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K243" s="2" t="inlineStr">
@@ -11464,7 +11464,7 @@
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K244" s="2" t="inlineStr">
@@ -11509,7 +11509,7 @@
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K245" s="2" t="inlineStr">
@@ -11554,7 +11554,7 @@
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K246" s="2" t="inlineStr">
@@ -11599,7 +11599,7 @@
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K247" s="2" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="J248" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K248" s="2" t="inlineStr">
@@ -11689,7 +11689,7 @@
       </c>
       <c r="J249" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -11734,7 +11734,7 @@
       </c>
       <c r="J250" s="4" t="inlineStr">
         <is>
-          <t>MEDIUM THREAT - MONITOR</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K250" s="2" t="inlineStr">
@@ -11779,7 +11779,7 @@
       </c>
       <c r="J251" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -11824,7 +11824,7 @@
       </c>
       <c r="J252" s="5" t="inlineStr">
         <is>
-          <t>HIGH THREAT ALERT - NEED ACTION</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr">
@@ -11869,7 +11869,7 @@
       </c>
       <c r="J253" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K253" s="2" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="J254" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K254" s="2" t="inlineStr">
@@ -11959,7 +11959,7 @@
       </c>
       <c r="J255" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K255" s="2" t="inlineStr">
@@ -12004,7 +12004,7 @@
       </c>
       <c r="J256" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K256" s="2" t="inlineStr">
@@ -12049,7 +12049,7 @@
       </c>
       <c r="J257" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K257" s="2" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="J258" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K258" s="2" t="inlineStr">
@@ -12139,7 +12139,7 @@
       </c>
       <c r="J259" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K259" s="2" t="inlineStr">
@@ -12184,7 +12184,7 @@
       </c>
       <c r="J260" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K260" s="2" t="inlineStr">
@@ -12229,7 +12229,7 @@
       </c>
       <c r="J261" s="3" t="inlineStr">
         <is>
-          <t>LOW THREAT</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K261" s="2" t="inlineStr">

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K261"/>
+  <dimension ref="A1:K252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>20-MAY-26</t>
+          <t>19-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>753</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>820</v>
+        <v>742</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-67</v>
+        <v>11</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -596,7 +596,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -641,26 +641,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>799</v>
+        <v>753</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-21</v>
+        <v>-67</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>40</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>0</v>
+        <v>-6</v>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
@@ -676,36 +676,36 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>20-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>13</v>
+        <v>-200</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-6</v>
+        <v>7</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -726,7 +726,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-486</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -735,13 +735,13 @@
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>25</v>
+        <v>-145</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -771,7 +771,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-486</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>25</v>
+        <v>-145</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -816,7 +816,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-486</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -825,13 +825,13 @@
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1018</v>
+        <v>833</v>
       </c>
       <c r="E8" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>120</v>
+        <v>-65</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -842,9 +842,9 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-486</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -870,13 +870,13 @@
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1075</v>
+        <v>980</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>177</v>
+        <v>82</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>923</v>
+        <v>1018</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -951,31 +951,31 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-494</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>923</v>
+        <v>698</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>103</v>
+        <v>-122</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -996,22 +996,22 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-494</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1018</v>
+        <v>753</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>198</v>
+        <v>-67</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>898</v>
+        <v>820</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>25</v>
+        <v>-67</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>923</v>
+        <v>833</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>898</v>
+        <v>820</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>923</v>
+        <v>980</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>898</v>
+        <v>820</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>25</v>
+        <v>160</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,17 +1181,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>980</v>
+        <v>1018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>898</v>
+        <v>820</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>82</v>
+        <v>198</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>890</v>
+        <v>753</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-8</v>
+        <v>-145</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>25</v>
+        <v>-145</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>46</v>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,17 +1316,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>25</v>
+        <v>-145</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>923</v>
+        <v>980</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>25</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1296</v>
+        <v>753</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-457</v>
+        <v>-67</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,26 +1451,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1296</v>
+        <v>753</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-457</v>
+        <v>-67</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1530</v>
+        <v>753</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-223</v>
+        <v>-67</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1530</v>
+        <v>909</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1753</v>
+        <v>1246</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-223</v>
+        <v>-337</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>716</v>
+        <v>804</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-26</v>
+        <v>-949</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>799</v>
+        <v>804</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>57</v>
+        <v>-949</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>799</v>
+        <v>1126</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>57</v>
+        <v>-627</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>40</v>
@@ -1697,9 +1697,9 @@
       <c r="I27" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>09-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>903</v>
+        <v>1296</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>161</v>
+        <v>-457</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>716</v>
+        <v>1296</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>682</v>
+        <v>1753</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>34</v>
+        <v>-457</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>799</v>
+        <v>559</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>682</v>
+        <v>1054</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>117</v>
+        <v>-495</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>494</v>
+        <v>671</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-866</v>
+        <v>-383</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>494</v>
+        <v>719</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-866</v>
+        <v>-335</v>
       </c>
       <c r="G32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>494</v>
+        <v>788</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-866</v>
+        <v>-266</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>626</v>
+        <v>788</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-734</v>
+        <v>-266</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>626</v>
+        <v>788</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-734</v>
+        <v>-266</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>716</v>
+        <v>788</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-644</v>
+        <v>-266</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J36" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>494</v>
+        <v>639</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1360</v>
+        <v>682</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-866</v>
+        <v>-43</v>
       </c>
       <c r="G37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,26 +2261,26 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>719</v>
+        <v>494</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-641</v>
+        <v>-866</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,26 +2306,26 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>494</v>
+        <v>449</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-866</v>
+        <v>-911</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,26 +2441,26 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>619</v>
+        <v>494</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-741</v>
+        <v>-866</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>719</v>
+        <v>799</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-641</v>
+        <v>-561</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>789</v>
+        <v>836</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-571</v>
+        <v>-524</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
@@ -2756,26 +2756,26 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>1113</v>
+        <v>596</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-247</v>
+        <v>-764</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
@@ -2801,26 +2801,26 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>1113</v>
+        <v>671</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-247</v>
+        <v>-689</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>1113</v>
+        <v>775</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-247</v>
+        <v>-585</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>46</v>
@@ -2891,26 +2891,26 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>1113</v>
+        <v>799</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-247</v>
+        <v>-561</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
@@ -2936,26 +2936,26 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>1170</v>
+        <v>836</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-190</v>
+        <v>-524</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2985,22 +2985,22 @@
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>671</v>
+        <v>903</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-689</v>
+        <v>-457</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,26 +3026,26 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>671</v>
+        <v>906</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-689</v>
+        <v>-454</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,26 +3071,26 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>671</v>
+        <v>1113</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-689</v>
+        <v>-247</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,26 +3116,26 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>699</v>
+        <v>1113</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-661</v>
+        <v>-247</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>826</v>
+        <v>1113</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-534</v>
+        <v>-247</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>906</v>
+        <v>1113</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-454</v>
+        <v>-247</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1113</v>
+        <v>1170</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-247</v>
+        <v>-190</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3296,26 +3296,26 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>1113</v>
+        <v>619</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-247</v>
+        <v>-741</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
@@ -3341,26 +3341,26 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>1113</v>
+        <v>619</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-247</v>
+        <v>-741</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
@@ -3386,26 +3386,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>1113</v>
+        <v>671</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-247</v>
+        <v>-689</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
@@ -3431,26 +3431,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>1170</v>
+        <v>671</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-190</v>
+        <v>-689</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>727</v>
+        <v>671</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-633</v>
+        <v>-689</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>23</v>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,26 +3521,26 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>727</v>
+        <v>789</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-633</v>
+        <v>-571</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,26 +3566,26 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>799</v>
+        <v>1113</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-561</v>
+        <v>-247</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J69" s="5" t="inlineStr">
         <is>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,26 +3611,26 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>844</v>
+        <v>1113</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-516</v>
+        <v>-247</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J70" s="5" t="inlineStr">
         <is>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,26 +3656,26 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>844</v>
+        <v>1113</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-516</v>
+        <v>-247</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J71" s="5" t="inlineStr">
         <is>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,26 +3701,26 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>844</v>
+        <v>1113</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-516</v>
+        <v>-247</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J72" s="5" t="inlineStr">
         <is>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1219</v>
+        <v>1170</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-141</v>
+        <v>-190</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>1358</v>
+        <v>727</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-2</v>
+        <v>-633</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3836,30 +3836,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>1358</v>
+        <v>727</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-2</v>
+        <v>-633</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3881,30 +3881,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>1358</v>
+        <v>799</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-2</v>
+        <v>-561</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>1358</v>
+        <v>844</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-2</v>
+        <v>-516</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3971,30 +3971,30 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>1415</v>
+        <v>844</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>55</v>
+        <v>-516</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>1309</v>
+        <v>844</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-51</v>
+        <v>-516</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,30 +4061,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1358</v>
+        <v>1309</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-2</v>
+        <v>-51</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,7 +4151,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1415</v>
+        <v>1358</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>55</v>
+        <v>-2</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>46</v>
@@ -4262,9 +4262,9 @@
       <c r="I84" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J84" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,26 +4286,26 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1499</v>
+        <v>1415</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>139</v>
+        <v>55</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,26 +4331,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>999</v>
+        <v>1309</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-361</v>
+        <v>-51</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,30 +4376,30 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>999</v>
+        <v>1358</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-361</v>
+        <v>-2</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J87" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,26 +4421,26 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1059</v>
+        <v>1358</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-301</v>
+        <v>-2</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,26 +4466,26 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1059</v>
+        <v>1358</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-301</v>
+        <v>-2</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,17 +4556,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1358</v>
+        <v>1415</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-2</v>
+        <v>55</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>46</v>
@@ -4577,9 +4577,9 @@
       <c r="I91" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J91" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J91" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4601,30 +4601,30 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>1358</v>
+        <v>876</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-2</v>
+        <v>-484</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K92" s="2" t="inlineStr">
@@ -4646,26 +4646,26 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1358</v>
+        <v>1059</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-2</v>
+        <v>-301</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -4691,30 +4691,30 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1415</v>
+        <v>1099</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>55</v>
+        <v>-261</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J94" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4736,30 +4736,30 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1544</v>
+        <v>1176</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>184</v>
+        <v>-184</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J95" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,30 +4781,30 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>999</v>
+        <v>1358</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-361</v>
+        <v>-2</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J96" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,30 +4826,30 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1259</v>
+        <v>1358</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-101</v>
+        <v>-2</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1358</v>
+        <v>1415</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-2</v>
+        <v>55</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>46</v>
@@ -4982,9 +4982,9 @@
       <c r="I100" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J100" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J100" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1358</v>
+        <v>1544</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-2</v>
+        <v>184</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>46</v>
@@ -5027,9 +5027,9 @@
       <c r="I101" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J101" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5051,30 +5051,30 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>1415</v>
+        <v>899</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>55</v>
+        <v>-461</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J102" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J102" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5096,26 +5096,26 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>1544</v>
+        <v>999</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>184</v>
+        <v>-361</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,26 +5141,26 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>699</v>
+        <v>1259</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-277</v>
+        <v>-101</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,30 +5186,30 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>789</v>
+        <v>1358</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-187</v>
+        <v>-2</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,30 +5231,30 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>959</v>
+        <v>1358</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-17</v>
+        <v>-2</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J106" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K106" s="2" t="inlineStr">
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,30 +5276,30 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>619</v>
+        <v>1358</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-357</v>
+        <v>-2</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,30 +5321,30 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>698</v>
+        <v>1358</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-278</v>
+        <v>-2</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,26 +5366,26 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>698</v>
+        <v>1415</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-278</v>
+        <v>55</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,26 +5411,26 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>698</v>
+        <v>559</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-278</v>
+        <v>-417</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,26 +5456,26 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-278</v>
+        <v>-277</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,26 +5501,26 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>755</v>
+        <v>976</v>
       </c>
       <c r="E112" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-221</v>
+        <v>0</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H112" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,30 +5546,30 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-188</v>
+        <v>-177</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J113" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,30 +5591,30 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>788</v>
+        <v>906</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-188</v>
+        <v>-70</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J114" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,26 +5636,26 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>789</v>
+        <v>1076</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-187</v>
+        <v>100</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,26 +5681,26 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>789</v>
+        <v>1099</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>-187</v>
+        <v>123</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -5726,26 +5726,26 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>826</v>
+        <v>449</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-150</v>
+        <v>-527</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J117" s="4" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,26 +5771,26 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>698</v>
+        <v>619</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-278</v>
+        <v>-357</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,30 +5861,30 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-223</v>
+        <v>-278</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,17 +5906,17 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G121" s="2" t="n">
         <v>23</v>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,30 +5951,30 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>788</v>
+        <v>753</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-188</v>
+        <v>-223</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J122" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,30 +5996,30 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>833</v>
+        <v>755</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-143</v>
+        <v>-221</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J123" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6045,22 +6045,22 @@
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>1020</v>
+        <v>788</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>44</v>
+        <v>-188</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,26 +6086,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>559</v>
+        <v>788</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-417</v>
+        <v>-188</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,26 +6131,26 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>698</v>
+        <v>789</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>-278</v>
+        <v>-187</v>
       </c>
       <c r="G126" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H126" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J126" s="3" t="inlineStr">
         <is>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,26 +6176,26 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>698</v>
+        <v>789</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-278</v>
+        <v>-187</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J127" s="3" t="inlineStr">
         <is>
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,26 +6221,26 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>698</v>
+        <v>619</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-278</v>
+        <v>-357</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,26 +6266,26 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>698</v>
+        <v>619</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-278</v>
+        <v>-357</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H129" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,26 +6311,26 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-277</v>
+        <v>-278</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6356,30 +6356,30 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-221</v>
+        <v>-223</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J131" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,30 +6401,30 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>788</v>
+        <v>753</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-188</v>
+        <v>-223</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J132" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,17 +6446,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>788</v>
+        <v>755</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-188</v>
+        <v>-221</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>23</v>
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,26 +6491,26 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H134" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,30 +6536,30 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>753</v>
+        <v>788</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>-223</v>
+        <v>-188</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,26 +6581,26 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>755</v>
+        <v>789</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-221</v>
+        <v>-187</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6626,26 +6626,26 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-150</v>
+        <v>-143</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J137" s="4" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6675,22 +6675,22 @@
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>826</v>
+        <v>419</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-150</v>
+        <v>-557</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J138" s="4" t="inlineStr">
         <is>
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>833</v>
+        <v>619</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-143</v>
+        <v>-357</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,30 +6761,30 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E140" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H140" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,30 +6806,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>906</v>
+        <v>698</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-70</v>
+        <v>-278</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,30 +6851,30 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>906</v>
+        <v>698</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-70</v>
+        <v>-278</v>
       </c>
       <c r="G142" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H142" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J142" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K142" s="2" t="inlineStr">
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6896,30 +6896,30 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>923</v>
+        <v>698</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-53</v>
+        <v>-278</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J143" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
@@ -6931,7 +6931,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6941,26 +6941,26 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1155</v>
+        <v>755</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>179</v>
+        <v>-221</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6986,17 +6986,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>698</v>
+        <v>788</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-278</v>
+        <v>-188</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>23</v>
@@ -7021,7 +7021,7 @@
     <row r="146">
       <c r="A146" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B146" s="2" t="inlineStr">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>698</v>
+        <v>788</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>-278</v>
+        <v>-188</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>23</v>
@@ -7066,7 +7066,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7076,30 +7076,30 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>698</v>
+        <v>906</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>-278</v>
+        <v>-70</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7121,26 +7121,26 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>755</v>
+        <v>619</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>-221</v>
+        <v>-357</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H148" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7166,30 +7166,30 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>833</v>
+        <v>619</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>-143</v>
+        <v>-357</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H149" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J149" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K149" s="2" t="inlineStr">
@@ -7201,7 +7201,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7211,17 +7211,17 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>903</v>
+        <v>753</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>-73</v>
+        <v>-223</v>
       </c>
       <c r="G150" s="2" t="n">
         <v>46</v>
@@ -7232,9 +7232,9 @@
       <c r="I150" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J150" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J150" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7256,30 +7256,30 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>903</v>
+        <v>755</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>-73</v>
+        <v>-221</v>
       </c>
       <c r="G151" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H151" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J151" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K151" s="2" t="inlineStr">
@@ -7291,7 +7291,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7301,26 +7301,26 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>698</v>
+        <v>789</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>-278</v>
+        <v>-187</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H152" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -7336,7 +7336,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7346,26 +7346,26 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>698</v>
+        <v>789</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>-278</v>
+        <v>-187</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H153" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J153" s="3" t="inlineStr">
         <is>
@@ -7381,7 +7381,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>755</v>
+        <v>833</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>-221</v>
+        <v>-143</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H154" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J154" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7436,30 +7436,30 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>-187</v>
+        <v>-143</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H155" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7485,13 +7485,13 @@
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>833</v>
+        <v>923</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>-143</v>
+        <v>-53</v>
       </c>
       <c r="G156" s="2" t="n">
         <v>46</v>
@@ -7516,7 +7516,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7526,26 +7526,26 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>903</v>
+        <v>449</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>-73</v>
+        <v>-527</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H157" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J157" s="4" t="inlineStr">
         <is>
@@ -7561,7 +7561,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7571,30 +7571,30 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>903</v>
+        <v>619</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>-73</v>
+        <v>-357</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H158" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J158" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7616,26 +7616,26 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>489</v>
+        <v>671</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>-487</v>
+        <v>-305</v>
       </c>
       <c r="G159" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H159" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7661,30 +7661,30 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>619</v>
+        <v>671</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>-357</v>
+        <v>-305</v>
       </c>
       <c r="G160" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H160" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J160" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -7696,7 +7696,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -7706,17 +7706,17 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>-305</v>
+        <v>-278</v>
       </c>
       <c r="G161" s="2" t="n">
         <v>23</v>
@@ -7727,9 +7727,9 @@
       <c r="I161" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J161" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
@@ -7741,7 +7741,7 @@
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B162" s="2" t="inlineStr">
@@ -7751,17 +7751,17 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="E162" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F162" s="2" t="n">
-        <v>-305</v>
+        <v>-278</v>
       </c>
       <c r="G162" s="2" t="n">
         <v>23</v>
@@ -7772,9 +7772,9 @@
       <c r="I162" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J162" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K162" s="2" t="inlineStr">
@@ -7786,7 +7786,7 @@
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B163" s="2" t="inlineStr">
@@ -7796,7 +7796,7 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
@@ -7831,7 +7831,7 @@
     <row r="164">
       <c r="A164" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B164" s="2" t="inlineStr">
@@ -7841,17 +7841,17 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>-278</v>
+        <v>-221</v>
       </c>
       <c r="G164" s="2" t="n">
         <v>23</v>
@@ -7876,7 +7876,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -7886,26 +7886,26 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>698</v>
+        <v>789</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>-278</v>
+        <v>-187</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H165" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -7931,26 +7931,26 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>755</v>
+        <v>789</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>-221</v>
+        <v>-187</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -7976,30 +7976,30 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>-187</v>
+        <v>-143</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H167" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J167" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K167" s="2" t="inlineStr">
@@ -8011,7 +8011,7 @@
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B168" s="2" t="inlineStr">
@@ -8021,26 +8021,26 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
-        <v>833</v>
+        <v>671</v>
       </c>
       <c r="E168" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F168" s="2" t="n">
-        <v>-143</v>
+        <v>-305</v>
       </c>
       <c r="G168" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H168" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J168" s="4" t="inlineStr">
         <is>
@@ -8056,7 +8056,7 @@
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B169" s="2" t="inlineStr">
@@ -8066,30 +8066,30 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>833</v>
+        <v>671</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>211</v>
+        <v>-305</v>
       </c>
       <c r="G169" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H169" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J169" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -8101,7 +8101,7 @@
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B170" s="2" t="inlineStr">
@@ -8111,26 +8111,26 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
-        <v>559</v>
+        <v>698</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F170" s="2" t="n">
-        <v>-63</v>
+        <v>-278</v>
       </c>
       <c r="G170" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H170" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J170" s="3" t="inlineStr">
         <is>
@@ -8146,7 +8146,7 @@
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B171" s="2" t="inlineStr">
@@ -8156,26 +8156,26 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>599</v>
+        <v>698</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>-23</v>
+        <v>-278</v>
       </c>
       <c r="G171" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H171" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J171" s="3" t="inlineStr">
         <is>
@@ -8191,7 +8191,7 @@
     <row r="172">
       <c r="A172" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B172" s="2" t="inlineStr">
@@ -8201,26 +8201,26 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>833</v>
+        <v>755</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>211</v>
+        <v>-221</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H172" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -8236,7 +8236,7 @@
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B173" s="2" t="inlineStr">
@@ -8246,17 +8246,17 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>596</v>
+        <v>789</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>-26</v>
+        <v>-187</v>
       </c>
       <c r="G173" s="2" t="n">
         <v>30</v>
@@ -8281,7 +8281,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -8291,30 +8291,30 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>596</v>
+        <v>833</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>-26</v>
+        <v>-143</v>
       </c>
       <c r="G174" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H174" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J174" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J174" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K174" s="2" t="inlineStr">
@@ -8326,7 +8326,7 @@
     <row r="175">
       <c r="A175" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B175" s="2" t="inlineStr">
@@ -8336,30 +8336,30 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>646</v>
+        <v>671</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>24</v>
+        <v>-305</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H175" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J175" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J175" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8371,7 +8371,7 @@
     <row r="176">
       <c r="A176" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B176" s="2" t="inlineStr">
@@ -8381,30 +8381,30 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
-        <v>698</v>
+        <v>671</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F176" s="2" t="n">
-        <v>76</v>
+        <v>-305</v>
       </c>
       <c r="G176" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H176" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J176" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J176" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K176" s="2" t="inlineStr">
@@ -8416,7 +8416,7 @@
     <row r="177">
       <c r="A177" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B177" s="2" t="inlineStr">
@@ -8426,26 +8426,26 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>775</v>
+        <v>698</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>153</v>
+        <v>-278</v>
       </c>
       <c r="G177" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H177" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J177" s="3" t="inlineStr">
         <is>
@@ -8461,7 +8461,7 @@
     <row r="178">
       <c r="A178" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B178" s="2" t="inlineStr">
@@ -8475,22 +8475,22 @@
         </is>
       </c>
       <c r="D178" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F178" s="2" t="n">
-        <v>211</v>
+        <v>-278</v>
       </c>
       <c r="G178" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H178" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J178" s="3" t="inlineStr">
         <is>
@@ -8506,7 +8506,7 @@
     <row r="179">
       <c r="A179" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B179" s="2" t="inlineStr">
@@ -8516,26 +8516,26 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
-        <v>596</v>
+        <v>698</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F179" s="2" t="n">
-        <v>-26</v>
+        <v>-278</v>
       </c>
       <c r="G179" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H179" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J179" s="3" t="inlineStr">
         <is>
@@ -8551,7 +8551,7 @@
     <row r="180">
       <c r="A180" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B180" s="2" t="inlineStr">
@@ -8561,26 +8561,26 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>596</v>
+        <v>755</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>-26</v>
+        <v>-221</v>
       </c>
       <c r="G180" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H180" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J180" s="3" t="inlineStr">
         <is>
@@ -8596,7 +8596,7 @@
     <row r="181">
       <c r="A181" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B181" s="2" t="inlineStr">
@@ -8606,17 +8606,17 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>646</v>
+        <v>799</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>24</v>
+        <v>-177</v>
       </c>
       <c r="G181" s="2" t="n">
         <v>40</v>
@@ -8627,9 +8627,9 @@
       <c r="I181" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="J181" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J181" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8641,7 +8641,7 @@
     <row r="182">
       <c r="A182" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B182" s="2" t="inlineStr">
@@ -8651,30 +8651,30 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>698</v>
+        <v>799</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>76</v>
+        <v>-177</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H182" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J182" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J182" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -8686,7 +8686,7 @@
     <row r="183">
       <c r="A183" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B183" s="2" t="inlineStr">
@@ -8696,17 +8696,17 @@
       </c>
       <c r="C183" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D183" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F183" s="2" t="n">
-        <v>76</v>
+        <v>-143</v>
       </c>
       <c r="G183" s="2" t="n">
         <v>46</v>
@@ -8717,9 +8717,9 @@
       <c r="I183" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J183" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J183" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K183" s="2" t="inlineStr">
@@ -8731,7 +8731,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -8741,30 +8741,30 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>559</v>
+        <v>906</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>-63</v>
+        <v>-70</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H184" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J184" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J184" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -8776,7 +8776,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -8786,26 +8786,26 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
-        <v>559</v>
+        <v>833</v>
       </c>
       <c r="E185" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F185" s="2" t="n">
-        <v>-63</v>
+        <v>211</v>
       </c>
       <c r="G185" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H185" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J185" s="3" t="inlineStr">
         <is>
@@ -8821,7 +8821,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -8831,17 +8831,17 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>596</v>
+        <v>559</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>-26</v>
+        <v>-63</v>
       </c>
       <c r="G186" s="2" t="n">
         <v>30</v>
@@ -8866,7 +8866,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -8876,17 +8876,17 @@
       </c>
       <c r="C187" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>-26</v>
+        <v>-23</v>
       </c>
       <c r="G187" s="2" t="n">
         <v>30</v>
@@ -8911,7 +8911,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -8921,17 +8921,17 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="G188" s="2" t="n">
         <v>46</v>
@@ -8956,7 +8956,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -8966,26 +8966,26 @@
       </c>
       <c r="C189" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G189" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H189" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J189" s="3" t="inlineStr">
         <is>
@@ -9001,7 +9001,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -9011,26 +9011,26 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
-        <v>529</v>
+        <v>833</v>
       </c>
       <c r="E190" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F190" s="2" t="n">
-        <v>-93</v>
+        <v>211</v>
       </c>
       <c r="G190" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H190" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J190" s="3" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -9091,7 +9091,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -9101,26 +9101,26 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>646</v>
+        <v>559</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>24</v>
+        <v>-63</v>
       </c>
       <c r="G192" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H192" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J192" s="3" t="inlineStr">
         <is>
@@ -9136,7 +9136,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -9146,26 +9146,26 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>775</v>
+        <v>559</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>153</v>
+        <v>-63</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H193" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -9226,7 +9226,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -9236,26 +9236,26 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G195" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H195" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J195" s="3" t="inlineStr">
         <is>
@@ -9271,7 +9271,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -9281,7 +9281,7 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
@@ -9316,7 +9316,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -9326,26 +9326,26 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>559</v>
+        <v>698</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>-63</v>
+        <v>76</v>
       </c>
       <c r="G197" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H197" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J197" s="3" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -9371,26 +9371,26 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>833</v>
+        <v>646</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>211</v>
+        <v>24</v>
       </c>
       <c r="G198" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H198" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -9416,7 +9416,7 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
@@ -9451,7 +9451,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -9506,26 +9506,26 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
-        <v>596</v>
+        <v>833</v>
       </c>
       <c r="E201" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F201" s="2" t="n">
-        <v>-26</v>
+        <v>211</v>
       </c>
       <c r="G201" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H201" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J201" s="3" t="inlineStr">
         <is>
@@ -9541,7 +9541,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -9555,22 +9555,22 @@
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>646</v>
+        <v>529</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>24</v>
+        <v>-93</v>
       </c>
       <c r="G202" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H202" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -9596,17 +9596,17 @@
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>596</v>
+        <v>559</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>-26</v>
+        <v>-63</v>
       </c>
       <c r="G203" s="2" t="n">
         <v>30</v>
@@ -9631,7 +9631,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -9641,26 +9641,26 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D204" s="2" t="n">
-        <v>596</v>
+        <v>833</v>
       </c>
       <c r="E204" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F204" s="2" t="n">
-        <v>-26</v>
+        <v>211</v>
       </c>
       <c r="G204" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H204" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J204" s="3" t="inlineStr">
         <is>
@@ -9676,7 +9676,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -9686,26 +9686,26 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>646</v>
+        <v>833</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>24</v>
+        <v>211</v>
       </c>
       <c r="G205" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H205" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -9731,26 +9731,26 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D206" s="2" t="n">
-        <v>698</v>
+        <v>529</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>76</v>
+        <v>-93</v>
       </c>
       <c r="G206" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H206" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -9776,26 +9776,26 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D207" s="2" t="n">
-        <v>698</v>
+        <v>529</v>
       </c>
       <c r="E207" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F207" s="2" t="n">
-        <v>76</v>
+        <v>-93</v>
       </c>
       <c r="G207" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H207" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J207" s="3" t="inlineStr">
         <is>
@@ -9821,17 +9821,17 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D208" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F208" s="2" t="n">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="G208" s="2" t="n">
         <v>46</v>
@@ -9866,7 +9866,7 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D209" s="2" t="n">
@@ -9901,7 +9901,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -9911,26 +9911,26 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E210" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H210" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -9956,26 +9956,26 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>596</v>
+        <v>646</v>
       </c>
       <c r="E211" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>-26</v>
+        <v>24</v>
       </c>
       <c r="G211" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H211" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -10001,17 +10001,17 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>596</v>
+        <v>529</v>
       </c>
       <c r="E212" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F212" s="2" t="n">
-        <v>-26</v>
+        <v>-93</v>
       </c>
       <c r="G212" s="2" t="n">
         <v>30</v>
@@ -10036,7 +10036,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -10050,22 +10050,22 @@
         </is>
       </c>
       <c r="D213" s="2" t="n">
-        <v>646</v>
+        <v>529</v>
       </c>
       <c r="E213" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F213" s="2" t="n">
-        <v>24</v>
+        <v>-93</v>
       </c>
       <c r="G213" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H213" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -10091,17 +10091,17 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D214" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E214" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="G214" s="2" t="n">
         <v>46</v>
@@ -10126,7 +10126,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -10136,7 +10136,7 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D215" s="2" t="n">
@@ -10171,7 +10171,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -10181,26 +10181,26 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>529</v>
+        <v>833</v>
       </c>
       <c r="E216" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F216" s="2" t="n">
-        <v>-93</v>
+        <v>211</v>
       </c>
       <c r="G216" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H216" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J216" s="3" t="inlineStr">
         <is>
@@ -10216,7 +10216,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -10226,26 +10226,26 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E217" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -10271,26 +10271,26 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D218" s="2" t="n">
-        <v>698</v>
+        <v>529</v>
       </c>
       <c r="E218" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>76</v>
+        <v>-93</v>
       </c>
       <c r="G218" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H218" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D219" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E219" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="G219" s="2" t="n">
         <v>46</v>
@@ -10351,7 +10351,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -10361,26 +10361,26 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D220" s="2" t="n">
-        <v>698</v>
+        <v>788</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F220" s="2" t="n">
-        <v>76</v>
+        <v>-110</v>
       </c>
       <c r="G220" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H220" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J220" s="3" t="inlineStr">
         <is>
@@ -10396,7 +10396,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -10406,26 +10406,26 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D221" s="2" t="n">
-        <v>833</v>
+        <v>788</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F221" s="2" t="n">
-        <v>211</v>
+        <v>-110</v>
       </c>
       <c r="G221" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H221" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J221" s="3" t="inlineStr">
         <is>
@@ -10441,7 +10441,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -10451,26 +10451,26 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D222" s="2" t="n">
-        <v>529</v>
+        <v>788</v>
       </c>
       <c r="E222" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F222" s="2" t="n">
-        <v>-93</v>
+        <v>-110</v>
       </c>
       <c r="G222" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H222" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I222" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J222" s="3" t="inlineStr">
         <is>
@@ -10486,7 +10486,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -10496,26 +10496,26 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D223" s="2" t="n">
-        <v>529</v>
+        <v>788</v>
       </c>
       <c r="E223" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F223" s="2" t="n">
-        <v>-93</v>
+        <v>-110</v>
       </c>
       <c r="G223" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H223" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I223" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J223" s="3" t="inlineStr">
         <is>
@@ -10531,7 +10531,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -10541,26 +10541,26 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D224" s="2" t="n">
-        <v>753</v>
+        <v>788</v>
       </c>
       <c r="E224" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F224" s="2" t="n">
-        <v>131</v>
+        <v>-110</v>
       </c>
       <c r="G224" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H224" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I224" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J224" s="3" t="inlineStr">
         <is>
@@ -10586,30 +10586,30 @@
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D225" s="2" t="n">
-        <v>646</v>
+        <v>1018</v>
       </c>
       <c r="E225" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F225" s="2" t="n">
-        <v>-252</v>
+        <v>120</v>
       </c>
       <c r="G225" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H225" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I225" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J225" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J225" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K225" s="2" t="inlineStr">
@@ -10631,26 +10631,26 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D226" s="2" t="n">
-        <v>788</v>
+        <v>1018</v>
       </c>
       <c r="E226" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F226" s="2" t="n">
-        <v>-110</v>
+        <v>120</v>
       </c>
       <c r="G226" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H226" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I226" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J226" s="3" t="inlineStr">
         <is>
@@ -10676,26 +10676,26 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D227" s="2" t="n">
-        <v>788</v>
+        <v>1018</v>
       </c>
       <c r="E227" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F227" s="2" t="n">
-        <v>-110</v>
+        <v>120</v>
       </c>
       <c r="G227" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H227" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I227" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J227" s="3" t="inlineStr">
         <is>
@@ -10721,7 +10721,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D228" s="2" t="n">
@@ -10766,17 +10766,17 @@
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D229" s="2" t="n">
-        <v>1018</v>
+        <v>1075</v>
       </c>
       <c r="E229" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F229" s="2" t="n">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="G229" s="2" t="n">
         <v>46</v>
@@ -10801,7 +10801,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -10811,26 +10811,26 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D230" s="2" t="n">
-        <v>1018</v>
+        <v>788</v>
       </c>
       <c r="E230" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F230" s="2" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="G230" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H230" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I230" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J230" s="3" t="inlineStr">
         <is>
@@ -10846,7 +10846,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -10856,26 +10856,26 @@
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D231" s="2" t="n">
-        <v>1018</v>
+        <v>788</v>
       </c>
       <c r="E231" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F231" s="2" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="G231" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H231" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I231" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J231" s="3" t="inlineStr">
         <is>
@@ -10891,7 +10891,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -10901,26 +10901,26 @@
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D232" s="2" t="n">
-        <v>1020</v>
+        <v>788</v>
       </c>
       <c r="E232" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F232" s="2" t="n">
-        <v>122</v>
+        <v>-110</v>
       </c>
       <c r="G232" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H232" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I232" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J232" s="3" t="inlineStr">
         <is>
@@ -10936,7 +10936,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -10946,26 +10946,26 @@
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D233" s="2" t="n">
-        <v>1020</v>
+        <v>788</v>
       </c>
       <c r="E233" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F233" s="2" t="n">
-        <v>122</v>
+        <v>-110</v>
       </c>
       <c r="G233" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H233" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I233" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J233" s="3" t="inlineStr">
         <is>
@@ -10981,7 +10981,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -10991,17 +10991,17 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D234" s="2" t="n">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="E234" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F234" s="2" t="n">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="G234" s="2" t="n">
         <v>46</v>
@@ -11026,7 +11026,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -11036,17 +11036,17 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D235" s="2" t="n">
-        <v>1075</v>
+        <v>1018</v>
       </c>
       <c r="E235" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F235" s="2" t="n">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="G235" s="2" t="n">
         <v>46</v>
@@ -11081,30 +11081,30 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D236" s="2" t="n">
-        <v>419</v>
+        <v>1018</v>
       </c>
       <c r="E236" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F236" s="2" t="n">
-        <v>-479</v>
+        <v>120</v>
       </c>
       <c r="G236" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H236" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I236" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J236" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J236" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K236" s="2" t="inlineStr">
@@ -11126,30 +11126,30 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D237" s="2" t="n">
-        <v>419</v>
+        <v>1018</v>
       </c>
       <c r="E237" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>-479</v>
+        <v>120</v>
       </c>
       <c r="G237" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H237" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I237" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J237" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J237" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K237" s="2" t="inlineStr">
@@ -11171,30 +11171,30 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>529</v>
+        <v>1020</v>
       </c>
       <c r="E238" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>-369</v>
+        <v>122</v>
       </c>
       <c r="G238" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H238" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I238" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J238" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J238" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
@@ -11216,26 +11216,26 @@
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D239" s="2" t="n">
-        <v>788</v>
+        <v>1075</v>
       </c>
       <c r="E239" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F239" s="2" t="n">
-        <v>-110</v>
+        <v>177</v>
       </c>
       <c r="G239" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H239" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I239" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J239" s="3" t="inlineStr">
         <is>
@@ -11251,7 +11251,7 @@
     <row r="240">
       <c r="A240" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B240" s="2" t="inlineStr">
@@ -11261,30 +11261,30 @@
       </c>
       <c r="C240" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D240" s="2" t="n">
-        <v>788</v>
+        <v>419</v>
       </c>
       <c r="E240" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F240" s="2" t="n">
-        <v>-110</v>
+        <v>-479</v>
       </c>
       <c r="G240" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H240" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I240" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J240" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J240" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K240" s="2" t="inlineStr">
@@ -11296,7 +11296,7 @@
     <row r="241">
       <c r="A241" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B241" s="2" t="inlineStr">
@@ -11306,30 +11306,30 @@
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D241" s="2" t="n">
-        <v>788</v>
+        <v>419</v>
       </c>
       <c r="E241" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F241" s="2" t="n">
-        <v>-110</v>
+        <v>-479</v>
       </c>
       <c r="G241" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H241" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I241" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J241" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J241" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K241" s="2" t="inlineStr">
@@ -11341,7 +11341,7 @@
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B242" s="2" t="inlineStr">
@@ -11351,30 +11351,30 @@
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D242" s="2" t="n">
-        <v>788</v>
+        <v>529</v>
       </c>
       <c r="E242" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F242" s="2" t="n">
-        <v>-110</v>
+        <v>-369</v>
       </c>
       <c r="G242" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H242" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I242" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J242" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J242" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K242" s="2" t="inlineStr">
@@ -11386,7 +11386,7 @@
     <row r="243">
       <c r="A243" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B243" s="2" t="inlineStr">
@@ -11396,30 +11396,30 @@
       </c>
       <c r="C243" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D243" s="2" t="n">
-        <v>788</v>
+        <v>529</v>
       </c>
       <c r="E243" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F243" s="2" t="n">
-        <v>-110</v>
+        <v>-369</v>
       </c>
       <c r="G243" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H243" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I243" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J243" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J243" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K243" s="2" t="inlineStr">
@@ -11431,7 +11431,7 @@
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B244" s="2" t="inlineStr">
@@ -11441,26 +11441,26 @@
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D244" s="2" t="n">
-        <v>1018</v>
+        <v>788</v>
       </c>
       <c r="E244" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F244" s="2" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="G244" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H244" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I244" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J244" s="3" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B245" s="2" t="inlineStr">
@@ -11486,26 +11486,26 @@
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D245" s="2" t="n">
-        <v>1018</v>
+        <v>788</v>
       </c>
       <c r="E245" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F245" s="2" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="G245" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H245" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I245" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J245" s="3" t="inlineStr">
         <is>
@@ -11521,7 +11521,7 @@
     <row r="246">
       <c r="A246" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B246" s="2" t="inlineStr">
@@ -11531,26 +11531,26 @@
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D246" s="2" t="n">
-        <v>1018</v>
+        <v>788</v>
       </c>
       <c r="E246" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F246" s="2" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="G246" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H246" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I246" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J246" s="3" t="inlineStr">
         <is>
@@ -11566,7 +11566,7 @@
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B247" s="2" t="inlineStr">
@@ -11576,26 +11576,26 @@
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D247" s="2" t="n">
-        <v>1018</v>
+        <v>788</v>
       </c>
       <c r="E247" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F247" s="2" t="n">
-        <v>120</v>
+        <v>-110</v>
       </c>
       <c r="G247" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H247" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I247" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J247" s="3" t="inlineStr">
         <is>
@@ -11611,7 +11611,7 @@
     <row r="248">
       <c r="A248" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B248" s="2" t="inlineStr">
@@ -11621,17 +11621,17 @@
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D248" s="2" t="n">
-        <v>1075</v>
+        <v>1018</v>
       </c>
       <c r="E248" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F248" s="2" t="n">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="G248" s="2" t="n">
         <v>46</v>
@@ -11666,30 +11666,30 @@
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D249" s="2" t="n">
-        <v>419</v>
+        <v>1018</v>
       </c>
       <c r="E249" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F249" s="2" t="n">
-        <v>-479</v>
+        <v>120</v>
       </c>
       <c r="G249" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H249" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I249" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J249" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J249" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K249" s="2" t="inlineStr">
@@ -11711,30 +11711,30 @@
       </c>
       <c r="C250" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D250" s="2" t="n">
-        <v>596</v>
+        <v>1018</v>
       </c>
       <c r="E250" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F250" s="2" t="n">
-        <v>-302</v>
+        <v>120</v>
       </c>
       <c r="G250" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H250" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I250" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J250" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J250" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K250" s="2" t="inlineStr">
@@ -11756,30 +11756,30 @@
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D251" s="2" t="n">
-        <v>646</v>
+        <v>1075</v>
       </c>
       <c r="E251" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F251" s="2" t="n">
-        <v>-252</v>
+        <v>177</v>
       </c>
       <c r="G251" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H251" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I251" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J251" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J251" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K251" s="2" t="inlineStr">
@@ -11801,438 +11801,33 @@
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D252" s="2" t="n">
-        <v>646</v>
+        <v>1113</v>
       </c>
       <c r="E252" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F252" s="2" t="n">
-        <v>-252</v>
+        <v>215</v>
       </c>
       <c r="G252" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H252" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I252" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J252" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J252" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K252" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B253" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C253" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-317</t>
-        </is>
-      </c>
-      <c r="D253" s="2" t="n">
-        <v>788</v>
-      </c>
-      <c r="E253" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F253" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G253" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H253" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I253" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J253" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K253" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="254">
-      <c r="A254" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B254" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C254" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-315</t>
-        </is>
-      </c>
-      <c r="D254" s="2" t="n">
-        <v>788</v>
-      </c>
-      <c r="E254" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F254" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G254" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H254" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I254" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J254" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K254" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="255">
-      <c r="A255" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B255" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C255" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D255" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E255" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F255" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G255" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H255" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I255" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J255" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K255" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="256">
-      <c r="A256" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B256" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C256" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D256" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E256" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F256" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G256" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H256" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I256" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J256" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K256" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="257">
-      <c r="A257" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B257" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C257" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D257" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E257" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F257" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G257" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H257" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I257" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J257" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K257" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="258">
-      <c r="A258" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B258" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C258" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-391</t>
-        </is>
-      </c>
-      <c r="D258" s="2" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E258" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F258" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="G258" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H258" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I258" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J258" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K258" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="259">
-      <c r="A259" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B259" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C259" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-381</t>
-        </is>
-      </c>
-      <c r="D259" s="2" t="n">
-        <v>1020</v>
-      </c>
-      <c r="E259" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F259" s="2" t="n">
-        <v>122</v>
-      </c>
-      <c r="G259" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H259" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I259" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J259" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K259" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B260" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C260" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D260" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E260" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F260" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G260" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H260" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I260" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J260" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K260" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B261" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C261" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D261" s="2" t="n">
-        <v>1113</v>
-      </c>
-      <c r="E261" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F261" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="G261" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H261" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I261" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J261" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K261" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K252"/>
+  <dimension ref="A1:K238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -596,7 +596,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -641,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -681,7 +681,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-486</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -693,10 +693,10 @@
         <v>698</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-200</v>
+        <v>-278</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>23</v>
@@ -726,7 +726,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-486</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -738,10 +738,10 @@
         <v>753</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-145</v>
+        <v>-223</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -754,7 +754,7 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-486</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -783,10 +783,10 @@
         <v>753</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>-145</v>
+        <v>-223</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -799,7 +799,7 @@
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-486</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -828,10 +828,10 @@
         <v>833</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-65</v>
+        <v>-143</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -842,7 +842,7 @@
       <c r="I8" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J8" s="4" t="inlineStr">
+      <c r="J8" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -861,31 +861,31 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-486</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>980</v>
+        <v>909</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>82</v>
+        <v>-67</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -906,22 +906,22 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SM-490</t>
+          <t>SM-486</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1018</v>
+        <v>980</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>120</v>
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -951,31 +951,31 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-486</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>698</v>
+        <v>1018</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>820</v>
+        <v>976</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-122</v>
+        <v>42</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
@@ -996,35 +996,35 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-67</v>
+        <v>-200</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1041,22 +1041,22 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
         <v>753</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-67</v>
+        <v>-145</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>46</v>
@@ -1067,7 +1067,7 @@
       <c r="I13" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1086,22 +1086,22 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>13</v>
+        <v>-145</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,7 +1112,7 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
+      <c r="J14" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1131,22 +1131,22 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>980</v>
+        <v>833</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>160</v>
+        <v>-65</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1176,22 +1176,22 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1018</v>
+        <v>980</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>198</v>
+        <v>82</v>
       </c>
       <c r="G16" s="2" t="n">
         <v>46</v>
@@ -1216,27 +1216,27 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>SM-494</t>
+          <t>SM-490</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>753</v>
+        <v>1018</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-145</v>
+        <v>120</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>46</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1275,26 +1275,26 @@
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>898</v>
+        <v>820</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-145</v>
+        <v>-122</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1323,10 +1323,10 @@
         <v>753</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>898</v>
+        <v>820</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-145</v>
+        <v>-67</v>
       </c>
       <c r="G19" s="2" t="n">
         <v>46</v>
@@ -1337,7 +1337,7 @@
       <c r="I19" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J19" s="4" t="inlineStr">
+      <c r="J19" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>980</v>
+        <v>753</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>898</v>
+        <v>820</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>82</v>
+        <v>-67</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>46</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J20" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1410,13 +1410,13 @@
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-67</v>
+        <v>13</v>
       </c>
       <c r="G21" s="2" t="n">
         <v>46</v>
@@ -1427,7 +1427,7 @@
       <c r="I21" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J21" s="4" t="inlineStr">
+      <c r="J21" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>753</v>
+        <v>980</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-67</v>
+        <v>160</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>21-MAY-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>753</v>
+        <v>1018</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-67</v>
+        <v>198</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>46</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J23" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,28 +1541,28 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>909</v>
+        <v>753</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1246</v>
+        <v>898</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-337</v>
+        <v>-145</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>804</v>
+        <v>753</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1753</v>
+        <v>898</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-949</v>
+        <v>-145</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>804</v>
+        <v>753</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1753</v>
+        <v>898</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-949</v>
+        <v>-145</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>30</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1126</v>
+        <v>980</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1753</v>
+        <v>898</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-627</v>
+        <v>82</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,28 +1721,28 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1296</v>
+        <v>753</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-457</v>
+        <v>-67</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,28 +1766,28 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1296</v>
+        <v>753</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-457</v>
+        <v>-67</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,28 +1811,28 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>559</v>
+        <v>753</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1054</v>
+        <v>820</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-495</v>
+        <v>-67</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J30" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,28 +1856,28 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>671</v>
+        <v>799</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1054</v>
+        <v>1246</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-383</v>
+        <v>-447</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,28 +1901,28 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>719</v>
+        <v>799</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1054</v>
+        <v>1246</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-335</v>
+        <v>-447</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>788</v>
+        <v>909</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1054</v>
+        <v>1246</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-266</v>
+        <v>-337</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-266</v>
+        <v>-949</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>788</v>
+        <v>804</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-266</v>
+        <v>-949</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>788</v>
+        <v>1009</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-266</v>
+        <v>-744</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>10-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>639</v>
+        <v>1296</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>682</v>
+        <v>1753</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-43</v>
+        <v>-457</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>494</v>
+        <v>1296</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-866</v>
+        <v>-457</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>30</v>
+        <v>7</v>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,28 +2216,28 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>494</v>
+        <v>1499</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1360</v>
+        <v>1753</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-866</v>
+        <v>-254</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J39" s="5" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>16-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>494</v>
+        <v>559</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-866</v>
+        <v>-495</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>449</v>
+        <v>671</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-911</v>
+        <v>-383</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>494</v>
+        <v>719</v>
       </c>
       <c r="E42" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-866</v>
+        <v>-335</v>
       </c>
       <c r="G42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="H42" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I42" s="2" t="n">
-        <v>30</v>
-      </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>494</v>
+        <v>788</v>
       </c>
       <c r="E43" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-866</v>
+        <v>-266</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J43" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>494</v>
+        <v>788</v>
       </c>
       <c r="E44" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-866</v>
+        <v>-266</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>17-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>719</v>
+        <v>788</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-641</v>
+        <v>-266</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>494</v>
+        <v>788</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>1360</v>
+        <v>1054</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-866</v>
+        <v>-266</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J46" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J46" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>494</v>
+        <v>489</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>1360</v>
+        <v>742</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-866</v>
+        <v>-253</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J47" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>671</v>
+        <v>489</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>1360</v>
+        <v>742</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-689</v>
+        <v>-253</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J48" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,30 +2666,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>799</v>
+        <v>599</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>1360</v>
+        <v>742</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-561</v>
+        <v>-143</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J49" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>18-JUN-26</t>
+          <t>09-JUN-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2715,26 +2715,26 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>836</v>
+        <v>599</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>1360</v>
+        <v>682</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-524</v>
+        <v>-83</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>10-JUN-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>596</v>
+        <v>639</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>1360</v>
+        <v>682</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-764</v>
+        <v>-43</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>30</v>
@@ -2777,9 +2777,9 @@
       <c r="I51" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,28 +2801,28 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>671</v>
+        <v>449</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-689</v>
+        <v>-911</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J52" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,28 +2846,28 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>775</v>
+        <v>449</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-585</v>
+        <v>-911</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J53" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,28 +2891,28 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>799</v>
+        <v>494</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-561</v>
+        <v>-866</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,28 +2936,28 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>836</v>
+        <v>494</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-524</v>
+        <v>-866</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J55" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J55" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,28 +2981,28 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>903</v>
+        <v>494</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-457</v>
+        <v>-866</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J56" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>16-JUN-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3030,24 +3030,24 @@
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>906</v>
+        <v>599</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-454</v>
+        <v>-761</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,28 +3071,28 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1113</v>
+        <v>429</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-247</v>
+        <v>-931</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,28 +3116,28 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>1113</v>
+        <v>449</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-247</v>
+        <v>-911</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,28 +3161,28 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>1113</v>
+        <v>494</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-247</v>
+        <v>-866</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,28 +3206,28 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>1113</v>
+        <v>494</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-247</v>
+        <v>-866</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>22-JUN-26</t>
+          <t>17-JUN-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,28 +3251,28 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>1170</v>
+        <v>719</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-190</v>
+        <v>-641</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,28 +3296,28 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>619</v>
+        <v>494</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-741</v>
+        <v>-866</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,28 +3341,28 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>619</v>
+        <v>494</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-741</v>
+        <v>-866</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J64" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,28 +3386,28 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>671</v>
+        <v>559</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-689</v>
+        <v>-801</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J65" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,7 +3431,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
@@ -3452,7 +3452,7 @@
       <c r="I66" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J66" s="5" t="inlineStr">
+      <c r="J66" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>18-JUN-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,28 +3476,28 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>671</v>
+        <v>719</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-689</v>
+        <v>-641</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>789</v>
+        <v>419</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-571</v>
+        <v>-941</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,28 +3566,28 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>1113</v>
+        <v>494</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-247</v>
+        <v>-866</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,28 +3611,28 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>1113</v>
+        <v>494</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-247</v>
+        <v>-866</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,28 +3656,28 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>1113</v>
+        <v>494</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-247</v>
+        <v>-866</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
+        <v>30</v>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,28 +3701,28 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>1113</v>
+        <v>619</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-247</v>
+        <v>-741</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>23-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,28 +3746,28 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>1170</v>
+        <v>719</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-190</v>
+        <v>-641</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,28 +3791,28 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>727</v>
+        <v>789</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-633</v>
+        <v>-571</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,28 +3836,28 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>727</v>
+        <v>1113</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-633</v>
+        <v>-247</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,28 +3881,28 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>799</v>
+        <v>1113</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-561</v>
+        <v>-247</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,28 +3926,28 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>844</v>
+        <v>1113</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-516</v>
+        <v>-247</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,28 +3971,28 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>844</v>
+        <v>1113</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-516</v>
+        <v>-247</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>22-JUN-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,28 +4016,28 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>844</v>
+        <v>1170</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-516</v>
+        <v>-190</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J79" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,30 +4061,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>1309</v>
+        <v>671</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-51</v>
+        <v>-689</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,30 +4106,30 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>1358</v>
+        <v>671</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-2</v>
+        <v>-689</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J81" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,30 +4151,30 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>1358</v>
+        <v>671</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-2</v>
+        <v>-689</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J82" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K82" s="2" t="inlineStr">
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>1358</v>
+        <v>1113</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-2</v>
+        <v>-247</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>46</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>1358</v>
+        <v>1113</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-2</v>
+        <v>-247</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>46</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>24-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,17 +4286,17 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>1415</v>
+        <v>1113</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>55</v>
+        <v>-247</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>46</v>
@@ -4307,9 +4307,9 @@
       <c r="I85" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J85" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,30 +4331,30 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>1309</v>
+        <v>1113</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-51</v>
+        <v>-247</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J86" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>23-JUN-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,17 +4376,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>1358</v>
+        <v>1170</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-2</v>
+        <v>-190</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>46</v>
@@ -4399,7 +4399,7 @@
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,30 +4421,30 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>1358</v>
+        <v>489</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-2</v>
+        <v>-871</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J88" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,30 +4466,30 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>1358</v>
+        <v>727</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-2</v>
+        <v>-633</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J89" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,30 +4511,30 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>1358</v>
+        <v>727</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-2</v>
+        <v>-633</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J90" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K90" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>25-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,30 +4556,30 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>1415</v>
+        <v>844</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>55</v>
+        <v>-516</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J91" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K91" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,28 +4601,28 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>876</v>
+        <v>844</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-484</v>
+        <v>-516</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J92" s="5" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,30 +4646,30 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>1059</v>
+        <v>844</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-301</v>
+        <v>-516</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,30 +4691,30 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>1099</v>
+        <v>1309</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-261</v>
+        <v>-51</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J94" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,28 +4736,28 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>1176</v>
+        <v>1358</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-184</v>
+        <v>-2</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J95" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
@@ -4802,7 +4802,7 @@
       <c r="I96" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J96" s="4" t="inlineStr">
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
@@ -4847,7 +4847,7 @@
       <c r="I97" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J97" s="4" t="inlineStr">
+      <c r="J97" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
@@ -4892,7 +4892,7 @@
       <c r="I98" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J98" s="4" t="inlineStr">
+      <c r="J98" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>24-JUN-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1358</v>
+        <v>1415</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-2</v>
+        <v>55</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>46</v>
@@ -4937,9 +4937,9 @@
       <c r="I99" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J99" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J99" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1415</v>
+        <v>1358</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>55</v>
+        <v>-2</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>46</v>
@@ -4982,9 +4982,9 @@
       <c r="I100" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>29-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,17 +5006,17 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>1544</v>
+        <v>1358</v>
       </c>
       <c r="E101" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>184</v>
+        <v>-2</v>
       </c>
       <c r="G101" s="2" t="n">
         <v>46</v>
@@ -5027,9 +5027,9 @@
       <c r="I101" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,28 +5051,28 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>899</v>
+        <v>1358</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-461</v>
+        <v>-2</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J102" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J102" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,30 +5096,30 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>999</v>
+        <v>1358</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-361</v>
+        <v>-2</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J103" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>25-JUN-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,26 +5141,26 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1259</v>
+        <v>1415</v>
       </c>
       <c r="E104" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-101</v>
+        <v>55</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,30 +5186,30 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1358</v>
+        <v>699</v>
       </c>
       <c r="E105" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-2</v>
+        <v>-661</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J105" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,28 +5231,28 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1358</v>
+        <v>899</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>-2</v>
+        <v>-461</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J106" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J106" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,28 +5276,28 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1358</v>
+        <v>1059</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>-2</v>
+        <v>-301</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J107" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,28 +5321,28 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1358</v>
+        <v>1059</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-2</v>
+        <v>-301</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>30-JUN-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>1415</v>
+        <v>1358</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>1360</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>55</v>
+        <v>-2</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>46</v>
@@ -5387,9 +5387,9 @@
       <c r="I109" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,30 +5411,30 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>559</v>
+        <v>1358</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-417</v>
+        <v>-2</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,30 +5456,30 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>699</v>
+        <v>1358</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-277</v>
+        <v>-2</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J111" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J111" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>01-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,30 +5501,30 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>976</v>
+        <v>1358</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>0</v>
+        <v>-2</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H112" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J112" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J112" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>29-JUN-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,30 +5546,30 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>799</v>
+        <v>1415</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-177</v>
+        <v>55</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K113" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,28 +5591,28 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-70</v>
+        <v>-461</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J114" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,26 +5636,26 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1076</v>
+        <v>999</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>100</v>
+        <v>-361</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>02-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,26 +5681,26 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1099</v>
+        <v>1259</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>123</v>
+        <v>-101</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,28 +5726,28 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>449</v>
+        <v>1358</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-527</v>
+        <v>-2</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J117" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J117" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,30 +5771,30 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>619</v>
+        <v>1358</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>-357</v>
+        <v>-2</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J118" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K118" s="2" t="inlineStr">
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,30 +5816,30 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>698</v>
+        <v>1358</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>-278</v>
+        <v>-2</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,30 +5861,30 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>698</v>
+        <v>1358</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>-278</v>
+        <v>-2</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>30-JUN-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,26 +5906,26 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>698</v>
+        <v>1415</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>976</v>
+        <v>1360</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-278</v>
+        <v>55</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,30 +5951,30 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>753</v>
+        <v>619</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-223</v>
+        <v>-357</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J122" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K122" s="2" t="inlineStr">
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,26 +5996,26 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>755</v>
+        <v>699</v>
       </c>
       <c r="E123" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>-221</v>
+        <v>-277</v>
       </c>
       <c r="G123" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H123" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J123" s="3" t="inlineStr">
         <is>
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>01-JUL-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,26 +6041,26 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>788</v>
+        <v>859</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-188</v>
+        <v>-117</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,26 +6086,26 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>788</v>
+        <v>619</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>-188</v>
+        <v>-357</v>
       </c>
       <c r="G125" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H125" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J125" s="3" t="inlineStr">
         <is>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>02-JUL-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6180,13 +6180,13 @@
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>789</v>
+        <v>959</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>-187</v>
+        <v>-17</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>30</v>
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,17 +6221,17 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>619</v>
+        <v>449</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-357</v>
+        <v>-527</v>
       </c>
       <c r="G128" s="2" t="n">
         <v>15</v>
@@ -6242,9 +6242,9 @@
       <c r="I128" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,7 +6266,7 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6356,30 +6356,30 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E131" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-223</v>
+        <v>-278</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J131" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K131" s="2" t="inlineStr">
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,30 +6401,30 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-223</v>
+        <v>-278</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J132" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K132" s="2" t="inlineStr">
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,30 +6446,30 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-221</v>
+        <v>-223</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J133" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K133" s="2" t="inlineStr">
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>788</v>
+        <v>755</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-188</v>
+        <v>-221</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>23</v>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,7 +6536,7 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,26 +6581,26 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6626,30 +6626,30 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>833</v>
+        <v>789</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-143</v>
+        <v>-187</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J137" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6671,30 +6671,30 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>419</v>
+        <v>789</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>-557</v>
+        <v>-187</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J138" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,26 +6716,26 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>619</v>
+        <v>698</v>
       </c>
       <c r="E139" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-357</v>
+        <v>-278</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,30 +6806,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E141" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,17 +6851,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="E142" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>-278</v>
+        <v>-221</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>23</v>
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6896,17 +6896,17 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>698</v>
+        <v>788</v>
       </c>
       <c r="E143" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-278</v>
+        <v>-188</v>
       </c>
       <c r="G143" s="2" t="n">
         <v>23</v>
@@ -6931,7 +6931,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6941,17 +6941,17 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="E144" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>-221</v>
+        <v>-188</v>
       </c>
       <c r="G144" s="2" t="n">
         <v>23</v>
@@ -6976,7 +6976,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6986,30 +6986,30 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>788</v>
+        <v>833</v>
       </c>
       <c r="E145" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>-188</v>
+        <v>-143</v>
       </c>
       <c r="G145" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H145" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J145" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K145" s="2" t="inlineStr">
@@ -7031,17 +7031,17 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>788</v>
+        <v>698</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>-188</v>
+        <v>-278</v>
       </c>
       <c r="G146" s="2" t="n">
         <v>23</v>
@@ -7076,30 +7076,30 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>906</v>
+        <v>698</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>-70</v>
+        <v>-278</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7121,26 +7121,26 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>619</v>
+        <v>698</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>-357</v>
+        <v>-278</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H148" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J148" s="3" t="inlineStr">
         <is>
@@ -7156,7 +7156,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7166,26 +7166,26 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
-        <v>619</v>
+        <v>698</v>
       </c>
       <c r="E149" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F149" s="2" t="n">
-        <v>-357</v>
+        <v>-278</v>
       </c>
       <c r="G149" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H149" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J149" s="3" t="inlineStr">
         <is>
@@ -7201,7 +7201,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7211,30 +7211,30 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E150" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F150" s="2" t="n">
-        <v>-223</v>
+        <v>-221</v>
       </c>
       <c r="G150" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H150" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J150" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K150" s="2" t="inlineStr">
@@ -7246,7 +7246,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7256,17 +7256,17 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>755</v>
+        <v>788</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>-221</v>
+        <v>-188</v>
       </c>
       <c r="G151" s="2" t="n">
         <v>23</v>
@@ -7291,7 +7291,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7301,26 +7301,26 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>-187</v>
+        <v>-188</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H152" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J152" s="3" t="inlineStr">
         <is>
@@ -7346,30 +7346,30 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>789</v>
+        <v>753</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>-187</v>
+        <v>-223</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H153" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>833</v>
+        <v>755</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>-143</v>
+        <v>-221</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H154" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J154" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
@@ -7457,7 +7457,7 @@
       <c r="I155" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J155" s="4" t="inlineStr">
+      <c r="J155" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>923</v>
+        <v>833</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>-53</v>
+        <v>-143</v>
       </c>
       <c r="G156" s="2" t="n">
         <v>46</v>
@@ -7502,7 +7502,7 @@
       <c r="I156" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J156" s="4" t="inlineStr">
+      <c r="J156" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7516,7 +7516,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7526,28 +7526,28 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
-        <v>449</v>
+        <v>923</v>
       </c>
       <c r="E157" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F157" s="2" t="n">
-        <v>-527</v>
+        <v>-53</v>
       </c>
       <c r="G157" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H157" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J157" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J157" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7571,30 +7571,30 @@
       </c>
       <c r="C158" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D158" s="2" t="n">
-        <v>619</v>
+        <v>671</v>
       </c>
       <c r="E158" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F158" s="2" t="n">
-        <v>-357</v>
+        <v>-305</v>
       </c>
       <c r="G158" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H158" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J158" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K158" s="2" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
@@ -7637,7 +7637,7 @@
       <c r="I159" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J159" s="4" t="inlineStr">
+      <c r="J159" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -7661,17 +7661,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>-305</v>
+        <v>-278</v>
       </c>
       <c r="G160" s="2" t="n">
         <v>23</v>
@@ -7682,9 +7682,9 @@
       <c r="I160" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J160" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K160" s="2" t="inlineStr">
@@ -7706,7 +7706,7 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="C162" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D162" s="2" t="n">
@@ -7796,17 +7796,17 @@
       </c>
       <c r="C163" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D163" s="2" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="E163" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F163" s="2" t="n">
-        <v>-278</v>
+        <v>-221</v>
       </c>
       <c r="G163" s="2" t="n">
         <v>23</v>
@@ -7841,30 +7841,30 @@
       </c>
       <c r="C164" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D164" s="2" t="n">
-        <v>755</v>
+        <v>833</v>
       </c>
       <c r="E164" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F164" s="2" t="n">
-        <v>-221</v>
+        <v>-143</v>
       </c>
       <c r="G164" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H164" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J164" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J164" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K164" s="2" t="inlineStr">
@@ -7876,7 +7876,7 @@
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B165" s="2" t="inlineStr">
@@ -7886,26 +7886,26 @@
       </c>
       <c r="C165" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D165" s="2" t="n">
-        <v>789</v>
+        <v>619</v>
       </c>
       <c r="E165" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F165" s="2" t="n">
-        <v>-187</v>
+        <v>-357</v>
       </c>
       <c r="G165" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H165" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J165" s="3" t="inlineStr">
         <is>
@@ -7921,7 +7921,7 @@
     <row r="166">
       <c r="A166" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B166" s="2" t="inlineStr">
@@ -7931,26 +7931,26 @@
       </c>
       <c r="C166" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D166" s="2" t="n">
-        <v>789</v>
+        <v>619</v>
       </c>
       <c r="E166" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F166" s="2" t="n">
-        <v>-187</v>
+        <v>-357</v>
       </c>
       <c r="G166" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H166" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J166" s="3" t="inlineStr">
         <is>
@@ -7966,7 +7966,7 @@
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B167" s="2" t="inlineStr">
@@ -7976,28 +7976,28 @@
       </c>
       <c r="C167" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D167" s="2" t="n">
-        <v>833</v>
+        <v>671</v>
       </c>
       <c r="E167" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F167" s="2" t="n">
-        <v>-143</v>
+        <v>-305</v>
       </c>
       <c r="G167" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H167" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J167" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8021,7 +8021,7 @@
       </c>
       <c r="C168" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D168" s="2" t="n">
@@ -8042,7 +8042,7 @@
       <c r="I168" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J168" s="4" t="inlineStr">
+      <c r="J168" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8066,17 +8066,17 @@
       </c>
       <c r="C169" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D169" s="2" t="n">
-        <v>671</v>
+        <v>698</v>
       </c>
       <c r="E169" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F169" s="2" t="n">
-        <v>-305</v>
+        <v>-278</v>
       </c>
       <c r="G169" s="2" t="n">
         <v>23</v>
@@ -8087,9 +8087,9 @@
       <c r="I169" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J169" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K169" s="2" t="inlineStr">
@@ -8111,7 +8111,7 @@
       </c>
       <c r="C170" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D170" s="2" t="n">
@@ -8156,17 +8156,17 @@
       </c>
       <c r="C171" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D171" s="2" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="E171" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F171" s="2" t="n">
-        <v>-278</v>
+        <v>-221</v>
       </c>
       <c r="G171" s="2" t="n">
         <v>23</v>
@@ -8201,26 +8201,26 @@
       </c>
       <c r="C172" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D172" s="2" t="n">
-        <v>755</v>
+        <v>789</v>
       </c>
       <c r="E172" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F172" s="2" t="n">
-        <v>-221</v>
+        <v>-187</v>
       </c>
       <c r="G172" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H172" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J172" s="3" t="inlineStr">
         <is>
@@ -8246,30 +8246,30 @@
       </c>
       <c r="C173" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D173" s="2" t="n">
-        <v>789</v>
+        <v>833</v>
       </c>
       <c r="E173" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F173" s="2" t="n">
-        <v>-187</v>
+        <v>-143</v>
       </c>
       <c r="G173" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H173" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J173" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J173" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K173" s="2" t="inlineStr">
@@ -8281,7 +8281,7 @@
     <row r="174">
       <c r="A174" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B174" s="2" t="inlineStr">
@@ -8291,28 +8291,28 @@
       </c>
       <c r="C174" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D174" s="2" t="n">
-        <v>833</v>
+        <v>489</v>
       </c>
       <c r="E174" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F174" s="2" t="n">
-        <v>-143</v>
+        <v>-487</v>
       </c>
       <c r="G174" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H174" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J174" s="4" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J174" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8336,30 +8336,30 @@
       </c>
       <c r="C175" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D175" s="2" t="n">
-        <v>671</v>
+        <v>619</v>
       </c>
       <c r="E175" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F175" s="2" t="n">
-        <v>-305</v>
+        <v>-357</v>
       </c>
       <c r="G175" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H175" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J175" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J175" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K175" s="2" t="inlineStr">
@@ -8381,7 +8381,7 @@
       </c>
       <c r="C176" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D176" s="2" t="n">
@@ -8402,7 +8402,7 @@
       <c r="I176" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J176" s="4" t="inlineStr">
+      <c r="J176" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8426,17 +8426,17 @@
       </c>
       <c r="C177" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D177" s="2" t="n">
-        <v>698</v>
+        <v>671</v>
       </c>
       <c r="E177" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F177" s="2" t="n">
-        <v>-278</v>
+        <v>-305</v>
       </c>
       <c r="G177" s="2" t="n">
         <v>23</v>
@@ -8447,9 +8447,9 @@
       <c r="I177" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J177" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J177" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K177" s="2" t="inlineStr">
@@ -8471,7 +8471,7 @@
       </c>
       <c r="C178" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D178" s="2" t="n">
@@ -8516,7 +8516,7 @@
       </c>
       <c r="C179" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D179" s="2" t="n">
@@ -8561,17 +8561,17 @@
       </c>
       <c r="C180" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D180" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E180" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F180" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G180" s="2" t="n">
         <v>23</v>
@@ -8606,30 +8606,30 @@
       </c>
       <c r="C181" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D181" s="2" t="n">
-        <v>799</v>
+        <v>755</v>
       </c>
       <c r="E181" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F181" s="2" t="n">
-        <v>-177</v>
+        <v>-221</v>
       </c>
       <c r="G181" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H181" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J181" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J181" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K181" s="2" t="inlineStr">
@@ -8651,30 +8651,30 @@
       </c>
       <c r="C182" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D182" s="2" t="n">
-        <v>799</v>
+        <v>789</v>
       </c>
       <c r="E182" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F182" s="2" t="n">
-        <v>-177</v>
+        <v>-187</v>
       </c>
       <c r="G182" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H182" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J182" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J182" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K182" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       <c r="I183" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J183" s="4" t="inlineStr">
+      <c r="J183" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -8731,7 +8731,7 @@
     <row r="184">
       <c r="A184" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B184" s="2" t="inlineStr">
@@ -8741,30 +8741,30 @@
       </c>
       <c r="C184" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D184" s="2" t="n">
-        <v>906</v>
+        <v>833</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F184" s="2" t="n">
-        <v>-70</v>
+        <v>211</v>
       </c>
       <c r="G184" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H184" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J184" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J184" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K184" s="2" t="inlineStr">
@@ -8776,7 +8776,7 @@
     <row r="185">
       <c r="A185" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B185" s="2" t="inlineStr">
@@ -8786,7 +8786,7 @@
       </c>
       <c r="C185" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D185" s="2" t="n">
@@ -8821,7 +8821,7 @@
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B186" s="2" t="inlineStr">
@@ -8831,26 +8831,26 @@
       </c>
       <c r="C186" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D186" s="2" t="n">
-        <v>559</v>
+        <v>833</v>
       </c>
       <c r="E186" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F186" s="2" t="n">
-        <v>-63</v>
+        <v>211</v>
       </c>
       <c r="G186" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H186" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J186" s="3" t="inlineStr">
         <is>
@@ -8866,7 +8866,7 @@
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B187" s="2" t="inlineStr">
@@ -8880,13 +8880,13 @@
         </is>
       </c>
       <c r="D187" s="2" t="n">
-        <v>599</v>
+        <v>529</v>
       </c>
       <c r="E187" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F187" s="2" t="n">
-        <v>-23</v>
+        <v>-93</v>
       </c>
       <c r="G187" s="2" t="n">
         <v>30</v>
@@ -8911,7 +8911,7 @@
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B188" s="2" t="inlineStr">
@@ -8921,26 +8921,26 @@
       </c>
       <c r="C188" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D188" s="2" t="n">
-        <v>833</v>
+        <v>559</v>
       </c>
       <c r="E188" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F188" s="2" t="n">
-        <v>211</v>
+        <v>-63</v>
       </c>
       <c r="G188" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H188" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J188" s="3" t="inlineStr">
         <is>
@@ -8956,7 +8956,7 @@
     <row r="189">
       <c r="A189" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B189" s="2" t="inlineStr">
@@ -8970,13 +8970,13 @@
         </is>
       </c>
       <c r="D189" s="2" t="n">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="E189" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F189" s="2" t="n">
-        <v>-93</v>
+        <v>-63</v>
       </c>
       <c r="G189" s="2" t="n">
         <v>30</v>
@@ -9001,7 +9001,7 @@
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B190" s="2" t="inlineStr">
@@ -9011,7 +9011,7 @@
       </c>
       <c r="C190" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D190" s="2" t="n">
@@ -9046,7 +9046,7 @@
     <row r="191">
       <c r="A191" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B191" s="2" t="inlineStr">
@@ -9056,26 +9056,26 @@
       </c>
       <c r="C191" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D191" s="2" t="n">
-        <v>529</v>
+        <v>833</v>
       </c>
       <c r="E191" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F191" s="2" t="n">
-        <v>-93</v>
+        <v>211</v>
       </c>
       <c r="G191" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H191" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J191" s="3" t="inlineStr">
         <is>
@@ -9091,7 +9091,7 @@
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B192" s="2" t="inlineStr">
@@ -9101,17 +9101,17 @@
       </c>
       <c r="C192" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D192" s="2" t="n">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="E192" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F192" s="2" t="n">
-        <v>-63</v>
+        <v>-93</v>
       </c>
       <c r="G192" s="2" t="n">
         <v>30</v>
@@ -9136,7 +9136,7 @@
     <row r="193">
       <c r="A193" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B193" s="2" t="inlineStr">
@@ -9146,26 +9146,26 @@
       </c>
       <c r="C193" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D193" s="2" t="n">
-        <v>559</v>
+        <v>833</v>
       </c>
       <c r="E193" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F193" s="2" t="n">
-        <v>-63</v>
+        <v>211</v>
       </c>
       <c r="G193" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H193" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J193" s="3" t="inlineStr">
         <is>
@@ -9181,7 +9181,7 @@
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B194" s="2" t="inlineStr">
@@ -9191,26 +9191,26 @@
       </c>
       <c r="C194" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D194" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E194" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F194" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G194" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H194" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J194" s="3" t="inlineStr">
         <is>
@@ -9226,7 +9226,7 @@
     <row r="195">
       <c r="A195" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B195" s="2" t="inlineStr">
@@ -9236,17 +9236,17 @@
       </c>
       <c r="C195" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D195" s="2" t="n">
-        <v>529</v>
+        <v>559</v>
       </c>
       <c r="E195" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F195" s="2" t="n">
-        <v>-93</v>
+        <v>-63</v>
       </c>
       <c r="G195" s="2" t="n">
         <v>30</v>
@@ -9271,7 +9271,7 @@
     <row r="196">
       <c r="A196" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B196" s="2" t="inlineStr">
@@ -9281,26 +9281,26 @@
       </c>
       <c r="C196" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D196" s="2" t="n">
-        <v>529</v>
+        <v>833</v>
       </c>
       <c r="E196" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F196" s="2" t="n">
-        <v>-93</v>
+        <v>211</v>
       </c>
       <c r="G196" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H196" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J196" s="3" t="inlineStr">
         <is>
@@ -9316,7 +9316,7 @@
     <row r="197">
       <c r="A197" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B197" s="2" t="inlineStr">
@@ -9326,17 +9326,17 @@
       </c>
       <c r="C197" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D197" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E197" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F197" s="2" t="n">
-        <v>76</v>
+        <v>211</v>
       </c>
       <c r="G197" s="2" t="n">
         <v>46</v>
@@ -9361,7 +9361,7 @@
     <row r="198">
       <c r="A198" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B198" s="2" t="inlineStr">
@@ -9371,26 +9371,26 @@
       </c>
       <c r="C198" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D198" s="2" t="n">
-        <v>646</v>
+        <v>529</v>
       </c>
       <c r="E198" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F198" s="2" t="n">
-        <v>24</v>
+        <v>-93</v>
       </c>
       <c r="G198" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H198" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J198" s="3" t="inlineStr">
         <is>
@@ -9406,7 +9406,7 @@
     <row r="199">
       <c r="A199" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B199" s="2" t="inlineStr">
@@ -9416,26 +9416,26 @@
       </c>
       <c r="C199" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D199" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E199" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F199" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G199" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H199" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J199" s="3" t="inlineStr">
         <is>
@@ -9451,7 +9451,7 @@
     <row r="200">
       <c r="A200" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B200" s="2" t="inlineStr">
@@ -9496,7 +9496,7 @@
     <row r="201">
       <c r="A201" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B201" s="2" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="C201" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D201" s="2" t="n">
@@ -9541,7 +9541,7 @@
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B202" s="2" t="inlineStr">
@@ -9551,26 +9551,26 @@
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D202" s="2" t="n">
-        <v>529</v>
+        <v>833</v>
       </c>
       <c r="E202" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F202" s="2" t="n">
-        <v>-93</v>
+        <v>211</v>
       </c>
       <c r="G202" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H202" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J202" s="3" t="inlineStr">
         <is>
@@ -9586,7 +9586,7 @@
     <row r="203">
       <c r="A203" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B203" s="2" t="inlineStr">
@@ -9600,13 +9600,13 @@
         </is>
       </c>
       <c r="D203" s="2" t="n">
-        <v>559</v>
+        <v>529</v>
       </c>
       <c r="E203" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F203" s="2" t="n">
-        <v>-63</v>
+        <v>-93</v>
       </c>
       <c r="G203" s="2" t="n">
         <v>30</v>
@@ -9631,7 +9631,7 @@
     <row r="204">
       <c r="A204" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B204" s="2" t="inlineStr">
@@ -9641,7 +9641,7 @@
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D204" s="2" t="n">
@@ -9676,7 +9676,7 @@
     <row r="205">
       <c r="A205" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B205" s="2" t="inlineStr">
@@ -9686,26 +9686,26 @@
       </c>
       <c r="C205" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D205" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E205" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F205" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G205" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H205" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J205" s="3" t="inlineStr">
         <is>
@@ -9721,7 +9721,7 @@
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B206" s="2" t="inlineStr">
@@ -9731,26 +9731,26 @@
       </c>
       <c r="C206" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D206" s="2" t="n">
-        <v>529</v>
+        <v>833</v>
       </c>
       <c r="E206" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F206" s="2" t="n">
-        <v>-93</v>
+        <v>211</v>
       </c>
       <c r="G206" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H206" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J206" s="3" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
     <row r="207">
       <c r="A207" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B207" s="2" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D207" s="2" t="n">
@@ -9811,7 +9811,7 @@
     <row r="208">
       <c r="A208" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B208" s="2" t="inlineStr">
@@ -9821,26 +9821,26 @@
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D208" s="2" t="n">
-        <v>833</v>
+        <v>529</v>
       </c>
       <c r="E208" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F208" s="2" t="n">
-        <v>211</v>
+        <v>-93</v>
       </c>
       <c r="G208" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H208" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J208" s="3" t="inlineStr">
         <is>
@@ -9856,7 +9856,7 @@
     <row r="209">
       <c r="A209" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B209" s="2" t="inlineStr">
@@ -9866,17 +9866,17 @@
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D209" s="2" t="n">
-        <v>833</v>
+        <v>753</v>
       </c>
       <c r="E209" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F209" s="2" t="n">
-        <v>211</v>
+        <v>131</v>
       </c>
       <c r="G209" s="2" t="n">
         <v>46</v>
@@ -9901,7 +9901,7 @@
     <row r="210">
       <c r="A210" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B210" s="2" t="inlineStr">
@@ -9911,26 +9911,26 @@
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D210" s="2" t="n">
-        <v>529</v>
+        <v>788</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F210" s="2" t="n">
-        <v>-93</v>
+        <v>-110</v>
       </c>
       <c r="G210" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H210" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J210" s="3" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
     <row r="211">
       <c r="A211" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B211" s="2" t="inlineStr">
@@ -9956,26 +9956,26 @@
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D211" s="2" t="n">
-        <v>646</v>
+        <v>788</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F211" s="2" t="n">
-        <v>24</v>
+        <v>-110</v>
       </c>
       <c r="G211" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H211" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>-10</v>
+        <v>7</v>
       </c>
       <c r="J211" s="3" t="inlineStr">
         <is>
@@ -9991,7 +9991,7 @@
     <row r="212">
       <c r="A212" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B212" s="2" t="inlineStr">
@@ -10001,26 +10001,26 @@
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D212" s="2" t="n">
-        <v>529</v>
+        <v>788</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F212" s="2" t="n">
-        <v>-93</v>
+        <v>-110</v>
       </c>
       <c r="G212" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H212" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J212" s="3" t="inlineStr">
         <is>
@@ -10036,7 +10036,7 @@
     <row r="213">
       <c r="A213" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B213" s="2" t="inlineStr">
@@ -10046,26 +10046,26 @@
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D213" s="2" t="n">
-        <v>529</v>
+        <v>788</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F213" s="2" t="n">
-        <v>-93</v>
+        <v>-110</v>
       </c>
       <c r="G213" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H213" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J213" s="3" t="inlineStr">
         <is>
@@ -10081,7 +10081,7 @@
     <row r="214">
       <c r="A214" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B214" s="2" t="inlineStr">
@@ -10091,26 +10091,26 @@
       </c>
       <c r="C214" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D214" s="2" t="n">
-        <v>833</v>
+        <v>788</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F214" s="2" t="n">
-        <v>211</v>
+        <v>-110</v>
       </c>
       <c r="G214" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H214" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J214" s="3" t="inlineStr">
         <is>
@@ -10126,7 +10126,7 @@
     <row r="215">
       <c r="A215" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B215" s="2" t="inlineStr">
@@ -10136,26 +10136,26 @@
       </c>
       <c r="C215" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D215" s="2" t="n">
-        <v>529</v>
+        <v>1018</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F215" s="2" t="n">
-        <v>-93</v>
+        <v>120</v>
       </c>
       <c r="G215" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H215" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J215" s="3" t="inlineStr">
         <is>
@@ -10171,7 +10171,7 @@
     <row r="216">
       <c r="A216" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B216" s="2" t="inlineStr">
@@ -10181,17 +10181,17 @@
       </c>
       <c r="C216" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D216" s="2" t="n">
-        <v>833</v>
+        <v>1018</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F216" s="2" t="n">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="G216" s="2" t="n">
         <v>46</v>
@@ -10216,7 +10216,7 @@
     <row r="217">
       <c r="A217" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B217" s="2" t="inlineStr">
@@ -10226,26 +10226,26 @@
       </c>
       <c r="C217" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D217" s="2" t="n">
-        <v>529</v>
+        <v>1018</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F217" s="2" t="n">
-        <v>-93</v>
+        <v>120</v>
       </c>
       <c r="G217" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H217" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J217" s="3" t="inlineStr">
         <is>
@@ -10261,7 +10261,7 @@
     <row r="218">
       <c r="A218" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B218" s="2" t="inlineStr">
@@ -10271,26 +10271,26 @@
       </c>
       <c r="C218" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D218" s="2" t="n">
-        <v>529</v>
+        <v>1018</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F218" s="2" t="n">
-        <v>-93</v>
+        <v>120</v>
       </c>
       <c r="G218" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H218" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J218" s="3" t="inlineStr">
         <is>
@@ -10306,7 +10306,7 @@
     <row r="219">
       <c r="A219" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B219" s="2" t="inlineStr">
@@ -10316,17 +10316,17 @@
       </c>
       <c r="C219" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D219" s="2" t="n">
-        <v>753</v>
+        <v>1075</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F219" s="2" t="n">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="G219" s="2" t="n">
         <v>46</v>
@@ -10351,7 +10351,7 @@
     <row r="220">
       <c r="A220" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B220" s="2" t="inlineStr">
@@ -10361,7 +10361,7 @@
       </c>
       <c r="C220" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D220" s="2" t="n">
@@ -10396,7 +10396,7 @@
     <row r="221">
       <c r="A221" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B221" s="2" t="inlineStr">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C221" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D221" s="2" t="n">
@@ -10441,7 +10441,7 @@
     <row r="222">
       <c r="A222" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B222" s="2" t="inlineStr">
@@ -10451,7 +10451,7 @@
       </c>
       <c r="C222" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D222" s="2" t="n">
@@ -10486,7 +10486,7 @@
     <row r="223">
       <c r="A223" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B223" s="2" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="C223" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D223" s="2" t="n">
@@ -10531,7 +10531,7 @@
     <row r="224">
       <c r="A224" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B224" s="2" t="inlineStr">
@@ -10541,7 +10541,7 @@
       </c>
       <c r="C224" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D224" s="2" t="n">
@@ -10576,7 +10576,7 @@
     <row r="225">
       <c r="A225" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B225" s="2" t="inlineStr">
@@ -10621,7 +10621,7 @@
     <row r="226">
       <c r="A226" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B226" s="2" t="inlineStr">
@@ -10631,7 +10631,7 @@
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D226" s="2" t="n">
@@ -10666,7 +10666,7 @@
     <row r="227">
       <c r="A227" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B227" s="2" t="inlineStr">
@@ -10676,7 +10676,7 @@
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D227" s="2" t="n">
@@ -10711,7 +10711,7 @@
     <row r="228">
       <c r="A228" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B228" s="2" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D228" s="2" t="n">
@@ -10756,7 +10756,7 @@
     <row r="229">
       <c r="A229" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B229" s="2" t="inlineStr">
@@ -10801,7 +10801,7 @@
     <row r="230">
       <c r="A230" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B230" s="2" t="inlineStr">
@@ -10811,7 +10811,7 @@
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D230" s="2" t="n">
@@ -10846,7 +10846,7 @@
     <row r="231">
       <c r="A231" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B231" s="2" t="inlineStr">
@@ -10891,7 +10891,7 @@
     <row r="232">
       <c r="A232" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B232" s="2" t="inlineStr">
@@ -10936,7 +10936,7 @@
     <row r="233">
       <c r="A233" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B233" s="2" t="inlineStr">
@@ -10981,7 +10981,7 @@
     <row r="234">
       <c r="A234" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B234" s="2" t="inlineStr">
@@ -10991,7 +10991,7 @@
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D234" s="2" t="n">
@@ -11026,7 +11026,7 @@
     <row r="235">
       <c r="A235" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B235" s="2" t="inlineStr">
@@ -11036,7 +11036,7 @@
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D235" s="2" t="n">
@@ -11071,7 +11071,7 @@
     <row r="236">
       <c r="A236" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B236" s="2" t="inlineStr">
@@ -11081,7 +11081,7 @@
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D236" s="2" t="n">
@@ -11116,7 +11116,7 @@
     <row r="237">
       <c r="A237" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B237" s="2" t="inlineStr">
@@ -11126,17 +11126,17 @@
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D237" s="2" t="n">
-        <v>1018</v>
+        <v>1075</v>
       </c>
       <c r="E237" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F237" s="2" t="n">
-        <v>120</v>
+        <v>177</v>
       </c>
       <c r="G237" s="2" t="n">
         <v>46</v>
@@ -11161,7 +11161,7 @@
     <row r="238">
       <c r="A238" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B238" s="2" t="inlineStr">
@@ -11171,17 +11171,17 @@
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D238" s="2" t="n">
-        <v>1020</v>
+        <v>1113</v>
       </c>
       <c r="E238" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F238" s="2" t="n">
-        <v>122</v>
+        <v>215</v>
       </c>
       <c r="G238" s="2" t="n">
         <v>46</v>
@@ -11198,636 +11198,6 @@
         </is>
       </c>
       <c r="K238" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="239">
-      <c r="A239" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B239" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C239" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E239" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F239" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G239" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H239" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I239" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J239" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K239" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="240">
-      <c r="A240" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B240" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C240" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D240" s="2" t="n">
-        <v>419</v>
-      </c>
-      <c r="E240" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F240" s="2" t="n">
-        <v>-479</v>
-      </c>
-      <c r="G240" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H240" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I240" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J240" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K240" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="241">
-      <c r="A241" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B241" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C241" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D241" s="2" t="n">
-        <v>419</v>
-      </c>
-      <c r="E241" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F241" s="2" t="n">
-        <v>-479</v>
-      </c>
-      <c r="G241" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H241" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I241" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J241" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K241" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="242">
-      <c r="A242" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B242" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C242" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-793</t>
-        </is>
-      </c>
-      <c r="D242" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="E242" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F242" s="2" t="n">
-        <v>-369</v>
-      </c>
-      <c r="G242" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H242" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I242" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J242" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K242" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="243">
-      <c r="A243" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B243" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C243" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D243" s="2" t="n">
-        <v>529</v>
-      </c>
-      <c r="E243" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F243" s="2" t="n">
-        <v>-369</v>
-      </c>
-      <c r="G243" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H243" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I243" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J243" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K243" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="244">
-      <c r="A244" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B244" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C244" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-391</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="n">
-        <v>788</v>
-      </c>
-      <c r="E244" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F244" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G244" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H244" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I244" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J244" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K244" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="245">
-      <c r="A245" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B245" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C245" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-317</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="n">
-        <v>788</v>
-      </c>
-      <c r="E245" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F245" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G245" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H245" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I245" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J245" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K245" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="246">
-      <c r="A246" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B246" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C246" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-315</t>
-        </is>
-      </c>
-      <c r="D246" s="2" t="n">
-        <v>788</v>
-      </c>
-      <c r="E246" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F246" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G246" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H246" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I246" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J246" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K246" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="247">
-      <c r="A247" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B247" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C247" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-381</t>
-        </is>
-      </c>
-      <c r="D247" s="2" t="n">
-        <v>788</v>
-      </c>
-      <c r="E247" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F247" s="2" t="n">
-        <v>-110</v>
-      </c>
-      <c r="G247" s="2" t="n">
-        <v>23</v>
-      </c>
-      <c r="H247" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I247" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J247" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K247" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="248">
-      <c r="A248" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B248" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C248" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D248" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E248" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F248" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G248" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H248" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I248" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J248" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K248" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="249">
-      <c r="A249" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B249" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C249" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D249" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E249" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F249" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G249" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H249" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I249" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J249" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K249" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="250">
-      <c r="A250" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B250" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C250" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D250" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E250" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F250" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G250" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H250" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I250" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J250" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K250" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="251">
-      <c r="A251" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B251" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C251" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D251" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E251" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F251" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G251" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H251" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I251" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J251" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K251" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="252">
-      <c r="A252" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B252" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C252" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D252" s="2" t="n">
-        <v>1113</v>
-      </c>
-      <c r="E252" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F252" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="G252" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H252" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I252" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J252" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K252" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -33,7 +33,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -58,6 +58,12 @@
         <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -77,7 +83,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -89,6 +95,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -456,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:K18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -542,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
         <v>1018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>820</v>
+        <v>898</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>198</v>
+        <v>120</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -577,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -587,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1018</v>
+        <v>753</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>820</v>
+        <v>742</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>198</v>
+        <v>11</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -608,9 +617,9 @@
       <c r="I3" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -632,7 +641,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
@@ -677,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>753</v>
+        <v>810</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>742</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -698,9 +707,9 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -722,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>753</v>
+        <v>923</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>742</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>11</v>
+        <v>181</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -743,9 +752,9 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J6" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -757,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -767,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>810</v>
+        <v>753</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>742</v>
+        <v>622</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>68</v>
+        <v>131</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -794,6 +803,501 @@
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>806</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>-947</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>809</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>-944</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-315</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>875</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>-878</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>909</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>-844</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-680</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>1223</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>-530</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>1328</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>-425</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-317</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>1328</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>-425</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>1358</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>-395</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>1519</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>-234</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>1710</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>-43</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>04-JUN-26</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>1818</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1753</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>65</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K18"/>
+  <dimension ref="A1:K117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1018</v>
+        <v>753</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>898</v>
+        <v>742</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>120</v>
+        <v>11</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -596,7 +596,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
@@ -617,7 +617,7 @@
       <c r="I3" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J3" s="4" t="inlineStr">
+      <c r="J3" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>753</v>
+        <v>810</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>742</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>11</v>
+        <v>68</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -664,7 +664,7 @@
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>810</v>
+        <v>923</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>742</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>68</v>
+        <v>181</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -707,7 +707,7 @@
       <c r="I5" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J5" s="3" t="inlineStr">
+      <c r="J5" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>742</v>
+        <v>682</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>181</v>
+        <v>71</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>46</v>
@@ -752,7 +752,7 @@
       <c r="I6" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -797,7 +797,7 @@
       <c r="I7" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="J7" s="4" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1223</v>
+        <v>1328</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-530</v>
+        <v>-425</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
@@ -1067,7 +1067,7 @@
       <c r="I13" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
+      <c r="J13" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1328</v>
+        <v>1555</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-425</v>
+        <v>-198</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1358</v>
+        <v>1653</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-395</v>
+        <v>-100</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1157,9 +1157,9 @@
       <c r="I15" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,28 +1181,28 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1519</v>
+        <v>690</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-234</v>
+        <v>-364</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>1710</v>
+        <v>813</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-43</v>
+        <v>-241</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,33 +1271,4488 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>-241</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-317</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>-241</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-315</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>-241</v>
+      </c>
+      <c r="G20" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H20" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>923</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>-131</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H21" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I21" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J21" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>08-JUN-26</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>1223</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>1054</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>169</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H22" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H23" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H24" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J24" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H25" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H26" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J26" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H27" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K27" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H28" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K28" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H29" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K29" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
           <t>EgyptAir MS-640</t>
         </is>
       </c>
-      <c r="D18" s="2" t="n">
-        <v>1818</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>1753</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>65</v>
-      </c>
-      <c r="G18" s="2" t="n">
+      <c r="D30" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G30" s="2" t="n">
         <v>46</v>
       </c>
-      <c r="H18" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I18" s="2" t="n">
+      <c r="H30" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I30" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H31" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J31" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K31" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>-163</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H32" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>06-JUL-26</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>-163</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H33" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H34" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G35" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H35" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G36" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H36" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G37" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H37" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J37" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G38" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H38" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E39" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>-163</v>
+      </c>
+      <c r="G39" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H39" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F40" s="2" t="n">
+        <v>-163</v>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H40" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J40" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>07-JUL-26</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F41" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H41" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H42" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J42" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H43" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H44" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J44" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G45" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H45" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J45" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G46" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H46" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>-163</v>
+      </c>
+      <c r="G47" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H47" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>08-JUL-26</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="n">
+        <v>813</v>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>-163</v>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H48" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H49" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H50" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H51" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H52" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K52" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>-223</v>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H53" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J53" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K53" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G54" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H54" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J54" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K54" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G55" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H55" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J55" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K55" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E56" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G56" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H56" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I56" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K56" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>09-JUL-26</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="n">
+        <v>923</v>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>-53</v>
+      </c>
+      <c r="G57" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H57" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K57" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>-286</v>
+      </c>
+      <c r="G58" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H58" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K58" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E59" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>-286</v>
+      </c>
+      <c r="G59" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H59" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I59" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J59" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K59" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G60" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H60" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J60" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K60" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E61" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G61" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H61" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I61" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J61" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K61" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G62" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H62" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K62" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G63" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H63" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J63" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K63" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>13-JUL-26</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G64" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H64" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J64" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K64" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>-286</v>
+      </c>
+      <c r="G65" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H65" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K65" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>-286</v>
+      </c>
+      <c r="G66" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H66" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K66" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E67" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G67" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H67" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I67" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K67" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G68" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H68" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K68" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E69" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G69" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H69" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I69" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K69" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>14-JUL-26</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G70" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H70" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K70" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G71" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H71" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K71" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="n">
+        <v>469</v>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F72" s="2" t="n">
+        <v>-507</v>
+      </c>
+      <c r="G72" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H72" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K72" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="n">
+        <v>499</v>
+      </c>
+      <c r="E73" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F73" s="2" t="n">
+        <v>-477</v>
+      </c>
+      <c r="G73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H73" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I73" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K73" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E74" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F74" s="2" t="n">
+        <v>-286</v>
+      </c>
+      <c r="G74" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H74" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I74" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K74" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="n">
+        <v>690</v>
+      </c>
+      <c r="E75" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F75" s="2" t="n">
+        <v>-286</v>
+      </c>
+      <c r="G75" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H75" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I75" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K75" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E76" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F76" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G76" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H76" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I76" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K76" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E77" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F77" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G77" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H77" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I77" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K77" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="n">
+        <v>698</v>
+      </c>
+      <c r="E78" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F78" s="2" t="n">
+        <v>-278</v>
+      </c>
+      <c r="G78" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H78" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I78" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J78" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K78" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="n">
+        <v>755</v>
+      </c>
+      <c r="E79" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F79" s="2" t="n">
+        <v>-221</v>
+      </c>
+      <c r="G79" s="2" t="n">
+        <v>23</v>
+      </c>
+      <c r="H79" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I79" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J79" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K79" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
+        <is>
+          <t>15-JUL-26</t>
+        </is>
+      </c>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E80" s="2" t="n">
+        <v>976</v>
+      </c>
+      <c r="F80" s="2" t="n">
+        <v>-143</v>
+      </c>
+      <c r="G80" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H80" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I80" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J80" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K80" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
+        <is>
+          <t>16-JUL-26</t>
+        </is>
+      </c>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E81" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F81" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G81" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H81" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I81" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J81" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K81" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E82" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F82" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="G82" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H82" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I82" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J82" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K82" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E83" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F83" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="G83" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H83" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I83" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J83" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K83" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
+        <is>
+          <t>20-JUL-26</t>
+        </is>
+      </c>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E84" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F84" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G84" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H84" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I84" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J84" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K84" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
+        <is>
+          <t>21-JUL-26</t>
+        </is>
+      </c>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E85" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F85" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G85" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H85" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I85" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J85" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K85" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
+        <is>
+          <t>23-JUL-26</t>
+        </is>
+      </c>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E86" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F86" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G86" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H86" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I86" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J86" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K86" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E87" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F87" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G87" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H87" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I87" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J87" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K87" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E88" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F88" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G88" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H88" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I88" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K88" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E89" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F89" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G89" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H89" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I89" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K89" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E90" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F90" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G90" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H90" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I90" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J90" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K90" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E91" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F91" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G91" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H91" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I91" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J91" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K91" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E92" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F92" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G92" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H92" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I92" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J92" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K92" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E93" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F93" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G93" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H93" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I93" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J93" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K93" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E94" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F94" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G94" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H94" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I94" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J94" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K94" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E95" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F95" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="G95" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H95" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I95" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J95" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K95" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E96" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F96" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G96" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H96" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I96" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J96" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K96" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E97" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F97" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G97" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H97" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I97" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K97" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E98" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F98" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G98" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H98" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I98" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K98" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E99" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F99" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G99" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H99" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I99" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J99" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K99" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E100" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F100" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G100" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H100" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I100" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J100" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K100" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E101" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F101" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G101" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H101" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I101" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J101" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K101" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E102" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F102" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G102" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H102" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I102" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J102" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K102" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E103" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F103" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G103" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H103" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I103" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K103" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E104" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F104" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G104" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H104" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I104" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J104" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K104" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E105" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F105" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G105" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H105" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I105" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K105" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E106" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F106" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G106" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H106" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I106" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J106" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K106" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E107" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F107" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G107" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H107" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I107" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J107" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K107" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E108" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F108" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G108" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H108" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I108" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J108" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K108" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E109" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F109" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G109" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H109" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I109" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J109" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K109" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E110" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F110" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G110" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H110" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I110" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J110" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K110" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E111" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F111" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G111" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H111" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I111" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J111" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K111" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E112" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F112" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G112" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H112" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I112" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J112" s="3" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K112" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E113" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F113" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G113" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H113" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I113" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J113" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K113" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E114" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F114" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G114" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H114" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I114" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J114" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K114" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E115" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F115" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G115" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H115" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I115" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J115" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K115" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E116" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F116" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G116" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H116" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I116" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J116" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K116" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E117" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F117" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="G117" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H117" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I117" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J117" s="4" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K117" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -48,14 +48,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00D4EDDA"/>
+        <bgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00D4EDDA"/>
-        <bgColor rgb="00D4EDDA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
     <fill>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K117"/>
+  <dimension ref="A1:K161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>753</v>
+        <v>1018</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>742</v>
+        <v>976</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -574,7 +574,7 @@
       </c>
       <c r="J2" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -596,17 +596,17 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>753</v>
+        <v>1018</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>742</v>
+        <v>976</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -619,7 +619,7 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K3" s="2" t="inlineStr">
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,28 +641,28 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>810</v>
+        <v>1099</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>742</v>
+        <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>68</v>
+        <v>123</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -686,17 +686,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>923</v>
+        <v>810</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>742</v>
+        <v>820</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>181</v>
+        <v>-10</v>
       </c>
       <c r="G5" s="2" t="n">
         <v>46</v>
@@ -709,7 +709,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,28 +731,28 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>753</v>
+        <v>819</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>682</v>
+        <v>820</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>71</v>
+        <v>-1</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,28 +776,28 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>753</v>
+        <v>829</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>622</v>
+        <v>820</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>131</v>
+        <v>9</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J7" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>806</v>
+        <v>810</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>1753</v>
+        <v>742</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>-947</v>
+        <v>68</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J8" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,30 +866,30 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>809</v>
+        <v>819</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>1753</v>
+        <v>742</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-944</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J9" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,30 +911,30 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>875</v>
+        <v>899</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-878</v>
+        <v>79</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J10" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -960,26 +960,26 @@
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>909</v>
+        <v>829</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>1753</v>
+        <v>742</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-844</v>
+        <v>87</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1328</v>
+        <v>923</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-425</v>
+        <v>103</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1328</v>
+        <v>923</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>1753</v>
+        <v>820</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-425</v>
+        <v>103</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1555</v>
+        <v>923</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>1753</v>
+        <v>742</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-198</v>
+        <v>181</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J14" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,17 +1136,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1653</v>
+        <v>923</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>1753</v>
+        <v>742</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-100</v>
+        <v>181</v>
       </c>
       <c r="G15" s="2" t="n">
         <v>46</v>
@@ -1159,7 +1159,7 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>690</v>
+        <v>1018</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1054</v>
+        <v>820</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-364</v>
+        <v>198</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,28 +1226,28 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>813</v>
+        <v>753</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1054</v>
+        <v>682</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-241</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J17" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>813</v>
+        <v>1113</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-241</v>
+        <v>-640</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J18" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>813</v>
+        <v>1170</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-241</v>
+        <v>-583</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J19" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,17 +1361,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>813</v>
+        <v>1328</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-241</v>
+        <v>-425</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>23</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,28 +1406,28 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>923</v>
+        <v>1328</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-131</v>
+        <v>-425</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J21" s="3" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1223</v>
+        <v>1328</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1054</v>
+        <v>1753</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>169</v>
+        <v>-425</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,30 +1496,30 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>469</v>
+        <v>1491</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-507</v>
+        <v>-262</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>469</v>
+        <v>999</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-507</v>
+        <v>-754</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J24" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>499</v>
+        <v>1093</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-477</v>
+        <v>-660</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,26 +1635,26 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>499</v>
+        <v>1099</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-477</v>
+        <v>-654</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>698</v>
+        <v>1175</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-278</v>
+        <v>-578</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J27" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,17 +1721,17 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>753</v>
+        <v>1223</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-223</v>
+        <v>-530</v>
       </c>
       <c r="G28" s="2" t="n">
         <v>46</v>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>753</v>
+        <v>1328</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-223</v>
+        <v>-425</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,17 +1811,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>753</v>
+        <v>1358</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-223</v>
+        <v>-395</v>
       </c>
       <c r="G30" s="2" t="n">
         <v>46</v>
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>755</v>
+        <v>1519</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-221</v>
+        <v>-234</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>813</v>
+        <v>1555</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-163</v>
+        <v>-198</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,30 +1946,30 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>813</v>
+        <v>1572</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-163</v>
+        <v>-181</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>499</v>
+        <v>1818</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-477</v>
+        <v>65</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,17 +2036,17 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-278</v>
+        <v>-364</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>23</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,17 +2081,17 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>698</v>
+        <v>813</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-278</v>
+        <v>-241</v>
       </c>
       <c r="G36" s="2" t="n">
         <v>23</v>
@@ -2102,7 +2102,7 @@
       <c r="I36" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J36" s="4" t="inlineStr">
+      <c r="J36" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>753</v>
+        <v>813</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-223</v>
+        <v>-241</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J37" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>755</v>
+        <v>813</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-221</v>
+        <v>-241</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>23</v>
@@ -2192,7 +2192,7 @@
       <c r="I38" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J38" s="4" t="inlineStr">
+      <c r="J38" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
         <v>813</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-163</v>
+        <v>-241</v>
       </c>
       <c r="G39" s="2" t="n">
         <v>23</v>
@@ -2237,7 +2237,7 @@
       <c r="I39" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J39" s="4" t="inlineStr">
+      <c r="J39" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,30 +2261,30 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>813</v>
+        <v>923</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-163</v>
+        <v>-131</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,17 +2306,17 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>833</v>
+        <v>1223</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>976</v>
+        <v>1054</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-143</v>
+        <v>169</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
@@ -2372,7 +2372,7 @@
       <c r="I42" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="4" t="inlineStr">
+      <c r="J42" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J43" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J43" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2445,26 +2445,26 @@
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2490,26 +2490,26 @@
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2552,7 +2552,7 @@
       <c r="I46" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J46" s="4" t="inlineStr">
+      <c r="J46" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2597,7 +2597,7 @@
       <c r="I47" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J47" s="4" t="inlineStr">
+      <c r="J47" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2642,7 +2642,7 @@
       <c r="I48" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J48" s="4" t="inlineStr">
+      <c r="J48" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2670,24 +2670,24 @@
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>469</v>
+        <v>646</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-507</v>
+        <v>-330</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J49" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J49" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2715,24 +2715,24 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>469</v>
+        <v>646</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-507</v>
+        <v>-330</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J50" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,30 +2756,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>499</v>
+        <v>689</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-477</v>
+        <v>-287</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J51" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J51" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>499</v>
+        <v>698</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-477</v>
+        <v>-278</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2850,26 +2850,26 @@
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-223</v>
+        <v>-278</v>
       </c>
       <c r="G53" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H53" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J53" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J53" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K53" s="2" t="inlineStr">
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-221</v>
+        <v>-223</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J54" s="4" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,30 +2936,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>833</v>
+        <v>755</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-143</v>
+        <v>-221</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -3002,7 +3002,7 @@
       <c r="I56" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J56" s="3" t="inlineStr">
+      <c r="J56" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,17 +3026,17 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>923</v>
+        <v>1056</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-53</v>
+        <v>80</v>
       </c>
       <c r="G57" s="2" t="n">
         <v>46</v>
@@ -3049,7 +3049,7 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,28 +3071,28 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>690</v>
+        <v>1056</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-286</v>
+        <v>80</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J58" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J58" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>690</v>
+        <v>439</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-286</v>
+        <v>-537</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,30 +3161,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>698</v>
+        <v>469</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-278</v>
+        <v>-507</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,30 +3206,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>698</v>
+        <v>499</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-278</v>
+        <v>-477</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3272,7 +3272,7 @@
       <c r="I62" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
+      <c r="J62" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>23</v>
@@ -3317,7 +3317,7 @@
       <c r="I63" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J63" s="4" t="inlineStr">
+      <c r="J63" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>690</v>
+        <v>698</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-286</v>
+        <v>-278</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>23</v>
@@ -3407,7 +3407,7 @@
       <c r="I65" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J65" s="4" t="inlineStr">
+      <c r="J65" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>690</v>
+        <v>755</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-286</v>
+        <v>-221</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>23</v>
@@ -3452,7 +3452,7 @@
       <c r="I66" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J66" s="4" t="inlineStr">
+      <c r="J66" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,17 +3476,17 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>698</v>
+        <v>813</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-278</v>
+        <v>-163</v>
       </c>
       <c r="G67" s="2" t="n">
         <v>23</v>
@@ -3497,7 +3497,7 @@
       <c r="I67" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J67" s="4" t="inlineStr">
+      <c r="J67" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,28 +3521,28 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>698</v>
+        <v>1056</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-278</v>
+        <v>80</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>755</v>
+        <v>469</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-221</v>
+        <v>-507</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3611,28 +3611,28 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>833</v>
+        <v>469</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-143</v>
+        <v>-507</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J70" s="3" t="inlineStr">
+        <v>15</v>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,17 +3656,17 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-507</v>
+        <v>-477</v>
       </c>
       <c r="G71" s="2" t="n">
         <v>15</v>
@@ -3677,7 +3677,7 @@
       <c r="I71" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J71" s="3" t="inlineStr">
+      <c r="J71" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-507</v>
+        <v>-477</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>15</v>
@@ -3722,7 +3722,7 @@
       <c r="I72" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J72" s="3" t="inlineStr">
+      <c r="J72" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>499</v>
+        <v>753</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-477</v>
+        <v>-223</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,17 +3791,17 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>690</v>
+        <v>755</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-286</v>
+        <v>-221</v>
       </c>
       <c r="G74" s="2" t="n">
         <v>23</v>
@@ -3812,7 +3812,7 @@
       <c r="I74" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J74" s="4" t="inlineStr">
+      <c r="J74" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,30 +3836,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>690</v>
+        <v>833</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-286</v>
+        <v>-143</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J75" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,30 +3881,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-278</v>
+        <v>-143</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>698</v>
+        <v>923</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-278</v>
+        <v>-53</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,17 +3971,17 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G78" s="2" t="n">
         <v>23</v>
@@ -3992,7 +3992,7 @@
       <c r="I78" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J78" s="4" t="inlineStr">
+      <c r="J78" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,17 +4016,17 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G79" s="2" t="n">
         <v>23</v>
@@ -4037,7 +4037,7 @@
       <c r="I79" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J79" s="4" t="inlineStr">
+      <c r="J79" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,30 +4061,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,28 +4106,28 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>211</v>
+        <v>-278</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J81" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J81" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,28 +4151,28 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>800</v>
+        <v>755</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>178</v>
+        <v>-221</v>
       </c>
       <c r="G82" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H82" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J82" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J82" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4196,17 +4196,17 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>800</v>
+        <v>833</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>178</v>
+        <v>-143</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>46</v>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="J83" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4241,17 +4241,17 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>833</v>
+        <v>933</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>211</v>
+        <v>-43</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>46</v>
@@ -4264,7 +4264,7 @@
       </c>
       <c r="J84" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,30 +4286,30 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>833</v>
+        <v>469</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>211</v>
+        <v>-507</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J85" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,30 +4331,30 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>833</v>
+        <v>469</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>211</v>
+        <v>-507</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K86" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,30 +4376,30 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>833</v>
+        <v>499</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>211</v>
+        <v>-477</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J87" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,28 +4421,28 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>833</v>
+        <v>690</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>211</v>
+        <v>-286</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J88" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,28 +4466,28 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>833</v>
+        <v>690</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>211</v>
+        <v>-286</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J89" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,28 +4511,28 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>211</v>
+        <v>-278</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J90" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J90" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,28 +4556,28 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>211</v>
+        <v>-278</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J91" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J91" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,28 +4601,28 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>833</v>
+        <v>755</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>211</v>
+        <v>-221</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J92" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J92" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4653,10 +4653,10 @@
         <v>833</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>211</v>
+        <v>-143</v>
       </c>
       <c r="G93" s="2" t="n">
         <v>46</v>
@@ -4669,7 +4669,7 @@
       </c>
       <c r="J93" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,30 +4691,30 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>833</v>
+        <v>469</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>211</v>
+        <v>-507</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J94" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,30 +4736,30 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>753</v>
+        <v>469</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>131</v>
+        <v>-507</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,30 +4781,30 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>1018</v>
+        <v>499</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>120</v>
+        <v>-477</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J96" s="4" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,28 +4826,28 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>1018</v>
+        <v>690</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>120</v>
+        <v>-286</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,28 +4871,28 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>1018</v>
+        <v>690</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>120</v>
+        <v>-286</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,28 +4916,28 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>1018</v>
+        <v>698</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>120</v>
+        <v>-278</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J99" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J99" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,28 +4961,28 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>1075</v>
+        <v>698</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>177</v>
+        <v>-278</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J100" s="4" t="inlineStr">
+        <v>7</v>
+      </c>
+      <c r="J100" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,30 +5006,30 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>429</v>
+        <v>698</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-469</v>
+        <v>-278</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,30 +5051,30 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>439</v>
+        <v>755</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-459</v>
+        <v>-221</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K102" s="2" t="inlineStr">
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,28 +5096,28 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>439</v>
+        <v>833</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>898</v>
+        <v>976</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-459</v>
+        <v>-143</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J103" s="3" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J103" s="4" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5145,13 +5145,13 @@
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>1018</v>
+        <v>833</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>46</v>
@@ -5162,7 +5162,7 @@
       <c r="I104" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J104" s="4" t="inlineStr">
+      <c r="J104" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,17 +5186,17 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>1018</v>
+        <v>833</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>46</v>
@@ -5207,7 +5207,7 @@
       <c r="I105" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J105" s="4" t="inlineStr">
+      <c r="J105" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>1018</v>
+        <v>833</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>46</v>
@@ -5252,7 +5252,7 @@
       <c r="I106" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J106" s="4" t="inlineStr">
+      <c r="J106" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,17 +5276,17 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>1018</v>
+        <v>718</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="G107" s="2" t="n">
         <v>46</v>
@@ -5297,7 +5297,7 @@
       <c r="I107" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J107" s="4" t="inlineStr">
+      <c r="J107" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,28 +5321,28 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>1075</v>
+        <v>616</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>177</v>
+        <v>-6</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J108" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J108" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,30 +5366,30 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>429</v>
+        <v>616</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-469</v>
+        <v>-6</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,30 +5411,30 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>429</v>
+        <v>649</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>-469</v>
+        <v>27</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,30 +5456,30 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>439</v>
+        <v>649</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-459</v>
+        <v>27</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K111" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,30 +5501,30 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>439</v>
+        <v>833</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>-459</v>
+        <v>211</v>
       </c>
       <c r="G112" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H112" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J112" s="3" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K112" s="2" t="inlineStr">
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,28 +5546,28 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>1018</v>
+        <v>616</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>120</v>
+        <v>-6</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J113" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J113" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,28 +5591,28 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>1018</v>
+        <v>616</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>120</v>
+        <v>-6</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J114" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J114" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,28 +5636,28 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>1018</v>
+        <v>619</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>120</v>
+        <v>-3</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J115" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J115" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,28 +5681,28 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>1075</v>
+        <v>649</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>177</v>
+        <v>27</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J116" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J116" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,17 +5726,17 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>1113</v>
+        <v>718</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>215</v>
+        <v>96</v>
       </c>
       <c r="G117" s="2" t="n">
         <v>46</v>
@@ -5747,12 +5747,1992 @@
       <c r="I117" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J117" s="4" t="inlineStr">
+      <c r="J117" s="3" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
       <c r="K117" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
+        <is>
+          <t>27-JUL-26</t>
+        </is>
+      </c>
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="E118" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F118" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G118" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H118" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I118" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J118" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K118" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E119" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="G119" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H119" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I119" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J119" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K119" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="n">
+        <v>800</v>
+      </c>
+      <c r="E120" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F120" s="2" t="n">
+        <v>178</v>
+      </c>
+      <c r="G120" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H120" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I120" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J120" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K120" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
+        <is>
+          <t>28-JUL-26</t>
+        </is>
+      </c>
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E121" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G121" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H121" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I121" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J121" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K121" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
+        <is>
+          <t>29-JUL-26</t>
+        </is>
+      </c>
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E122" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F122" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G122" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H122" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I122" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J122" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K122" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E123" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F123" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G123" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H123" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I123" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J123" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K123" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
+        <is>
+          <t>30-JUL-26</t>
+        </is>
+      </c>
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E124" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F124" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G124" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H124" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I124" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J124" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K124" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="E125" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F125" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G125" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H125" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I125" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J125" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K125" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-319</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="E126" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F126" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G126" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H126" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I126" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J126" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K126" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-391</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="n">
+        <v>718</v>
+      </c>
+      <c r="E127" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F127" s="2" t="n">
+        <v>96</v>
+      </c>
+      <c r="G127" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H127" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I127" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J127" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K127" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E128" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F128" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G128" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H128" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I128" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J128" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K128" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
+        <is>
+          <t>04-AUG-26</t>
+        </is>
+      </c>
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E129" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F129" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G129" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H129" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I129" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J129" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K129" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
+        <is>
+          <t>05-AUG-26</t>
+        </is>
+      </c>
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E130" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F130" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H130" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I130" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J130" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K130" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E131" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F131" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H131" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I131" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J131" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K131" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E132" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F132" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H132" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I132" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J132" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K132" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E133" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F133" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G133" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H133" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I133" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J133" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K133" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E134" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F134" s="2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="G134" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H134" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I134" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J134" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K134" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
+        <is>
+          <t>10-AUG-26</t>
+        </is>
+      </c>
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E135" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F135" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G135" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H135" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I135" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J135" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K135" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
+        <is>
+          <t>11-AUG-26</t>
+        </is>
+      </c>
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="n">
+        <v>833</v>
+      </c>
+      <c r="E136" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F136" s="2" t="n">
+        <v>211</v>
+      </c>
+      <c r="G136" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H136" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I136" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J136" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K136" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E137" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F137" s="2" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H137" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I137" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K137" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
+        <is>
+          <t>13-AUG-26</t>
+        </is>
+      </c>
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="n">
+        <v>753</v>
+      </c>
+      <c r="E138" s="2" t="n">
+        <v>622</v>
+      </c>
+      <c r="F138" s="2" t="n">
+        <v>131</v>
+      </c>
+      <c r="G138" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H138" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I138" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J138" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K138" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E139" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F139" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G139" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H139" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I139" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J139" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K139" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E140" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F140" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G140" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H140" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I140" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J140" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K140" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E141" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F141" s="2" t="n">
+        <v>-282</v>
+      </c>
+      <c r="G141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H141" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I141" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J141" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K141" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E142" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F142" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G142" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H142" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I142" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J142" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K142" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E143" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F143" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G143" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H143" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I143" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J143" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K143" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E144" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F144" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G144" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H144" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I144" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J144" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K144" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E145" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F145" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G145" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H145" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I145" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J145" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K145" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
+        <is>
+          <t>22-SEP-26</t>
+        </is>
+      </c>
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E146" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F146" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G146" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H146" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I146" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J146" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K146" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E147" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F147" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G147" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H147" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I147" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J147" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K147" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E148" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F148" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G148" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H148" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I148" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J148" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K148" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E149" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F149" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G149" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H149" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I149" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J149" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K149" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E150" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F150" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G150" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H150" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I150" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J150" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K150" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E151" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F151" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G151" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H151" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I151" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J151" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K151" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E152" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F152" s="2" t="n">
+        <v>-282</v>
+      </c>
+      <c r="G152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H152" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I152" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J152" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K152" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="n">
+        <v>616</v>
+      </c>
+      <c r="E153" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F153" s="2" t="n">
+        <v>-282</v>
+      </c>
+      <c r="G153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="H153" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I153" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J153" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K153" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E154" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F154" s="2" t="n">
+        <v>-279</v>
+      </c>
+      <c r="G154" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H154" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I154" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J154" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K154" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="n">
+        <v>619</v>
+      </c>
+      <c r="E155" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F155" s="2" t="n">
+        <v>-279</v>
+      </c>
+      <c r="G155" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H155" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I155" s="2" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J155" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="K155" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E156" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F156" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G156" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H156" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I156" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J156" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K156" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E157" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F157" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G157" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H157" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I157" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J157" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K157" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E158" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F158" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G158" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H158" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I158" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J158" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K158" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-381</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="n">
+        <v>1056</v>
+      </c>
+      <c r="E159" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F159" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="G159" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H159" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I159" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J159" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K159" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E160" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F160" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G160" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H160" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I160" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J160" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K160" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B161" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C161" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D161" s="2" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E161" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F161" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="G161" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H161" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I161" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J161" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K161" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K161"/>
+  <dimension ref="A1:K172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>26-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1099</v>
+        <v>810</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>976</v>
+        <v>820</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>123</v>
+        <v>-10</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>810</v>
+        <v>819</v>
       </c>
       <c r="E5" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F5" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>40</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I5" s="2" t="n">
         <v>-10</v>
       </c>
-      <c r="G5" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -731,17 +731,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>819</v>
+        <v>829</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="G6" s="2" t="n">
         <v>40</v>
@@ -776,26 +776,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>829</v>
+        <v>923</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>820</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>9</v>
+        <v>103</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>810</v>
+        <v>923</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>742</v>
+        <v>820</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>68</v>
+        <v>103</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>819</v>
+        <v>1018</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>742</v>
+        <v>820</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>899</v>
+        <v>753</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>820</v>
+        <v>682</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>829</v>
+        <v>1113</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>87</v>
+        <v>-640</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,17 +1001,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>923</v>
+        <v>1170</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>820</v>
+        <v>1753</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>103</v>
+        <v>-583</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>46</v>
@@ -1022,9 +1022,9 @@
       <c r="I12" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J12" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>923</v>
+        <v>1328</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>820</v>
+        <v>1753</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>103</v>
+        <v>-425</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,30 +1091,30 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>923</v>
+        <v>1328</v>
       </c>
       <c r="E14" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>181</v>
+        <v>-425</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J14" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>923</v>
+        <v>1328</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>181</v>
+        <v>-425</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J15" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,26 +1181,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1018</v>
+        <v>1491</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>820</v>
+        <v>1753</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>198</v>
+        <v>-262</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,30 +1226,30 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>753</v>
+        <v>806</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>682</v>
+        <v>1753</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>71</v>
+        <v>-947</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H17" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J17" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J17" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,26 +1271,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>1113</v>
+        <v>809</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-640</v>
+        <v>-944</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,26 +1316,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1170</v>
+        <v>875</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-583</v>
+        <v>-878</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
+        <v>30</v>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1328</v>
+        <v>909</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-425</v>
+        <v>-844</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J20" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>15</v>
+      </c>
+      <c r="J20" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1328</v>
+        <v>1223</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-425</v>
+        <v>-530</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J21" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J21" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1491</v>
+        <v>1328</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-262</v>
+        <v>-425</v>
       </c>
       <c r="G23" s="2" t="n">
         <v>23</v>
@@ -1517,9 +1517,9 @@
       <c r="I23" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -1541,26 +1541,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>999</v>
+        <v>1358</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-754</v>
+        <v>-395</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1093</v>
+        <v>1519</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-660</v>
+        <v>-234</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-10</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1631,26 +1631,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1099</v>
+        <v>1555</v>
       </c>
       <c r="E26" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-654</v>
+        <v>-198</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1175</v>
+        <v>1818</v>
       </c>
       <c r="E27" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-578</v>
+        <v>65</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>46</v>
@@ -1697,9 +1697,9 @@
       <c r="I27" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,26 +1721,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>1223</v>
+        <v>729</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-530</v>
+        <v>-325</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,17 +1766,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>1328</v>
+        <v>813</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-425</v>
+        <v>-241</v>
       </c>
       <c r="G29" s="2" t="n">
         <v>23</v>
@@ -1787,9 +1787,9 @@
       <c r="I29" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J29" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>1358</v>
+        <v>813</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-395</v>
+        <v>-241</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J30" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,30 +1856,30 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>1519</v>
+        <v>813</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-234</v>
+        <v>-241</v>
       </c>
       <c r="G31" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K31" s="2" t="inlineStr">
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,17 +1901,17 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>1555</v>
+        <v>923</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-198</v>
+        <v>-131</v>
       </c>
       <c r="G32" s="2" t="n">
         <v>46</v>
@@ -1922,9 +1922,9 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J32" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1572</v>
+        <v>933</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-181</v>
+        <v>-121</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J33" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,17 +1991,17 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1818</v>
+        <v>1056</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>65</v>
+        <v>2</v>
       </c>
       <c r="G34" s="2" t="n">
         <v>46</v>
@@ -2012,9 +2012,9 @@
       <c r="I34" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J34" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>690</v>
+        <v>1223</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-364</v>
+        <v>169</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>813</v>
+        <v>469</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-241</v>
+        <v>-507</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J36" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>813</v>
+        <v>469</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-241</v>
+        <v>-507</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J37" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J37" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>813</v>
+        <v>499</v>
       </c>
       <c r="E38" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-241</v>
+        <v>-477</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J38" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J38" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>813</v>
+        <v>499</v>
       </c>
       <c r="E39" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-241</v>
+        <v>-477</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2265,26 +2265,26 @@
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>923</v>
+        <v>698</v>
       </c>
       <c r="E40" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-131</v>
+        <v>-278</v>
       </c>
       <c r="G40" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H40" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J40" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K40" s="2" t="inlineStr">
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2310,13 +2310,13 @@
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>1223</v>
+        <v>753</v>
       </c>
       <c r="E41" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>169</v>
+        <v>-223</v>
       </c>
       <c r="G41" s="2" t="n">
         <v>46</v>
@@ -2327,9 +2327,9 @@
       <c r="I41" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J41" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J41" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J42" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J42" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-223</v>
+        <v>-221</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J44" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>753</v>
+        <v>813</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J45" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J45" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2531,17 +2531,17 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>755</v>
+        <v>813</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-221</v>
+        <v>-163</v>
       </c>
       <c r="G46" s="2" t="n">
         <v>23</v>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>813</v>
+        <v>469</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-163</v>
+        <v>-507</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J47" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J47" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>813</v>
+        <v>469</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-163</v>
+        <v>-507</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J48" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J48" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2666,26 +2666,26 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>646</v>
+        <v>499</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-330</v>
+        <v>-477</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>646</v>
+        <v>698</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-330</v>
+        <v>-278</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2756,30 +2756,30 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>689</v>
+        <v>698</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-287</v>
+        <v>-278</v>
       </c>
       <c r="G51" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H51" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J51" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J51" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K51" s="2" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J52" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J52" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-278</v>
+        <v>-221</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>23</v>
@@ -2891,30 +2891,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>753</v>
+        <v>813</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-223</v>
+        <v>-163</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J54" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J54" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>755</v>
+        <v>813</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-221</v>
+        <v>-163</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>23</v>
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1056</v>
+        <v>439</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>80</v>
+        <v>-537</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J57" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3071,30 +3071,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>1056</v>
+        <v>469</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>80</v>
+        <v>-507</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J58" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>439</v>
+        <v>499</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-537</v>
+        <v>-477</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>15</v>
@@ -3161,30 +3161,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>469</v>
+        <v>698</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-507</v>
+        <v>-278</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J60" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J60" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3206,30 +3206,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>499</v>
+        <v>698</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-477</v>
+        <v>-278</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J61" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J61" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
@@ -3341,17 +3341,17 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-278</v>
+        <v>-221</v>
       </c>
       <c r="G64" s="2" t="n">
         <v>23</v>
@@ -3386,17 +3386,17 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>698</v>
+        <v>813</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-278</v>
+        <v>-163</v>
       </c>
       <c r="G65" s="2" t="n">
         <v>23</v>
@@ -3431,17 +3431,17 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>755</v>
+        <v>813</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-221</v>
+        <v>-163</v>
       </c>
       <c r="G66" s="2" t="n">
         <v>23</v>
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3476,30 +3476,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>813</v>
+        <v>469</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-163</v>
+        <v>-507</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J67" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3521,30 +3521,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>1056</v>
+        <v>469</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>80</v>
+        <v>-507</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J68" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-507</v>
+        <v>-477</v>
       </c>
       <c r="G69" s="2" t="n">
         <v>15</v>
@@ -3611,17 +3611,17 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>469</v>
+        <v>499</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-507</v>
+        <v>-477</v>
       </c>
       <c r="G70" s="2" t="n">
         <v>15</v>
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>499</v>
+        <v>753</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-477</v>
+        <v>-223</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J71" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3701,30 +3701,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>499</v>
+        <v>755</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-477</v>
+        <v>-221</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J72" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J72" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3746,17 +3746,17 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-223</v>
+        <v>-143</v>
       </c>
       <c r="G73" s="2" t="n">
         <v>46</v>
@@ -3767,9 +3767,9 @@
       <c r="I73" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>755</v>
+        <v>833</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-221</v>
+        <v>-143</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>833</v>
+        <v>923</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-143</v>
+        <v>-53</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>46</v>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,26 +3881,26 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>833</v>
+        <v>646</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-143</v>
+        <v>-330</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J76" s="4" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,26 +3926,26 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>923</v>
+        <v>646</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-53</v>
+        <v>-330</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J77" s="4" t="inlineStr">
         <is>
@@ -3971,30 +3971,30 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-286</v>
+        <v>-287</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J78" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J78" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-278</v>
+        <v>-287</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J79" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J79" s="5" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4061,17 +4061,17 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G80" s="2" t="n">
         <v>23</v>
@@ -4106,17 +4106,17 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G81" s="2" t="n">
         <v>23</v>
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>23</v>
@@ -4196,30 +4196,30 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G83" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H83" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J83" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J83" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K83" s="2" t="inlineStr">
@@ -4241,30 +4241,30 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>933</v>
+        <v>698</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-43</v>
+        <v>-278</v>
       </c>
       <c r="G84" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H84" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J84" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J84" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4286,30 +4286,30 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>469</v>
+        <v>755</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-507</v>
+        <v>-221</v>
       </c>
       <c r="G85" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H85" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J85" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J85" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4331,26 +4331,26 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>469</v>
+        <v>833</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-507</v>
+        <v>-143</v>
       </c>
       <c r="G86" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H86" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J86" s="4" t="inlineStr">
         <is>
@@ -4376,17 +4376,17 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="E87" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-477</v>
+        <v>-507</v>
       </c>
       <c r="G87" s="2" t="n">
         <v>15</v>
@@ -4421,30 +4421,30 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>690</v>
+        <v>469</v>
       </c>
       <c r="E88" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-286</v>
+        <v>-507</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J88" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J88" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4466,30 +4466,30 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>690</v>
+        <v>499</v>
       </c>
       <c r="E89" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-286</v>
+        <v>-477</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J89" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J89" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E90" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G90" s="2" t="n">
         <v>23</v>
@@ -4556,17 +4556,17 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E91" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G91" s="2" t="n">
         <v>23</v>
@@ -4601,17 +4601,17 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E92" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G92" s="2" t="n">
         <v>23</v>
@@ -4646,30 +4646,30 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E93" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J93" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J93" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K93" s="2" t="inlineStr">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,30 +4691,30 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>469</v>
+        <v>755</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-507</v>
+        <v>-221</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J94" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J94" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K94" s="2" t="inlineStr">
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,26 +4736,26 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>469</v>
+        <v>833</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-507</v>
+        <v>-143</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J95" s="4" t="inlineStr">
         <is>
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-477</v>
+        <v>-507</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>15</v>
@@ -4826,30 +4826,30 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>690</v>
+        <v>469</v>
       </c>
       <c r="E97" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-286</v>
+        <v>-507</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J97" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J97" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4871,30 +4871,30 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>690</v>
+        <v>499</v>
       </c>
       <c r="E98" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-286</v>
+        <v>-477</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J98" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J98" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4916,17 +4916,17 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E99" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G99" s="2" t="n">
         <v>23</v>
@@ -4961,17 +4961,17 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E100" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G100" s="2" t="n">
         <v>23</v>
@@ -5006,7 +5006,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E102" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>23</v>
@@ -5096,30 +5096,30 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E103" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J103" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J103" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K103" s="2" t="inlineStr">
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,26 +5141,26 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>833</v>
+        <v>755</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>211</v>
+        <v>-221</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5193,10 +5193,10 @@
         <v>833</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>622</v>
+        <v>976</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>211</v>
+        <v>-143</v>
       </c>
       <c r="G105" s="2" t="n">
         <v>46</v>
@@ -5207,9 +5207,9 @@
       <c r="I105" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J105" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J105" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,26 +5231,26 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>833</v>
+        <v>729</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>211</v>
+        <v>107</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,26 +5276,26 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>96</v>
+        <v>107</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,26 +5321,26 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>616</v>
+        <v>833</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>-6</v>
+        <v>211</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J108" s="3" t="inlineStr">
         <is>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,26 +5366,26 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>616</v>
+        <v>800</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>-6</v>
+        <v>178</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J109" s="3" t="inlineStr">
         <is>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,26 +5411,26 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>649</v>
+        <v>833</v>
       </c>
       <c r="E110" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>27</v>
+        <v>211</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J110" s="3" t="inlineStr">
         <is>
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5460,13 +5460,13 @@
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>649</v>
+        <v>619</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>27</v>
+        <v>-3</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>40</v>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>22-JUL-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,26 +5681,26 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
-        <v>649</v>
+        <v>616</v>
       </c>
       <c r="E116" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F116" s="2" t="n">
-        <v>27</v>
+        <v>-6</v>
       </c>
       <c r="G116" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H116" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J116" s="3" t="inlineStr">
         <is>
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,26 +5726,26 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>718</v>
+        <v>616</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>96</v>
+        <v>-6</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,26 +5771,26 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>718</v>
+        <v>649</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>96</v>
+        <v>27</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5816,26 +5816,26 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>800</v>
+        <v>649</v>
       </c>
       <c r="E119" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>178</v>
+        <v>27</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J119" s="3" t="inlineStr">
         <is>
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,17 +5861,17 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>800</v>
+        <v>833</v>
       </c>
       <c r="E120" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="G120" s="2" t="n">
         <v>46</v>
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,26 +5906,26 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>833</v>
+        <v>616</v>
       </c>
       <c r="E121" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>211</v>
+        <v>-6</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J121" s="3" t="inlineStr">
         <is>
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,26 +5951,26 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>833</v>
+        <v>619</v>
       </c>
       <c r="E122" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>211</v>
+        <v>-3</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,26 +6041,26 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>833</v>
+        <v>616</v>
       </c>
       <c r="E124" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>211</v>
+        <v>-6</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>718</v>
+        <v>833</v>
       </c>
       <c r="E125" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>46</v>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>718</v>
+        <v>833</v>
       </c>
       <c r="E126" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>46</v>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>718</v>
+        <v>833</v>
       </c>
       <c r="E127" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>96</v>
+        <v>211</v>
       </c>
       <c r="G127" s="2" t="n">
         <v>46</v>
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,26 +6221,26 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>833</v>
+        <v>616</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>211</v>
+        <v>-6</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J128" s="3" t="inlineStr">
         <is>
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,26 +6266,26 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>833</v>
+        <v>619</v>
       </c>
       <c r="E129" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>211</v>
+        <v>-3</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H129" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J129" s="3" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,26 +6311,26 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E130" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6356,7 +6356,7 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,26 +6401,26 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E132" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,26 +6446,26 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>619</v>
+        <v>833</v>
       </c>
       <c r="E133" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>-3</v>
+        <v>211</v>
       </c>
       <c r="G133" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H133" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J133" s="3" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,26 +6491,26 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>619</v>
+        <v>833</v>
       </c>
       <c r="E134" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>-3</v>
+        <v>211</v>
       </c>
       <c r="G134" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H134" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J134" s="3" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>05-AUG-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,17 +6536,17 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>833</v>
+        <v>718</v>
       </c>
       <c r="E135" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>211</v>
+        <v>96</v>
       </c>
       <c r="G135" s="2" t="n">
         <v>46</v>
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,26 +6581,26 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>833</v>
+        <v>619</v>
       </c>
       <c r="E136" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>211</v>
+        <v>-3</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J136" s="3" t="inlineStr">
         <is>
@@ -6616,7 +6616,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>06-AUG-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6626,26 +6626,26 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E137" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J137" s="3" t="inlineStr">
         <is>
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>13-AUG-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6671,17 +6671,17 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>753</v>
+        <v>833</v>
       </c>
       <c r="E138" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>131</v>
+        <v>211</v>
       </c>
       <c r="G138" s="2" t="n">
         <v>46</v>
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,30 +6716,30 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>429</v>
+        <v>616</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-469</v>
+        <v>-6</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J139" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J139" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K139" s="2" t="inlineStr">
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,30 +6761,30 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>439</v>
+        <v>619</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-459</v>
+        <v>-3</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H140" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J140" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J140" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K140" s="2" t="inlineStr">
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,30 +6806,30 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>616</v>
+        <v>718</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>-282</v>
+        <v>96</v>
       </c>
       <c r="G141" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H141" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J141" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J141" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K141" s="2" t="inlineStr">
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6855,13 +6855,13 @@
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>1018</v>
+        <v>833</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>120</v>
+        <v>211</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>46</v>
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6896,26 +6896,26 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>1018</v>
+        <v>616</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>120</v>
+        <v>-6</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>-16</v>
+        <v>0</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -6931,7 +6931,7 @@
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>12-AUG-26</t>
         </is>
       </c>
       <c r="B144" s="2" t="inlineStr">
@@ -6941,26 +6941,26 @@
       </c>
       <c r="C144" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D144" s="2" t="n">
-        <v>1018</v>
+        <v>619</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F144" s="2" t="n">
-        <v>120</v>
+        <v>-3</v>
       </c>
       <c r="G144" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H144" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J144" s="3" t="inlineStr">
         <is>
@@ -6976,7 +6976,7 @@
     <row r="145">
       <c r="A145" s="2" t="inlineStr">
         <is>
-          <t>22-SEP-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B145" s="2" t="inlineStr">
@@ -6986,17 +6986,17 @@
       </c>
       <c r="C145" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D145" s="2" t="n">
-        <v>1018</v>
+        <v>753</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>898</v>
+        <v>622</v>
       </c>
       <c r="F145" s="2" t="n">
-        <v>120</v>
+        <v>131</v>
       </c>
       <c r="G145" s="2" t="n">
         <v>46</v>
@@ -7031,30 +7031,30 @@
       </c>
       <c r="C146" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D146" s="2" t="n">
-        <v>1075</v>
+        <v>429</v>
       </c>
       <c r="E146" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F146" s="2" t="n">
-        <v>177</v>
+        <v>-469</v>
       </c>
       <c r="G146" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H146" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J146" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J146" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K146" s="2" t="inlineStr">
@@ -7066,7 +7066,7 @@
     <row r="147">
       <c r="A147" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B147" s="2" t="inlineStr">
@@ -7076,30 +7076,30 @@
       </c>
       <c r="C147" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D147" s="2" t="n">
-        <v>1018</v>
+        <v>439</v>
       </c>
       <c r="E147" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F147" s="2" t="n">
-        <v>120</v>
+        <v>-459</v>
       </c>
       <c r="G147" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H147" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J147" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J147" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K147" s="2" t="inlineStr">
@@ -7111,7 +7111,7 @@
     <row r="148">
       <c r="A148" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B148" s="2" t="inlineStr">
@@ -7121,30 +7121,30 @@
       </c>
       <c r="C148" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D148" s="2" t="n">
-        <v>1018</v>
+        <v>439</v>
       </c>
       <c r="E148" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F148" s="2" t="n">
-        <v>120</v>
+        <v>-459</v>
       </c>
       <c r="G148" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H148" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J148" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J148" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K148" s="2" t="inlineStr">
@@ -7156,7 +7156,7 @@
     <row r="149">
       <c r="A149" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B149" s="2" t="inlineStr">
@@ -7166,7 +7166,7 @@
       </c>
       <c r="C149" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D149" s="2" t="n">
@@ -7201,7 +7201,7 @@
     <row r="150">
       <c r="A150" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B150" s="2" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="C150" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D150" s="2" t="n">
@@ -7246,7 +7246,7 @@
     <row r="151">
       <c r="A151" s="2" t="inlineStr">
         <is>
-          <t>23-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B151" s="2" t="inlineStr">
@@ -7256,17 +7256,17 @@
       </c>
       <c r="C151" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D151" s="2" t="n">
-        <v>1075</v>
+        <v>1018</v>
       </c>
       <c r="E151" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F151" s="2" t="n">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="G151" s="2" t="n">
         <v>46</v>
@@ -7291,7 +7291,7 @@
     <row r="152">
       <c r="A152" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B152" s="2" t="inlineStr">
@@ -7301,30 +7301,30 @@
       </c>
       <c r="C152" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D152" s="2" t="n">
-        <v>616</v>
+        <v>1018</v>
       </c>
       <c r="E152" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F152" s="2" t="n">
-        <v>-282</v>
+        <v>120</v>
       </c>
       <c r="G152" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H152" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J152" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J152" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K152" s="2" t="inlineStr">
@@ -7336,7 +7336,7 @@
     <row r="153">
       <c r="A153" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B153" s="2" t="inlineStr">
@@ -7346,30 +7346,30 @@
       </c>
       <c r="C153" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D153" s="2" t="n">
-        <v>616</v>
+        <v>1075</v>
       </c>
       <c r="E153" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F153" s="2" t="n">
-        <v>-282</v>
+        <v>177</v>
       </c>
       <c r="G153" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H153" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J153" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J153" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K153" s="2" t="inlineStr">
@@ -7381,7 +7381,7 @@
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B154" s="2" t="inlineStr">
@@ -7391,30 +7391,30 @@
       </c>
       <c r="C154" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D154" s="2" t="n">
-        <v>619</v>
+        <v>429</v>
       </c>
       <c r="E154" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F154" s="2" t="n">
-        <v>-279</v>
+        <v>-469</v>
       </c>
       <c r="G154" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H154" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J154" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J154" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K154" s="2" t="inlineStr">
@@ -7426,7 +7426,7 @@
     <row r="155">
       <c r="A155" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B155" s="2" t="inlineStr">
@@ -7436,30 +7436,30 @@
       </c>
       <c r="C155" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D155" s="2" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E155" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F155" s="2" t="n">
-        <v>-279</v>
+        <v>-282</v>
       </c>
       <c r="G155" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H155" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J155" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J155" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K155" s="2" t="inlineStr">
@@ -7471,7 +7471,7 @@
     <row r="156">
       <c r="A156" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B156" s="2" t="inlineStr">
@@ -7481,30 +7481,30 @@
       </c>
       <c r="C156" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D156" s="2" t="n">
-        <v>1018</v>
+        <v>616</v>
       </c>
       <c r="E156" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F156" s="2" t="n">
-        <v>120</v>
+        <v>-282</v>
       </c>
       <c r="G156" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H156" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J156" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J156" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K156" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
     <row r="157">
       <c r="A157" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B157" s="2" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="C157" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D157" s="2" t="n">
@@ -7561,7 +7561,7 @@
     <row r="158">
       <c r="A158" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B158" s="2" t="inlineStr">
@@ -7606,7 +7606,7 @@
     <row r="159">
       <c r="A159" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B159" s="2" t="inlineStr">
@@ -7616,17 +7616,17 @@
       </c>
       <c r="C159" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D159" s="2" t="n">
-        <v>1056</v>
+        <v>1018</v>
       </c>
       <c r="E159" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F159" s="2" t="n">
-        <v>158</v>
+        <v>120</v>
       </c>
       <c r="G159" s="2" t="n">
         <v>46</v>
@@ -7651,7 +7651,7 @@
     <row r="160">
       <c r="A160" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B160" s="2" t="inlineStr">
@@ -7661,17 +7661,17 @@
       </c>
       <c r="C160" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D160" s="2" t="n">
-        <v>1075</v>
+        <v>1018</v>
       </c>
       <c r="E160" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F160" s="2" t="n">
-        <v>177</v>
+        <v>120</v>
       </c>
       <c r="G160" s="2" t="n">
         <v>46</v>
@@ -7696,7 +7696,7 @@
     <row r="161">
       <c r="A161" s="2" t="inlineStr">
         <is>
-          <t>24-SEP-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B161" s="2" t="inlineStr">
@@ -7706,17 +7706,17 @@
       </c>
       <c r="C161" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D161" s="2" t="n">
-        <v>1113</v>
+        <v>1056</v>
       </c>
       <c r="E161" s="2" t="n">
         <v>898</v>
       </c>
       <c r="F161" s="2" t="n">
-        <v>215</v>
+        <v>158</v>
       </c>
       <c r="G161" s="2" t="n">
         <v>46</v>
@@ -7733,6 +7733,501 @@
         </is>
       </c>
       <c r="K161" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B162" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C162" s="2" t="inlineStr">
+        <is>
+          <t>Saudia SV-315</t>
+        </is>
+      </c>
+      <c r="D162" s="2" t="n">
+        <v>1056</v>
+      </c>
+      <c r="E162" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F162" s="2" t="n">
+        <v>158</v>
+      </c>
+      <c r="G162" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H162" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I162" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J162" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K162" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="2" t="inlineStr">
+        <is>
+          <t>23-SEP-26</t>
+        </is>
+      </c>
+      <c r="B163" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C163" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D163" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E163" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F163" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G163" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H163" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I163" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J163" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K163" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B164" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C164" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-793</t>
+        </is>
+      </c>
+      <c r="D164" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E164" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F164" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G164" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H164" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I164" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J164" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K164" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B165" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C165" s="2" t="inlineStr">
+        <is>
+          <t>flynas XY-576</t>
+        </is>
+      </c>
+      <c r="D165" s="2" t="n">
+        <v>429</v>
+      </c>
+      <c r="E165" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F165" s="2" t="n">
+        <v>-469</v>
+      </c>
+      <c r="G165" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H165" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I165" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J165" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K165" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B166" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C166" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-775</t>
+        </is>
+      </c>
+      <c r="D166" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E166" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F166" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G166" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H166" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I166" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J166" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K166" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B167" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C167" s="2" t="inlineStr">
+        <is>
+          <t>flyadeal F3-771</t>
+        </is>
+      </c>
+      <c r="D167" s="2" t="n">
+        <v>439</v>
+      </c>
+      <c r="E167" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F167" s="2" t="n">
+        <v>-459</v>
+      </c>
+      <c r="G167" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="H167" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I167" s="2" t="n">
+        <v>15</v>
+      </c>
+      <c r="J167" s="4" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="K167" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B168" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C168" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-694</t>
+        </is>
+      </c>
+      <c r="D168" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E168" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F168" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G168" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H168" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I168" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J168" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K168" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B169" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C169" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-696</t>
+        </is>
+      </c>
+      <c r="D169" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E169" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F169" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G169" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H169" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I169" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J169" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K169" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B170" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C170" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-640</t>
+        </is>
+      </c>
+      <c r="D170" s="2" t="n">
+        <v>1018</v>
+      </c>
+      <c r="E170" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F170" s="2" t="n">
+        <v>120</v>
+      </c>
+      <c r="G170" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H170" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I170" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J170" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K170" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B171" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C171" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-678</t>
+        </is>
+      </c>
+      <c r="D171" s="2" t="n">
+        <v>1075</v>
+      </c>
+      <c r="E171" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F171" s="2" t="n">
+        <v>177</v>
+      </c>
+      <c r="G171" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H171" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I171" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J171" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K171" s="2" t="inlineStr">
+        <is>
+          <t>SAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="2" t="inlineStr">
+        <is>
+          <t>24-SEP-26</t>
+        </is>
+      </c>
+      <c r="B172" s="2" t="inlineStr">
+        <is>
+          <t>SM-494</t>
+        </is>
+      </c>
+      <c r="C172" s="2" t="inlineStr">
+        <is>
+          <t>EgyptAir MS-676</t>
+        </is>
+      </c>
+      <c r="D172" s="2" t="n">
+        <v>1113</v>
+      </c>
+      <c r="E172" s="2" t="n">
+        <v>898</v>
+      </c>
+      <c r="F172" s="2" t="n">
+        <v>215</v>
+      </c>
+      <c r="G172" s="2" t="n">
+        <v>46</v>
+      </c>
+      <c r="H172" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="I172" s="2" t="n">
+        <v>-16</v>
+      </c>
+      <c r="J172" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="K172" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -54,14 +54,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF3CD"/>
-        <bgColor rgb="00FFF3CD"/>
+        <fgColor rgb="00F8D7DA"/>
+        <bgColor rgb="00F8D7DA"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F8D7DA"/>
-        <bgColor rgb="00F8D7DA"/>
+        <fgColor rgb="00FFF3CD"/>
+        <bgColor rgb="00FFF3CD"/>
       </patternFill>
     </fill>
   </fills>
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K172"/>
+  <dimension ref="A1:K143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>25-MAY-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,17 +641,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>810</v>
+        <v>1018</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>820</v>
+        <v>976</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>-10</v>
+        <v>42</v>
       </c>
       <c r="G4" s="2" t="n">
         <v>46</v>
@@ -662,9 +662,9 @@
       <c r="I4" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J4" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J4" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -686,26 +686,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>819</v>
+        <v>810</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>820</v>
+        <v>742</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>-1</v>
+        <v>68</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
@@ -731,26 +731,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>829</v>
+        <v>923</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>820</v>
+        <v>742</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>9</v>
+        <v>181</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
@@ -776,17 +776,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
         <v>923</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>820</v>
+        <v>742</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>103</v>
+        <v>181</v>
       </c>
       <c r="G7" s="2" t="n">
         <v>46</v>
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,17 +821,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>923</v>
+        <v>753</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>820</v>
+        <v>682</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>103</v>
+        <v>71</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>46</v>
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,17 +866,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1018</v>
+        <v>1113</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>820</v>
+        <v>1753</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>198</v>
+        <v>-640</v>
       </c>
       <c r="G9" s="2" t="n">
         <v>46</v>
@@ -887,9 +887,9 @@
       <c r="I9" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J9" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>03-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,17 +911,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>753</v>
+        <v>1170</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>682</v>
+        <v>1753</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>71</v>
+        <v>-583</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>46</v>
@@ -932,9 +932,9 @@
       <c r="I10" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J10" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -956,30 +956,30 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1113</v>
+        <v>1328</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-640</v>
+        <v>-425</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1170</v>
+        <v>1328</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-583</v>
+        <v>-425</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1046,17 +1046,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1328</v>
+        <v>1491</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-425</v>
+        <v>-262</v>
       </c>
       <c r="G13" s="2" t="n">
         <v>23</v>
@@ -1067,9 +1067,9 @@
       <c r="I13" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J13" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1095,26 +1095,26 @@
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1328</v>
+        <v>1572</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-425</v>
+        <v>-181</v>
       </c>
       <c r="G14" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H14" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1328</v>
+        <v>806</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-425</v>
+        <v>-947</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>7</v>
+        <v>30</v>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>1491</v>
+        <v>809</v>
       </c>
       <c r="E16" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-262</v>
+        <v>-944</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J16" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>806</v>
+        <v>875</v>
       </c>
       <c r="E17" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-947</v>
+        <v>-878</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -1247,7 +1247,7 @@
       <c r="I17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="J17" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1271,17 +1271,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>809</v>
+        <v>909</v>
       </c>
       <c r="E18" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-944</v>
+        <v>-844</v>
       </c>
       <c r="G18" s="2" t="n">
         <v>15</v>
@@ -1292,7 +1292,7 @@
       <c r="I18" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J18" s="5" t="inlineStr">
+      <c r="J18" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1316,28 +1316,28 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>875</v>
+        <v>1223</v>
       </c>
       <c r="E19" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-878</v>
+        <v>-530</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J19" s="5" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1361,30 +1361,30 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>909</v>
+        <v>1328</v>
       </c>
       <c r="E20" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-844</v>
+        <v>-425</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H20" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1406,30 +1406,30 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1223</v>
+        <v>1328</v>
       </c>
       <c r="E21" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-530</v>
+        <v>-425</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -1451,30 +1451,30 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1328</v>
+        <v>1358</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-425</v>
+        <v>-395</v>
       </c>
       <c r="G22" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1496,28 +1496,28 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1328</v>
+        <v>1519</v>
       </c>
       <c r="E23" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-425</v>
+        <v>-234</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J23" s="4" t="inlineStr">
+        <v>-10</v>
+      </c>
+      <c r="J23" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1541,17 +1541,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1358</v>
+        <v>1555</v>
       </c>
       <c r="E24" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-395</v>
+        <v>-198</v>
       </c>
       <c r="G24" s="2" t="n">
         <v>46</v>
@@ -1562,7 +1562,7 @@
       <c r="I24" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J24" s="5" t="inlineStr">
+      <c r="J24" s="4" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1519</v>
+        <v>1818</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>-234</v>
+        <v>65</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J25" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1631,30 +1631,30 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>1555</v>
+        <v>499</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-198</v>
+        <v>-555</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,30 +1676,30 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>1818</v>
+        <v>690</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>65</v>
+        <v>-364</v>
       </c>
       <c r="G27" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H27" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>729</v>
+        <v>813</v>
       </c>
       <c r="E28" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-325</v>
+        <v>-241</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J28" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1922,7 +1922,7 @@
       <c r="I32" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J32" s="4" t="inlineStr">
+      <c r="J32" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -1946,17 +1946,17 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>933</v>
+        <v>1223</v>
       </c>
       <c r="E33" s="2" t="n">
         <v>1054</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>-121</v>
+        <v>169</v>
       </c>
       <c r="G33" s="2" t="n">
         <v>46</v>
@@ -1967,9 +1967,9 @@
       <c r="I33" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J33" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>1056</v>
+        <v>698</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>2</v>
+        <v>-278</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J34" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2040,13 +2040,13 @@
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>1223</v>
+        <v>753</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>169</v>
+        <v>-223</v>
       </c>
       <c r="G35" s="2" t="n">
         <v>46</v>
@@ -2057,9 +2057,9 @@
       <c r="I35" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="J35" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>469</v>
+        <v>753</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-507</v>
+        <v>-223</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>469</v>
+        <v>753</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-507</v>
+        <v>-223</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2171,30 +2171,30 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>499</v>
+        <v>755</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-477</v>
+        <v>-221</v>
       </c>
       <c r="G38" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H38" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J38" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K38" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>499</v>
+        <v>813</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-477</v>
+        <v>-163</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>698</v>
+        <v>813</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-278</v>
+        <v>-163</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>23</v>
@@ -2296,7 +2296,7 @@
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>753</v>
+        <v>469</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-223</v>
+        <v>-507</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2341,7 +2341,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>753</v>
+        <v>469</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-223</v>
+        <v>-507</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2386,7 +2386,7 @@
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
@@ -2396,30 +2396,30 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>753</v>
+        <v>499</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-223</v>
+        <v>-477</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K43" s="2" t="inlineStr">
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,17 +2441,17 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G44" s="2" t="n">
         <v>23</v>
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,17 +2486,17 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>813</v>
+        <v>698</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-163</v>
+        <v>-278</v>
       </c>
       <c r="G45" s="2" t="n">
         <v>23</v>
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,30 +2531,30 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>813</v>
+        <v>753</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-163</v>
+        <v>-223</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J46" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J46" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K46" s="2" t="inlineStr">
@@ -2576,30 +2576,30 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>469</v>
+        <v>755</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-507</v>
+        <v>-221</v>
       </c>
       <c r="G47" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H47" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J47" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J47" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K47" s="2" t="inlineStr">
@@ -2621,30 +2621,30 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>469</v>
+        <v>813</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-507</v>
+        <v>-163</v>
       </c>
       <c r="G48" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H48" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J48" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J48" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K48" s="2" t="inlineStr">
@@ -2666,30 +2666,30 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>499</v>
+        <v>813</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-477</v>
+        <v>-163</v>
       </c>
       <c r="G49" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H49" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J49" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J49" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K49" s="2" t="inlineStr">
@@ -2711,30 +2711,30 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-278</v>
+        <v>-143</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J50" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J50" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
@@ -2791,7 +2791,7 @@
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
@@ -2801,30 +2801,30 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>753</v>
+        <v>698</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-223</v>
+        <v>-278</v>
       </c>
       <c r="G52" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H52" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J52" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J52" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K52" s="2" t="inlineStr">
@@ -2836,7 +2836,7 @@
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>23</v>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,17 +2891,17 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>813</v>
+        <v>698</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-163</v>
+        <v>-278</v>
       </c>
       <c r="G54" s="2" t="n">
         <v>23</v>
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,17 +2936,17 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>813</v>
+        <v>755</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-163</v>
+        <v>-221</v>
       </c>
       <c r="G55" s="2" t="n">
         <v>23</v>
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,17 +2981,17 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>833</v>
+        <v>1056</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>-143</v>
+        <v>80</v>
       </c>
       <c r="G56" s="2" t="n">
         <v>46</v>
@@ -3002,9 +3002,9 @@
       <c r="I56" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J56" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J56" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>439</v>
+        <v>1056</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>-537</v>
+        <v>80</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J57" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J57" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3061,7 +3061,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
@@ -3092,7 +3092,7 @@
       <c r="I58" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J58" s="4" t="inlineStr">
+      <c r="J58" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3106,7 +3106,7 @@
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
@@ -3116,17 +3116,17 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>499</v>
+        <v>469</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-477</v>
+        <v>-507</v>
       </c>
       <c r="G59" s="2" t="n">
         <v>15</v>
@@ -3137,7 +3137,7 @@
       <c r="I59" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J59" s="4" t="inlineStr">
+      <c r="J59" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3151,7 +3151,7 @@
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
@@ -3161,30 +3161,30 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>698</v>
+        <v>499</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-278</v>
+        <v>-477</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J60" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K60" s="2" t="inlineStr">
@@ -3196,7 +3196,7 @@
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
@@ -3206,30 +3206,30 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>698</v>
+        <v>499</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-278</v>
+        <v>-477</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J61" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K61" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3255,26 +3255,26 @@
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>698</v>
+        <v>753</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-278</v>
+        <v>-223</v>
       </c>
       <c r="G62" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J62" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J62" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,17 +3296,17 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>698</v>
+        <v>755</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-278</v>
+        <v>-221</v>
       </c>
       <c r="G63" s="2" t="n">
         <v>23</v>
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,30 +3341,30 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>755</v>
+        <v>833</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-221</v>
+        <v>-143</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J64" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K64" s="2" t="inlineStr">
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,30 +3386,30 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-163</v>
+        <v>-143</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J65" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J65" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K65" s="2" t="inlineStr">
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,30 +3431,30 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>813</v>
+        <v>923</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-163</v>
+        <v>-53</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J66" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J66" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K66" s="2" t="inlineStr">
@@ -3466,7 +3466,7 @@
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
@@ -3480,24 +3480,24 @@
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>469</v>
+        <v>646</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-507</v>
+        <v>-330</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J67" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J67" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3511,7 +3511,7 @@
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
@@ -3525,24 +3525,24 @@
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>469</v>
+        <v>646</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-507</v>
+        <v>-330</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J68" s="4" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3556,7 +3556,7 @@
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
@@ -3570,26 +3570,26 @@
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>499</v>
+        <v>689</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-477</v>
+        <v>-287</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J69" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
@@ -3615,26 +3615,26 @@
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>499</v>
+        <v>689</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-477</v>
+        <v>-287</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>15</v>
+        <v>-10</v>
       </c>
       <c r="J70" s="4" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3646,7 +3646,7 @@
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>753</v>
+        <v>690</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-223</v>
+        <v>-286</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J71" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,17 +3701,17 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G72" s="2" t="n">
         <v>23</v>
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J73" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J73" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3795,26 +3795,26 @@
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>833</v>
+        <v>698</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-143</v>
+        <v>-278</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J74" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J74" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,30 +3836,30 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>923</v>
+        <v>755</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-53</v>
+        <v>-221</v>
       </c>
       <c r="G75" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H75" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J75" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J75" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K75" s="2" t="inlineStr">
@@ -3881,28 +3881,28 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>646</v>
+        <v>833</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-330</v>
+        <v>-143</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J76" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J76" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3926,28 +3926,28 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>646</v>
+        <v>933</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-330</v>
+        <v>-43</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J77" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J77" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -3961,7 +3961,7 @@
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B78" s="2" t="inlineStr">
@@ -3971,30 +3971,30 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>689</v>
+        <v>469</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-287</v>
+        <v>-507</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K78" s="2" t="inlineStr">
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4016,30 +4016,30 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>689</v>
+        <v>646</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-287</v>
+        <v>-330</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="K79" s="2" t="inlineStr">
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,30 +4061,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-286</v>
+        <v>-287</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J80" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J80" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>698</v>
+        <v>690</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-278</v>
+        <v>-286</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>23</v>
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4352,7 +4352,7 @@
       <c r="I86" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J86" s="4" t="inlineStr">
+      <c r="J86" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4397,7 +4397,7 @@
       <c r="I87" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J87" s="4" t="inlineStr">
+      <c r="J87" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4442,7 +4442,7 @@
       <c r="I88" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J88" s="4" t="inlineStr">
+      <c r="J88" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4487,7 +4487,7 @@
       <c r="I89" s="2" t="n">
         <v>15</v>
       </c>
-      <c r="J89" s="4" t="inlineStr">
+      <c r="J89" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,7 +4601,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,7 +4646,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,17 +4691,17 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>755</v>
+        <v>698</v>
       </c>
       <c r="E94" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-221</v>
+        <v>-278</v>
       </c>
       <c r="G94" s="2" t="n">
         <v>23</v>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,30 +4736,30 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>833</v>
+        <v>755</v>
       </c>
       <c r="E95" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-143</v>
+        <v>-221</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J95" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J95" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K95" s="2" t="inlineStr">
@@ -4781,28 +4781,28 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>469</v>
+        <v>833</v>
       </c>
       <c r="E96" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-507</v>
+        <v>-143</v>
       </c>
       <c r="G96" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H96" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J96" s="4" t="inlineStr">
+        <v>-16</v>
+      </c>
+      <c r="J96" s="5" t="inlineStr">
         <is>
           <t>MED</t>
         </is>
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,30 +4826,30 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>469</v>
+        <v>833</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>-507</v>
+        <v>211</v>
       </c>
       <c r="G97" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H97" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J97" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J97" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K97" s="2" t="inlineStr">
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,30 +4871,30 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>499</v>
+        <v>586</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-477</v>
+        <v>-36</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J98" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J98" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K98" s="2" t="inlineStr">
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,26 +4916,26 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>690</v>
+        <v>649</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>-286</v>
+        <v>27</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J99" s="3" t="inlineStr">
         <is>
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,26 +4961,26 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>-286</v>
+        <v>67</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J100" s="3" t="inlineStr">
         <is>
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>20-JUL-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,26 +5006,26 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>-278</v>
+        <v>211</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J101" s="3" t="inlineStr">
         <is>
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>21-JUL-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,26 +5051,26 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>698</v>
+        <v>833</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>-278</v>
+        <v>211</v>
       </c>
       <c r="G102" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H102" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J102" s="3" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,26 +5096,26 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>698</v>
+        <v>616</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-278</v>
+        <v>-6</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>23-JUL-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,26 +5141,26 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>755</v>
+        <v>833</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>-221</v>
+        <v>211</v>
       </c>
       <c r="G104" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H104" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J104" s="3" t="inlineStr">
         <is>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>27-JUL-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,30 +5186,30 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>833</v>
+        <v>616</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-143</v>
+        <v>-6</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J105" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J105" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K105" s="2" t="inlineStr">
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,26 +5231,26 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>729</v>
+        <v>833</v>
       </c>
       <c r="E106" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="G106" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H106" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J106" s="3" t="inlineStr">
         <is>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,26 +5276,26 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>729</v>
+        <v>833</v>
       </c>
       <c r="E107" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>107</v>
+        <v>211</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J107" s="3" t="inlineStr">
         <is>
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,17 +5321,17 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>833</v>
+        <v>800</v>
       </c>
       <c r="E108" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>211</v>
+        <v>178</v>
       </c>
       <c r="G108" s="2" t="n">
         <v>46</v>
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,17 +5366,17 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>800</v>
+        <v>833</v>
       </c>
       <c r="E109" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>178</v>
+        <v>211</v>
       </c>
       <c r="G109" s="2" t="n">
         <v>46</v>
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>30-JUL-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,26 +5456,26 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>619</v>
+        <v>833</v>
       </c>
       <c r="E111" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>-3</v>
+        <v>211</v>
       </c>
       <c r="G111" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J111" s="3" t="inlineStr">
         <is>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>04-AUG-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D112" s="2" t="n">
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>10-AUG-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,26 +5546,26 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>616</v>
+        <v>833</v>
       </c>
       <c r="E113" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>-6</v>
+        <v>211</v>
       </c>
       <c r="G113" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J113" s="3" t="inlineStr">
         <is>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>11-AUG-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,26 +5591,26 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>616</v>
+        <v>833</v>
       </c>
       <c r="E114" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>-6</v>
+        <v>211</v>
       </c>
       <c r="G114" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H114" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J114" s="3" t="inlineStr">
         <is>
@@ -5626,7 +5626,7 @@
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
         <is>
-          <t>22-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B115" s="2" t="inlineStr">
@@ -5636,26 +5636,26 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D115" s="2" t="n">
-        <v>619</v>
+        <v>616</v>
       </c>
       <c r="E115" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F115" s="2" t="n">
-        <v>-3</v>
+        <v>-6</v>
       </c>
       <c r="G115" s="2" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="H115" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>-10</v>
+        <v>0</v>
       </c>
       <c r="J115" s="3" t="inlineStr">
         <is>
@@ -5671,7 +5671,7 @@
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B116" s="2" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D116" s="2" t="n">
@@ -5716,7 +5716,7 @@
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B117" s="2" t="inlineStr">
@@ -5726,26 +5726,26 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D117" s="2" t="n">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="E117" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F117" s="2" t="n">
-        <v>-6</v>
+        <v>-3</v>
       </c>
       <c r="G117" s="2" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="H117" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>0</v>
+        <v>-10</v>
       </c>
       <c r="J117" s="3" t="inlineStr">
         <is>
@@ -5761,7 +5761,7 @@
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B118" s="2" t="inlineStr">
@@ -5771,26 +5771,26 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D118" s="2" t="n">
-        <v>649</v>
+        <v>753</v>
       </c>
       <c r="E118" s="2" t="n">
         <v>622</v>
       </c>
       <c r="F118" s="2" t="n">
-        <v>27</v>
+        <v>131</v>
       </c>
       <c r="G118" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H118" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J118" s="3" t="inlineStr">
         <is>
@@ -5806,7 +5806,7 @@
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B119" s="2" t="inlineStr">
@@ -5820,26 +5820,26 @@
         </is>
       </c>
       <c r="D119" s="2" t="n">
-        <v>649</v>
+        <v>429</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F119" s="2" t="n">
-        <v>27</v>
+        <v>-469</v>
       </c>
       <c r="G119" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H119" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J119" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J119" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K119" s="2" t="inlineStr">
@@ -5851,7 +5851,7 @@
     <row r="120">
       <c r="A120" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B120" s="2" t="inlineStr">
@@ -5861,30 +5861,30 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D120" s="2" t="n">
-        <v>833</v>
+        <v>439</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F120" s="2" t="n">
-        <v>211</v>
+        <v>-459</v>
       </c>
       <c r="G120" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H120" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J120" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J120" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K120" s="2" t="inlineStr">
@@ -5896,7 +5896,7 @@
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B121" s="2" t="inlineStr">
@@ -5906,30 +5906,30 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D121" s="2" t="n">
-        <v>616</v>
+        <v>439</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F121" s="2" t="n">
-        <v>-6</v>
+        <v>-459</v>
       </c>
       <c r="G121" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H121" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J121" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J121" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K121" s="2" t="inlineStr">
@@ -5941,7 +5941,7 @@
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B122" s="2" t="inlineStr">
@@ -5951,26 +5951,26 @@
       </c>
       <c r="C122" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D122" s="2" t="n">
-        <v>619</v>
+        <v>1018</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F122" s="2" t="n">
-        <v>-3</v>
+        <v>120</v>
       </c>
       <c r="G122" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H122" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J122" s="3" t="inlineStr">
         <is>
@@ -5986,7 +5986,7 @@
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B123" s="2" t="inlineStr">
@@ -5996,17 +5996,17 @@
       </c>
       <c r="C123" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D123" s="2" t="n">
-        <v>833</v>
+        <v>1018</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F123" s="2" t="n">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="G123" s="2" t="n">
         <v>46</v>
@@ -6031,7 +6031,7 @@
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B124" s="2" t="inlineStr">
@@ -6041,26 +6041,26 @@
       </c>
       <c r="C124" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D124" s="2" t="n">
-        <v>616</v>
+        <v>1018</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F124" s="2" t="n">
-        <v>-6</v>
+        <v>120</v>
       </c>
       <c r="G124" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H124" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J124" s="3" t="inlineStr">
         <is>
@@ -6076,7 +6076,7 @@
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B125" s="2" t="inlineStr">
@@ -6086,17 +6086,17 @@
       </c>
       <c r="C125" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D125" s="2" t="n">
-        <v>833</v>
+        <v>1018</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F125" s="2" t="n">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="G125" s="2" t="n">
         <v>46</v>
@@ -6121,7 +6121,7 @@
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B126" s="2" t="inlineStr">
@@ -6131,17 +6131,17 @@
       </c>
       <c r="C126" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D126" s="2" t="n">
-        <v>833</v>
+        <v>1075</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F126" s="2" t="n">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="G126" s="2" t="n">
         <v>46</v>
@@ -6166,7 +6166,7 @@
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B127" s="2" t="inlineStr">
@@ -6176,30 +6176,30 @@
       </c>
       <c r="C127" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D127" s="2" t="n">
-        <v>833</v>
+        <v>429</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F127" s="2" t="n">
-        <v>211</v>
+        <v>-469</v>
       </c>
       <c r="G127" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H127" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J127" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J127" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K127" s="2" t="inlineStr">
@@ -6211,7 +6211,7 @@
     <row r="128">
       <c r="A128" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B128" s="2" t="inlineStr">
@@ -6221,30 +6221,30 @@
       </c>
       <c r="C128" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D128" s="2" t="n">
-        <v>616</v>
+        <v>439</v>
       </c>
       <c r="E128" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F128" s="2" t="n">
-        <v>-6</v>
+        <v>-459</v>
       </c>
       <c r="G128" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H128" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J128" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K128" s="2" t="inlineStr">
@@ -6256,7 +6256,7 @@
     <row r="129">
       <c r="A129" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B129" s="2" t="inlineStr">
@@ -6266,30 +6266,30 @@
       </c>
       <c r="C129" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D129" s="2" t="n">
-        <v>619</v>
+        <v>439</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F129" s="2" t="n">
-        <v>-3</v>
+        <v>-459</v>
       </c>
       <c r="G129" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H129" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J129" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J129" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K129" s="2" t="inlineStr">
@@ -6301,7 +6301,7 @@
     <row r="130">
       <c r="A130" s="2" t="inlineStr">
         <is>
-          <t>03-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B130" s="2" t="inlineStr">
@@ -6311,26 +6311,26 @@
       </c>
       <c r="C130" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D130" s="2" t="n">
-        <v>619</v>
+        <v>1018</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F130" s="2" t="n">
-        <v>-3</v>
+        <v>120</v>
       </c>
       <c r="G130" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H130" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J130" s="3" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
     <row r="131">
       <c r="A131" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B131" s="2" t="inlineStr">
@@ -6356,26 +6356,26 @@
       </c>
       <c r="C131" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D131" s="2" t="n">
-        <v>616</v>
+        <v>1018</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F131" s="2" t="n">
-        <v>-6</v>
+        <v>120</v>
       </c>
       <c r="G131" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H131" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J131" s="3" t="inlineStr">
         <is>
@@ -6391,7 +6391,7 @@
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B132" s="2" t="inlineStr">
@@ -6401,26 +6401,26 @@
       </c>
       <c r="C132" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D132" s="2" t="n">
-        <v>619</v>
+        <v>1018</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F132" s="2" t="n">
-        <v>-3</v>
+        <v>120</v>
       </c>
       <c r="G132" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H132" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J132" s="3" t="inlineStr">
         <is>
@@ -6436,7 +6436,7 @@
     <row r="133">
       <c r="A133" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B133" s="2" t="inlineStr">
@@ -6446,17 +6446,17 @@
       </c>
       <c r="C133" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D133" s="2" t="n">
-        <v>833</v>
+        <v>1018</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F133" s="2" t="n">
-        <v>211</v>
+        <v>120</v>
       </c>
       <c r="G133" s="2" t="n">
         <v>46</v>
@@ -6481,7 +6481,7 @@
     <row r="134">
       <c r="A134" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B134" s="2" t="inlineStr">
@@ -6491,17 +6491,17 @@
       </c>
       <c r="C134" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D134" s="2" t="n">
-        <v>833</v>
+        <v>1075</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F134" s="2" t="n">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="G134" s="2" t="n">
         <v>46</v>
@@ -6526,7 +6526,7 @@
     <row r="135">
       <c r="A135" s="2" t="inlineStr">
         <is>
-          <t>05-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B135" s="2" t="inlineStr">
@@ -6536,30 +6536,30 @@
       </c>
       <c r="C135" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D135" s="2" t="n">
-        <v>718</v>
+        <v>429</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F135" s="2" t="n">
-        <v>96</v>
+        <v>-469</v>
       </c>
       <c r="G135" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H135" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J135" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J135" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K135" s="2" t="inlineStr">
@@ -6571,7 +6571,7 @@
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B136" s="2" t="inlineStr">
@@ -6581,30 +6581,30 @@
       </c>
       <c r="C136" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D136" s="2" t="n">
-        <v>619</v>
+        <v>429</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F136" s="2" t="n">
-        <v>-3</v>
+        <v>-469</v>
       </c>
       <c r="G136" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H136" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J136" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J136" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K136" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>06-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B137" s="2" t="inlineStr">
@@ -6626,30 +6626,30 @@
       </c>
       <c r="C137" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D137" s="2" t="n">
-        <v>619</v>
+        <v>439</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F137" s="2" t="n">
-        <v>-3</v>
+        <v>-459</v>
       </c>
       <c r="G137" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H137" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J137" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J137" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K137" s="2" t="inlineStr">
@@ -6661,7 +6661,7 @@
     <row r="138">
       <c r="A138" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B138" s="2" t="inlineStr">
@@ -6671,30 +6671,30 @@
       </c>
       <c r="C138" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D138" s="2" t="n">
-        <v>833</v>
+        <v>439</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F138" s="2" t="n">
-        <v>211</v>
+        <v>-459</v>
       </c>
       <c r="G138" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H138" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J138" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J138" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K138" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
     <row r="139">
       <c r="A139" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B139" s="2" t="inlineStr">
@@ -6716,26 +6716,26 @@
       </c>
       <c r="C139" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D139" s="2" t="n">
-        <v>616</v>
+        <v>1018</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F139" s="2" t="n">
-        <v>-6</v>
+        <v>120</v>
       </c>
       <c r="G139" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H139" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J139" s="3" t="inlineStr">
         <is>
@@ -6751,7 +6751,7 @@
     <row r="140">
       <c r="A140" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B140" s="2" t="inlineStr">
@@ -6761,26 +6761,26 @@
       </c>
       <c r="C140" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D140" s="2" t="n">
-        <v>619</v>
+        <v>1018</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F140" s="2" t="n">
-        <v>-3</v>
+        <v>120</v>
       </c>
       <c r="G140" s="2" t="n">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H140" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>-10</v>
+        <v>-16</v>
       </c>
       <c r="J140" s="3" t="inlineStr">
         <is>
@@ -6796,7 +6796,7 @@
     <row r="141">
       <c r="A141" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B141" s="2" t="inlineStr">
@@ -6806,17 +6806,17 @@
       </c>
       <c r="C141" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D141" s="2" t="n">
-        <v>718</v>
+        <v>1018</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F141" s="2" t="n">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="G141" s="2" t="n">
         <v>46</v>
@@ -6841,7 +6841,7 @@
     <row r="142">
       <c r="A142" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B142" s="2" t="inlineStr">
@@ -6851,17 +6851,17 @@
       </c>
       <c r="C142" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D142" s="2" t="n">
-        <v>833</v>
+        <v>1075</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F142" s="2" t="n">
-        <v>211</v>
+        <v>177</v>
       </c>
       <c r="G142" s="2" t="n">
         <v>46</v>
@@ -6886,7 +6886,7 @@
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
         <is>
-          <t>12-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B143" s="2" t="inlineStr">
@@ -6896,26 +6896,26 @@
       </c>
       <c r="C143" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D143" s="2" t="n">
-        <v>616</v>
+        <v>1113</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F143" s="2" t="n">
-        <v>-6</v>
+        <v>215</v>
       </c>
       <c r="G143" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H143" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J143" s="3" t="inlineStr">
         <is>
@@ -6923,1311 +6923,6 @@
         </is>
       </c>
       <c r="K143" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
-        <is>
-          <t>12-AUG-26</t>
-        </is>
-      </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="n">
-        <v>619</v>
-      </c>
-      <c r="E144" s="2" t="n">
-        <v>622</v>
-      </c>
-      <c r="F144" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G144" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H144" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I144" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J144" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K144" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="n">
-        <v>753</v>
-      </c>
-      <c r="E145" s="2" t="n">
-        <v>622</v>
-      </c>
-      <c r="F145" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="G145" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H145" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I145" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J145" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K145" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E146" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F146" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G146" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H146" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I146" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J146" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K146" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E147" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F147" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G147" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H147" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I147" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J147" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K147" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E148" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F148" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G148" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H148" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I148" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J148" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K148" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E149" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F149" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G149" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H149" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I149" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J149" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K149" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E150" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F150" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G150" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H150" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I150" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J150" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K150" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E151" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F151" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G151" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H151" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I151" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J151" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K151" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E152" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F152" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G152" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H152" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I152" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J152" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K152" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E153" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F153" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G153" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H153" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I153" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J153" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K153" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E154" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F154" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G154" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H154" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I154" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J154" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K154" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="n">
-        <v>616</v>
-      </c>
-      <c r="E155" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F155" s="2" t="n">
-        <v>-282</v>
-      </c>
-      <c r="G155" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H155" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I155" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J155" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K155" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="n">
-        <v>616</v>
-      </c>
-      <c r="E156" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F156" s="2" t="n">
-        <v>-282</v>
-      </c>
-      <c r="G156" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H156" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I156" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J156" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K156" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E157" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F157" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G157" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H157" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I157" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J157" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K157" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E158" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F158" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G158" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H158" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I158" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J158" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K158" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E159" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F159" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G159" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H159" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I159" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J159" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K159" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E160" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F160" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G160" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H160" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I160" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J160" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K160" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B161" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C161" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-317</t>
-        </is>
-      </c>
-      <c r="D161" s="2" t="n">
-        <v>1056</v>
-      </c>
-      <c r="E161" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F161" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="G161" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H161" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I161" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J161" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K161" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B162" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C162" s="2" t="inlineStr">
-        <is>
-          <t>Saudia SV-315</t>
-        </is>
-      </c>
-      <c r="D162" s="2" t="n">
-        <v>1056</v>
-      </c>
-      <c r="E162" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F162" s="2" t="n">
-        <v>158</v>
-      </c>
-      <c r="G162" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H162" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I162" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J162" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K162" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B163" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C163" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D163" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E163" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F163" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G163" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H163" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I163" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J163" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K163" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B164" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C164" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-793</t>
-        </is>
-      </c>
-      <c r="D164" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E164" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F164" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G164" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H164" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I164" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J164" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K164" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B165" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C165" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D165" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E165" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F165" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G165" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H165" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I165" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J165" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K165" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B166" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C166" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D166" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E166" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F166" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G166" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H166" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I166" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J166" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K166" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B167" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C167" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D167" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E167" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F167" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G167" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H167" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I167" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J167" s="4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K167" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B168" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C168" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D168" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E168" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F168" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G168" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H168" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I168" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J168" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K168" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B169" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C169" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D169" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E169" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F169" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G169" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H169" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I169" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J169" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K169" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B170" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C170" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D170" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E170" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F170" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G170" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H170" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I170" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J170" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K170" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B171" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C171" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D171" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E171" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F171" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G171" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H171" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I171" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J171" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K171" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B172" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C172" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D172" s="2" t="n">
-        <v>1113</v>
-      </c>
-      <c r="E172" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F172" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="G172" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H172" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I172" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J172" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K172" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>

--- a/excel_routes/route_MED_CAI_threats.xlsx
+++ b/excel_routes/route_MED_CAI_threats.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K143"/>
+  <dimension ref="A1:K114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -541,7 +541,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D2" s="2" t="n">
-        <v>1018</v>
+        <v>960</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>976</v>
+        <v>820</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>42</v>
+        <v>140</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>46</v>
@@ -586,7 +586,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>02-JUN-26</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -600,13 +600,13 @@
         </is>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1018</v>
+        <v>960</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>976</v>
+        <v>742</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>42</v>
+        <v>218</v>
       </c>
       <c r="G3" s="2" t="n">
         <v>46</v>
@@ -631,7 +631,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>25-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -641,30 +641,30 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1018</v>
+        <v>431</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>976</v>
+        <v>1753</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>42</v>
+        <v>-1322</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H4" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J4" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J4" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -676,7 +676,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -686,30 +686,30 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>810</v>
+        <v>431</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>68</v>
+        <v>-1322</v>
       </c>
       <c r="G5" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>30</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -731,30 +731,30 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>181</v>
+        <v>-844</v>
       </c>
       <c r="G6" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H6" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J6" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -766,7 +766,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>26-MAY-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -776,30 +776,30 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>923</v>
+        <v>953</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>742</v>
+        <v>1753</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>181</v>
+        <v>-800</v>
       </c>
       <c r="G7" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H7" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J7" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -811,7 +811,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>02-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -821,30 +821,30 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-391</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>753</v>
+        <v>953</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>682</v>
+        <v>1753</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>71</v>
+        <v>-800</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H8" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J8" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>7</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -856,7 +856,7 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -866,26 +866,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>1113</v>
+        <v>953</v>
       </c>
       <c r="E9" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>-640</v>
+        <v>-800</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H9" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
@@ -901,7 +901,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -911,26 +911,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D10" s="2" t="n">
-        <v>1170</v>
+        <v>1009</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>-583</v>
+        <v>-744</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H10" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
@@ -946,7 +946,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -956,26 +956,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1328</v>
+        <v>1519</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>-425</v>
+        <v>-234</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>23</v>
+        <v>40</v>
       </c>
       <c r="H11" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>7</v>
+        <v>-10</v>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
@@ -991,7 +991,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1001,30 +1001,30 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>1328</v>
+        <v>1535</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>-425</v>
+        <v>-218</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H12" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J12" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1036,7 +1036,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1046,30 +1046,30 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-680</t>
         </is>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1491</v>
+        <v>1535</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>-262</v>
+        <v>-218</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H13" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J13" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>03-JUN-26</t>
+          <t>04-JUN-26</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1091,17 +1091,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1572</v>
+        <v>1747</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F14" s="2" t="n">
-        <v>-181</v>
+        <v>-6</v>
       </c>
       <c r="G14" s="2" t="n">
         <v>46</v>
@@ -1112,9 +1112,9 @@
       <c r="I14" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1136,30 +1136,30 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D15" s="2" t="n">
-        <v>806</v>
+        <v>1855</v>
       </c>
       <c r="E15" s="2" t="n">
         <v>1753</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>-947</v>
+        <v>102</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="H15" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>-16</v>
+      </c>
+      <c r="J15" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1171,7 +1171,7 @@
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1181,30 +1181,30 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D16" s="2" t="n">
-        <v>809</v>
+        <v>431</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>-944</v>
+        <v>-623</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>30</v>
+      </c>
+      <c r="J16" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1226,17 +1226,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D17" s="2" t="n">
-        <v>875</v>
+        <v>431</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>-878</v>
+        <v>-623</v>
       </c>
       <c r="G17" s="2" t="n">
         <v>0</v>
@@ -1247,9 +1247,9 @@
       <c r="I17" s="2" t="n">
         <v>30</v>
       </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J17" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -1261,7 +1261,7 @@
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
@@ -1271,30 +1271,30 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>Saudia SV-317</t>
         </is>
       </c>
       <c r="D18" s="2" t="n">
-        <v>909</v>
+        <v>431</v>
       </c>
       <c r="E18" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F18" s="2" t="n">
-        <v>-844</v>
+        <v>-623</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H18" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>30</v>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1306,7 +1306,7 @@
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
@@ -1316,30 +1316,30 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-680</t>
+          <t>Saudia SV-315</t>
         </is>
       </c>
       <c r="D19" s="2" t="n">
-        <v>1223</v>
+        <v>431</v>
       </c>
       <c r="E19" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F19" s="2" t="n">
-        <v>-530</v>
+        <v>-623</v>
       </c>
       <c r="G19" s="2" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="H19" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>30</v>
+      </c>
+      <c r="J19" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1351,7 +1351,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1365,13 +1365,13 @@
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>1328</v>
+        <v>813</v>
       </c>
       <c r="E20" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F20" s="2" t="n">
-        <v>-425</v>
+        <v>-241</v>
       </c>
       <c r="G20" s="2" t="n">
         <v>23</v>
@@ -1382,9 +1382,9 @@
       <c r="I20" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J20" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J20" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
@@ -1406,26 +1406,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D21" s="2" t="n">
-        <v>1328</v>
+        <v>960</v>
       </c>
       <c r="E21" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F21" s="2" t="n">
-        <v>-425</v>
+        <v>-94</v>
       </c>
       <c r="G21" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
@@ -1441,7 +1441,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>08-JUN-26</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
@@ -1451,17 +1451,17 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D22" s="2" t="n">
-        <v>1358</v>
+        <v>1260</v>
       </c>
       <c r="E22" s="2" t="n">
-        <v>1753</v>
+        <v>1054</v>
       </c>
       <c r="F22" s="2" t="n">
-        <v>-395</v>
+        <v>206</v>
       </c>
       <c r="G22" s="2" t="n">
         <v>46</v>
@@ -1472,9 +1472,9 @@
       <c r="I22" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J22" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J22" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -1486,7 +1486,7 @@
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
@@ -1496,26 +1496,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D23" s="2" t="n">
-        <v>1519</v>
+        <v>469</v>
       </c>
       <c r="E23" s="2" t="n">
-        <v>1753</v>
+        <v>976</v>
       </c>
       <c r="F23" s="2" t="n">
-        <v>-234</v>
+        <v>-507</v>
       </c>
       <c r="G23" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H23" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>-10</v>
+        <v>15</v>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
@@ -1531,7 +1531,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1541,30 +1541,30 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D24" s="2" t="n">
-        <v>1555</v>
+        <v>646</v>
       </c>
       <c r="E24" s="2" t="n">
-        <v>1753</v>
+        <v>976</v>
       </c>
       <c r="F24" s="2" t="n">
-        <v>-198</v>
+        <v>-330</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="H24" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J24" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0</v>
+      </c>
+      <c r="J24" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -1576,7 +1576,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>04-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
@@ -1586,30 +1586,30 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D25" s="2" t="n">
-        <v>1818</v>
+        <v>689</v>
       </c>
       <c r="E25" s="2" t="n">
-        <v>1753</v>
+        <v>976</v>
       </c>
       <c r="F25" s="2" t="n">
-        <v>65</v>
+        <v>-287</v>
       </c>
       <c r="G25" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H25" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-10</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
@@ -1621,7 +1621,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1635,26 +1635,26 @@
         </is>
       </c>
       <c r="D26" s="2" t="n">
-        <v>499</v>
+        <v>689</v>
       </c>
       <c r="E26" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F26" s="2" t="n">
-        <v>-555</v>
+        <v>-287</v>
       </c>
       <c r="G26" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H26" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J26" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
@@ -1676,17 +1676,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D27" s="2" t="n">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="E27" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F27" s="2" t="n">
-        <v>-364</v>
+        <v>-241</v>
       </c>
       <c r="G27" s="2" t="n">
         <v>23</v>
@@ -1697,9 +1697,9 @@
       <c r="I27" s="2" t="n">
         <v>7</v>
       </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
@@ -1711,7 +1711,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
@@ -1721,30 +1721,30 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D28" s="2" t="n">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F28" s="2" t="n">
-        <v>-241</v>
+        <v>-186</v>
       </c>
       <c r="G28" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H28" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J28" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K28" s="2" t="inlineStr">
@@ -1756,7 +1756,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
@@ -1766,30 +1766,30 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-391</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D29" s="2" t="n">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F29" s="2" t="n">
-        <v>-241</v>
+        <v>-186</v>
       </c>
       <c r="G29" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H29" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J29" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
@@ -1801,7 +1801,7 @@
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
@@ -1811,30 +1811,30 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-317</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D30" s="2" t="n">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F30" s="2" t="n">
-        <v>-241</v>
+        <v>-186</v>
       </c>
       <c r="G30" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H30" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J30" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J30" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
@@ -1846,7 +1846,7 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
@@ -1856,17 +1856,17 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-315</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D31" s="2" t="n">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F31" s="2" t="n">
-        <v>-241</v>
+        <v>-184</v>
       </c>
       <c r="G31" s="2" t="n">
         <v>23</v>
@@ -1891,7 +1891,7 @@
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
@@ -1901,30 +1901,30 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D32" s="2" t="n">
-        <v>923</v>
+        <v>813</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F32" s="2" t="n">
-        <v>-131</v>
+        <v>-163</v>
       </c>
       <c r="G32" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H32" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J32" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K32" s="2" t="inlineStr">
@@ -1936,7 +1936,7 @@
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>08-JUN-26</t>
+          <t>06-JUL-26</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
@@ -1946,26 +1946,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D33" s="2" t="n">
-        <v>1223</v>
+        <v>813</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>1054</v>
+        <v>976</v>
       </c>
       <c r="F33" s="2" t="n">
-        <v>169</v>
+        <v>-163</v>
       </c>
       <c r="G33" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H33" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>-16</v>
+        <v>7</v>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
@@ -1981,7 +1981,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
@@ -1991,30 +1991,30 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D34" s="2" t="n">
-        <v>698</v>
+        <v>469</v>
       </c>
       <c r="E34" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F34" s="2" t="n">
-        <v>-278</v>
+        <v>-507</v>
       </c>
       <c r="G34" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H34" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J34" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J34" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K34" s="2" t="inlineStr">
@@ -2026,7 +2026,7 @@
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2036,30 +2036,30 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D35" s="2" t="n">
-        <v>753</v>
+        <v>469</v>
       </c>
       <c r="E35" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F35" s="2" t="n">
-        <v>-223</v>
+        <v>-507</v>
       </c>
       <c r="G35" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H35" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J35" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
@@ -2071,7 +2071,7 @@
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2081,30 +2081,30 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D36" s="2" t="n">
-        <v>753</v>
+        <v>539</v>
       </c>
       <c r="E36" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F36" s="2" t="n">
-        <v>-223</v>
+        <v>-437</v>
       </c>
       <c r="G36" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H36" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J36" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K36" s="2" t="inlineStr">
@@ -2116,7 +2116,7 @@
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2126,30 +2126,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D37" s="2" t="n">
-        <v>753</v>
+        <v>735</v>
       </c>
       <c r="E37" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F37" s="2" t="n">
-        <v>-223</v>
+        <v>-241</v>
       </c>
       <c r="G37" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H37" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J37" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K37" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
@@ -2171,17 +2171,17 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D38" s="2" t="n">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="E38" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F38" s="2" t="n">
-        <v>-221</v>
+        <v>-241</v>
       </c>
       <c r="G38" s="2" t="n">
         <v>23</v>
@@ -2206,7 +2206,7 @@
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
@@ -2216,30 +2216,30 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D39" s="2" t="n">
-        <v>813</v>
+        <v>790</v>
       </c>
       <c r="E39" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F39" s="2" t="n">
-        <v>-163</v>
+        <v>-186</v>
       </c>
       <c r="G39" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H39" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J39" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K39" s="2" t="inlineStr">
@@ -2251,7 +2251,7 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>06-JUL-26</t>
+          <t>07-JUL-26</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
@@ -2261,17 +2261,17 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D40" s="2" t="n">
-        <v>813</v>
+        <v>792</v>
       </c>
       <c r="E40" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F40" s="2" t="n">
-        <v>-163</v>
+        <v>-184</v>
       </c>
       <c r="G40" s="2" t="n">
         <v>23</v>
@@ -2306,30 +2306,30 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D41" s="2" t="n">
-        <v>469</v>
+        <v>813</v>
       </c>
       <c r="E41" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F41" s="2" t="n">
-        <v>-507</v>
+        <v>-163</v>
       </c>
       <c r="G41" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H41" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J41" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J41" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K41" s="2" t="inlineStr">
@@ -2351,30 +2351,30 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D42" s="2" t="n">
-        <v>469</v>
+        <v>813</v>
       </c>
       <c r="E42" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F42" s="2" t="n">
-        <v>-507</v>
+        <v>-163</v>
       </c>
       <c r="G42" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H42" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J42" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J42" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K42" s="2" t="inlineStr">
@@ -2396,26 +2396,26 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D43" s="2" t="n">
-        <v>499</v>
+        <v>870</v>
       </c>
       <c r="E43" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F43" s="2" t="n">
-        <v>-477</v>
+        <v>-106</v>
       </c>
       <c r="G43" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H43" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
@@ -2431,7 +2431,7 @@
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
@@ -2441,30 +2441,30 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D44" s="2" t="n">
-        <v>698</v>
+        <v>469</v>
       </c>
       <c r="E44" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F44" s="2" t="n">
-        <v>-278</v>
+        <v>-507</v>
       </c>
       <c r="G44" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H44" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J44" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K44" s="2" t="inlineStr">
@@ -2476,7 +2476,7 @@
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
@@ -2486,30 +2486,30 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D45" s="2" t="n">
-        <v>698</v>
+        <v>616</v>
       </c>
       <c r="E45" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F45" s="2" t="n">
-        <v>-278</v>
+        <v>-360</v>
       </c>
       <c r="G45" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H45" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J45" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0</v>
+      </c>
+      <c r="J45" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K45" s="2" t="inlineStr">
@@ -2521,7 +2521,7 @@
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
@@ -2531,26 +2531,26 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D46" s="2" t="n">
-        <v>753</v>
+        <v>689</v>
       </c>
       <c r="E46" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F46" s="2" t="n">
-        <v>-223</v>
+        <v>-287</v>
       </c>
       <c r="G46" s="2" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="H46" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>-16</v>
+        <v>-10</v>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
@@ -2566,7 +2566,7 @@
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
@@ -2576,17 +2576,17 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D47" s="2" t="n">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="E47" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F47" s="2" t="n">
-        <v>-221</v>
+        <v>-241</v>
       </c>
       <c r="G47" s="2" t="n">
         <v>23</v>
@@ -2611,7 +2611,7 @@
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
@@ -2621,17 +2621,17 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D48" s="2" t="n">
-        <v>813</v>
+        <v>735</v>
       </c>
       <c r="E48" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F48" s="2" t="n">
-        <v>-163</v>
+        <v>-241</v>
       </c>
       <c r="G48" s="2" t="n">
         <v>23</v>
@@ -2656,7 +2656,7 @@
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
@@ -2666,17 +2666,17 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D49" s="2" t="n">
-        <v>813</v>
+        <v>735</v>
       </c>
       <c r="E49" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F49" s="2" t="n">
-        <v>-163</v>
+        <v>-241</v>
       </c>
       <c r="G49" s="2" t="n">
         <v>23</v>
@@ -2701,7 +2701,7 @@
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>07-JUL-26</t>
+          <t>08-JUL-26</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
@@ -2715,26 +2715,26 @@
         </is>
       </c>
       <c r="D50" s="2" t="n">
-        <v>833</v>
+        <v>735</v>
       </c>
       <c r="E50" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F50" s="2" t="n">
-        <v>-143</v>
+        <v>-241</v>
       </c>
       <c r="G50" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H50" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J50" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J50" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K50" s="2" t="inlineStr">
@@ -2756,17 +2756,17 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D51" s="2" t="n">
-        <v>698</v>
+        <v>792</v>
       </c>
       <c r="E51" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F51" s="2" t="n">
-        <v>-278</v>
+        <v>-184</v>
       </c>
       <c r="G51" s="2" t="n">
         <v>23</v>
@@ -2801,17 +2801,17 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>Saudia SV-381</t>
         </is>
       </c>
       <c r="D52" s="2" t="n">
-        <v>698</v>
+        <v>813</v>
       </c>
       <c r="E52" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F52" s="2" t="n">
-        <v>-278</v>
+        <v>-163</v>
       </c>
       <c r="G52" s="2" t="n">
         <v>23</v>
@@ -2846,17 +2846,17 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>Saudia SV-319</t>
         </is>
       </c>
       <c r="D53" s="2" t="n">
-        <v>698</v>
+        <v>813</v>
       </c>
       <c r="E53" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F53" s="2" t="n">
-        <v>-278</v>
+        <v>-163</v>
       </c>
       <c r="G53" s="2" t="n">
         <v>23</v>
@@ -2881,7 +2881,7 @@
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
@@ -2891,30 +2891,30 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D54" s="2" t="n">
-        <v>698</v>
+        <v>469</v>
       </c>
       <c r="E54" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F54" s="2" t="n">
-        <v>-278</v>
+        <v>-507</v>
       </c>
       <c r="G54" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H54" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J54" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J54" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K54" s="2" t="inlineStr">
@@ -2926,7 +2926,7 @@
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
@@ -2936,30 +2936,30 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D55" s="2" t="n">
-        <v>755</v>
+        <v>469</v>
       </c>
       <c r="E55" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F55" s="2" t="n">
-        <v>-221</v>
+        <v>-507</v>
       </c>
       <c r="G55" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H55" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J55" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J55" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K55" s="2" t="inlineStr">
@@ -2971,7 +2971,7 @@
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
@@ -2981,30 +2981,30 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D56" s="2" t="n">
-        <v>1056</v>
+        <v>499</v>
       </c>
       <c r="E56" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F56" s="2" t="n">
-        <v>80</v>
+        <v>-477</v>
       </c>
       <c r="G56" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H56" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J56" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J56" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K56" s="2" t="inlineStr">
@@ -3016,7 +3016,7 @@
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>08-JUL-26</t>
+          <t>09-JUL-26</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
@@ -3026,30 +3026,30 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D57" s="2" t="n">
-        <v>1056</v>
+        <v>499</v>
       </c>
       <c r="E57" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F57" s="2" t="n">
-        <v>80</v>
+        <v>-477</v>
       </c>
       <c r="G57" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H57" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J57" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K57" s="2" t="inlineStr">
@@ -3071,30 +3071,30 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D58" s="2" t="n">
-        <v>469</v>
+        <v>790</v>
       </c>
       <c r="E58" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F58" s="2" t="n">
-        <v>-507</v>
+        <v>-186</v>
       </c>
       <c r="G58" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H58" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-16</v>
+      </c>
+      <c r="J58" s="4" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="K58" s="2" t="inlineStr">
@@ -3116,30 +3116,30 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D59" s="2" t="n">
-        <v>469</v>
+        <v>792</v>
       </c>
       <c r="E59" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F59" s="2" t="n">
-        <v>-507</v>
+        <v>-184</v>
       </c>
       <c r="G59" s="2" t="n">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="H59" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J59" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K59" s="2" t="inlineStr">
@@ -3161,26 +3161,26 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D60" s="2" t="n">
-        <v>499</v>
+        <v>870</v>
       </c>
       <c r="E60" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F60" s="2" t="n">
-        <v>-477</v>
+        <v>-106</v>
       </c>
       <c r="G60" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
@@ -3206,26 +3206,26 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D61" s="2" t="n">
-        <v>499</v>
+        <v>870</v>
       </c>
       <c r="E61" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F61" s="2" t="n">
-        <v>-477</v>
+        <v>-106</v>
       </c>
       <c r="G61" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H61" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
@@ -3251,17 +3251,17 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D62" s="2" t="n">
-        <v>753</v>
+        <v>960</v>
       </c>
       <c r="E62" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F62" s="2" t="n">
-        <v>-223</v>
+        <v>-16</v>
       </c>
       <c r="G62" s="2" t="n">
         <v>46</v>
@@ -3272,9 +3272,9 @@
       <c r="I62" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J62" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K62" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
@@ -3296,30 +3296,30 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D63" s="2" t="n">
-        <v>755</v>
+        <v>439</v>
       </c>
       <c r="E63" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F63" s="2" t="n">
-        <v>-221</v>
+        <v>-537</v>
       </c>
       <c r="G63" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H63" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J63" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K63" s="2" t="inlineStr">
@@ -3331,7 +3331,7 @@
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
@@ -3341,26 +3341,26 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D64" s="2" t="n">
-        <v>833</v>
+        <v>469</v>
       </c>
       <c r="E64" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F64" s="2" t="n">
-        <v>-143</v>
+        <v>-507</v>
       </c>
       <c r="G64" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H64" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
@@ -3376,7 +3376,7 @@
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
@@ -3386,26 +3386,26 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D65" s="2" t="n">
-        <v>833</v>
+        <v>499</v>
       </c>
       <c r="E65" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F65" s="2" t="n">
-        <v>-143</v>
+        <v>-477</v>
       </c>
       <c r="G65" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H65" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
@@ -3421,7 +3421,7 @@
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>09-JUL-26</t>
+          <t>13-JUL-26</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
@@ -3431,26 +3431,26 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D66" s="2" t="n">
-        <v>923</v>
+        <v>499</v>
       </c>
       <c r="E66" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F66" s="2" t="n">
-        <v>-53</v>
+        <v>-477</v>
       </c>
       <c r="G66" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H66" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>-16</v>
+        <v>15</v>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
@@ -3476,30 +3476,30 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D67" s="2" t="n">
-        <v>646</v>
+        <v>735</v>
       </c>
       <c r="E67" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F67" s="2" t="n">
-        <v>-330</v>
+        <v>-241</v>
       </c>
       <c r="G67" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H67" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J67" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K67" s="2" t="inlineStr">
@@ -3521,30 +3521,30 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D68" s="2" t="n">
-        <v>646</v>
+        <v>735</v>
       </c>
       <c r="E68" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F68" s="2" t="n">
-        <v>-330</v>
+        <v>-241</v>
       </c>
       <c r="G68" s="2" t="n">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H68" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J68" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K68" s="2" t="inlineStr">
@@ -3566,30 +3566,30 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D69" s="2" t="n">
-        <v>689</v>
+        <v>735</v>
       </c>
       <c r="E69" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F69" s="2" t="n">
-        <v>-287</v>
+        <v>-241</v>
       </c>
       <c r="G69" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H69" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J69" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J69" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K69" s="2" t="inlineStr">
@@ -3611,30 +3611,30 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D70" s="2" t="n">
-        <v>689</v>
+        <v>792</v>
       </c>
       <c r="E70" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F70" s="2" t="n">
-        <v>-287</v>
+        <v>-184</v>
       </c>
       <c r="G70" s="2" t="n">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="H70" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J70" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>7</v>
+      </c>
+      <c r="J70" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K70" s="2" t="inlineStr">
@@ -3656,30 +3656,30 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D71" s="2" t="n">
-        <v>690</v>
+        <v>870</v>
       </c>
       <c r="E71" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F71" s="2" t="n">
-        <v>-286</v>
+        <v>-106</v>
       </c>
       <c r="G71" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H71" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J71" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>-16</v>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K71" s="2" t="inlineStr">
@@ -3691,7 +3691,7 @@
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
@@ -3701,30 +3701,30 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D72" s="2" t="n">
-        <v>698</v>
+        <v>469</v>
       </c>
       <c r="E72" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F72" s="2" t="n">
-        <v>-278</v>
+        <v>-507</v>
       </c>
       <c r="G72" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H72" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J72" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K72" s="2" t="inlineStr">
@@ -3736,7 +3736,7 @@
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B73" s="2" t="inlineStr">
@@ -3746,30 +3746,30 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D73" s="2" t="n">
-        <v>698</v>
+        <v>469</v>
       </c>
       <c r="E73" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F73" s="2" t="n">
-        <v>-278</v>
+        <v>-507</v>
       </c>
       <c r="G73" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H73" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J73" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K73" s="2" t="inlineStr">
@@ -3781,7 +3781,7 @@
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B74" s="2" t="inlineStr">
@@ -3791,30 +3791,30 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D74" s="2" t="n">
-        <v>698</v>
+        <v>499</v>
       </c>
       <c r="E74" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F74" s="2" t="n">
-        <v>-278</v>
+        <v>-477</v>
       </c>
       <c r="G74" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H74" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J74" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K74" s="2" t="inlineStr">
@@ -3826,7 +3826,7 @@
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B75" s="2" t="inlineStr">
@@ -3836,17 +3836,17 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D75" s="2" t="n">
-        <v>755</v>
+        <v>735</v>
       </c>
       <c r="E75" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F75" s="2" t="n">
-        <v>-221</v>
+        <v>-241</v>
       </c>
       <c r="G75" s="2" t="n">
         <v>23</v>
@@ -3871,7 +3871,7 @@
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B76" s="2" t="inlineStr">
@@ -3881,30 +3881,30 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D76" s="2" t="n">
-        <v>833</v>
+        <v>735</v>
       </c>
       <c r="E76" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F76" s="2" t="n">
-        <v>-143</v>
+        <v>-241</v>
       </c>
       <c r="G76" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H76" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J76" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J76" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K76" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
         <is>
-          <t>13-JUL-26</t>
+          <t>14-JUL-26</t>
         </is>
       </c>
       <c r="B77" s="2" t="inlineStr">
@@ -3926,30 +3926,30 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D77" s="2" t="n">
-        <v>933</v>
+        <v>792</v>
       </c>
       <c r="E77" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F77" s="2" t="n">
-        <v>-43</v>
+        <v>-184</v>
       </c>
       <c r="G77" s="2" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="H77" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J77" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>7</v>
+      </c>
+      <c r="J77" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K77" s="2" t="inlineStr">
@@ -3971,26 +3971,26 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D78" s="2" t="n">
-        <v>469</v>
+        <v>870</v>
       </c>
       <c r="E78" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F78" s="2" t="n">
-        <v>-507</v>
+        <v>-106</v>
       </c>
       <c r="G78" s="2" t="n">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="H78" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>15</v>
+        <v>-16</v>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
@@ -4006,7 +4006,7 @@
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B79" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
         </is>
       </c>
       <c r="D79" s="2" t="n">
-        <v>646</v>
+        <v>469</v>
       </c>
       <c r="E79" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F79" s="2" t="n">
-        <v>-330</v>
+        <v>-507</v>
       </c>
       <c r="G79" s="2" t="n">
-        <v>30</v>
+        <v>15</v>
       </c>
       <c r="H79" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B80" s="2" t="inlineStr">
@@ -4061,30 +4061,30 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D80" s="2" t="n">
-        <v>689</v>
+        <v>469</v>
       </c>
       <c r="E80" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F80" s="2" t="n">
-        <v>-287</v>
+        <v>-507</v>
       </c>
       <c r="G80" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H80" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J80" s="4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>15</v>
+      </c>
+      <c r="J80" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K80" s="2" t="inlineStr">
@@ -4096,7 +4096,7 @@
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B81" s="2" t="inlineStr">
@@ -4106,30 +4106,30 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D81" s="2" t="n">
-        <v>690</v>
+        <v>499</v>
       </c>
       <c r="E81" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F81" s="2" t="n">
-        <v>-286</v>
+        <v>-477</v>
       </c>
       <c r="G81" s="2" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="H81" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="J81" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J81" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K81" s="2" t="inlineStr">
@@ -4141,7 +4141,7 @@
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B82" s="2" t="inlineStr">
@@ -4151,17 +4151,17 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D82" s="2" t="n">
-        <v>690</v>
+        <v>735</v>
       </c>
       <c r="E82" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F82" s="2" t="n">
-        <v>-286</v>
+        <v>-241</v>
       </c>
       <c r="G82" s="2" t="n">
         <v>23</v>
@@ -4186,7 +4186,7 @@
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B83" s="2" t="inlineStr">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="D83" s="2" t="n">
-        <v>698</v>
+        <v>735</v>
       </c>
       <c r="E83" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F83" s="2" t="n">
-        <v>-278</v>
+        <v>-241</v>
       </c>
       <c r="G83" s="2" t="n">
         <v>23</v>
@@ -4231,7 +4231,7 @@
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B84" s="2" t="inlineStr">
@@ -4245,13 +4245,13 @@
         </is>
       </c>
       <c r="D84" s="2" t="n">
-        <v>698</v>
+        <v>735</v>
       </c>
       <c r="E84" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F84" s="2" t="n">
-        <v>-278</v>
+        <v>-241</v>
       </c>
       <c r="G84" s="2" t="n">
         <v>23</v>
@@ -4276,7 +4276,7 @@
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B85" s="2" t="inlineStr">
@@ -4290,13 +4290,13 @@
         </is>
       </c>
       <c r="D85" s="2" t="n">
-        <v>755</v>
+        <v>792</v>
       </c>
       <c r="E85" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F85" s="2" t="n">
-        <v>-221</v>
+        <v>-184</v>
       </c>
       <c r="G85" s="2" t="n">
         <v>23</v>
@@ -4321,7 +4321,7 @@
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
         <is>
-          <t>14-JUL-26</t>
+          <t>15-JUL-26</t>
         </is>
       </c>
       <c r="B86" s="2" t="inlineStr">
@@ -4335,13 +4335,13 @@
         </is>
       </c>
       <c r="D86" s="2" t="n">
-        <v>833</v>
+        <v>870</v>
       </c>
       <c r="E86" s="2" t="n">
         <v>976</v>
       </c>
       <c r="F86" s="2" t="n">
-        <v>-143</v>
+        <v>-106</v>
       </c>
       <c r="G86" s="2" t="n">
         <v>46</v>
@@ -4366,7 +4366,7 @@
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B87" s="2" t="inlineStr">
@@ -4376,30 +4376,30 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-775</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D87" s="2" t="n">
-        <v>469</v>
+        <v>729</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F87" s="2" t="n">
-        <v>-507</v>
+        <v>107</v>
       </c>
       <c r="G87" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H87" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J87" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K87" s="2" t="inlineStr">
@@ -4411,7 +4411,7 @@
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>16-JUL-26</t>
         </is>
       </c>
       <c r="B88" s="2" t="inlineStr">
@@ -4421,30 +4421,30 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D88" s="2" t="n">
-        <v>469</v>
+        <v>729</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F88" s="2" t="n">
-        <v>-507</v>
+        <v>107</v>
       </c>
       <c r="G88" s="2" t="n">
-        <v>15</v>
+        <v>40</v>
       </c>
       <c r="H88" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>-10</v>
+      </c>
+      <c r="J88" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K88" s="2" t="inlineStr">
@@ -4456,7 +4456,7 @@
     <row r="89">
       <c r="A89" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B89" s="2" t="inlineStr">
@@ -4466,30 +4466,30 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D89" s="2" t="n">
-        <v>499</v>
+        <v>586</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F89" s="2" t="n">
-        <v>-477</v>
+        <v>-36</v>
       </c>
       <c r="G89" s="2" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="H89" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+        <v>0</v>
+      </c>
+      <c r="J89" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K89" s="2" t="inlineStr">
@@ -4501,7 +4501,7 @@
     <row r="90">
       <c r="A90" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>28-JUL-26</t>
         </is>
       </c>
       <c r="B90" s="2" t="inlineStr">
@@ -4511,26 +4511,26 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D90" s="2" t="n">
-        <v>690</v>
+        <v>586</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F90" s="2" t="n">
-        <v>-286</v>
+        <v>-36</v>
       </c>
       <c r="G90" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H90" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J90" s="3" t="inlineStr">
         <is>
@@ -4546,7 +4546,7 @@
     <row r="91">
       <c r="A91" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>29-JUL-26</t>
         </is>
       </c>
       <c r="B91" s="2" t="inlineStr">
@@ -4556,26 +4556,26 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-319</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D91" s="2" t="n">
-        <v>690</v>
+        <v>616</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F91" s="2" t="n">
-        <v>-286</v>
+        <v>-6</v>
       </c>
       <c r="G91" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H91" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J91" s="3" t="inlineStr">
         <is>
@@ -4591,7 +4591,7 @@
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>03-AUG-26</t>
         </is>
       </c>
       <c r="B92" s="2" t="inlineStr">
@@ -4601,26 +4601,26 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D92" s="2" t="n">
-        <v>698</v>
+        <v>616</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F92" s="2" t="n">
-        <v>-278</v>
+        <v>-6</v>
       </c>
       <c r="G92" s="2" t="n">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H92" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J92" s="3" t="inlineStr">
         <is>
@@ -4636,7 +4636,7 @@
     <row r="93">
       <c r="A93" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>13-AUG-26</t>
         </is>
       </c>
       <c r="B93" s="2" t="inlineStr">
@@ -4646,26 +4646,26 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-696</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D93" s="2" t="n">
-        <v>698</v>
+        <v>790</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>976</v>
+        <v>622</v>
       </c>
       <c r="F93" s="2" t="n">
-        <v>-278</v>
+        <v>168</v>
       </c>
       <c r="G93" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H93" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J93" s="3" t="inlineStr">
         <is>
@@ -4681,7 +4681,7 @@
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B94" s="2" t="inlineStr">
@@ -4691,26 +4691,26 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D94" s="2" t="n">
-        <v>698</v>
+        <v>1055</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F94" s="2" t="n">
-        <v>-278</v>
+        <v>157</v>
       </c>
       <c r="G94" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H94" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J94" s="3" t="inlineStr">
         <is>
@@ -4726,7 +4726,7 @@
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B95" s="2" t="inlineStr">
@@ -4736,26 +4736,26 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-678</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D95" s="2" t="n">
-        <v>755</v>
+        <v>1055</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F95" s="2" t="n">
-        <v>-221</v>
+        <v>157</v>
       </c>
       <c r="G95" s="2" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="H95" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>7</v>
+        <v>-16</v>
       </c>
       <c r="J95" s="3" t="inlineStr">
         <is>
@@ -4771,7 +4771,7 @@
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
         <is>
-          <t>15-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B96" s="2" t="inlineStr">
@@ -4781,17 +4781,17 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D96" s="2" t="n">
-        <v>833</v>
+        <v>1055</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>976</v>
+        <v>898</v>
       </c>
       <c r="F96" s="2" t="n">
-        <v>-143</v>
+        <v>157</v>
       </c>
       <c r="G96" s="2" t="n">
         <v>46</v>
@@ -4802,9 +4802,9 @@
       <c r="I96" s="2" t="n">
         <v>-16</v>
       </c>
-      <c r="J96" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="J96" s="3" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="K96" s="2" t="inlineStr">
@@ -4816,7 +4816,7 @@
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
         <is>
-          <t>16-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B97" s="2" t="inlineStr">
@@ -4826,17 +4826,17 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D97" s="2" t="n">
-        <v>833</v>
+        <v>1055</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F97" s="2" t="n">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="G97" s="2" t="n">
         <v>46</v>
@@ -4861,7 +4861,7 @@
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>22-SEP-26</t>
         </is>
       </c>
       <c r="B98" s="2" t="inlineStr">
@@ -4871,26 +4871,26 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D98" s="2" t="n">
-        <v>586</v>
+        <v>1112</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F98" s="2" t="n">
-        <v>-36</v>
+        <v>214</v>
       </c>
       <c r="G98" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H98" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J98" s="3" t="inlineStr">
         <is>
@@ -4906,7 +4906,7 @@
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B99" s="2" t="inlineStr">
@@ -4916,30 +4916,30 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-793</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D99" s="2" t="n">
-        <v>649</v>
+        <v>429</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F99" s="2" t="n">
-        <v>27</v>
+        <v>-469</v>
       </c>
       <c r="G99" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H99" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J99" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J99" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K99" s="2" t="inlineStr">
@@ -4951,7 +4951,7 @@
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B100" s="2" t="inlineStr">
@@ -4961,30 +4961,30 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>flynas XY-576</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D100" s="2" t="n">
-        <v>689</v>
+        <v>439</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F100" s="2" t="n">
-        <v>67</v>
+        <v>-459</v>
       </c>
       <c r="G100" s="2" t="n">
-        <v>40</v>
+        <v>15</v>
       </c>
       <c r="H100" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J100" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J100" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K100" s="2" t="inlineStr">
@@ -4996,7 +4996,7 @@
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
         <is>
-          <t>20-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B101" s="2" t="inlineStr">
@@ -5006,30 +5006,30 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D101" s="2" t="n">
-        <v>833</v>
+        <v>439</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F101" s="2" t="n">
-        <v>211</v>
+        <v>-459</v>
       </c>
       <c r="G101" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H101" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J101" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J101" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K101" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
         <is>
-          <t>21-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B102" s="2" t="inlineStr">
@@ -5051,17 +5051,17 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-640</t>
+          <t>EgyptAir MS-676</t>
         </is>
       </c>
       <c r="D102" s="2" t="n">
-        <v>833</v>
+        <v>1055</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F102" s="2" t="n">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="G102" s="2" t="n">
         <v>46</v>
@@ -5086,7 +5086,7 @@
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B103" s="2" t="inlineStr">
@@ -5096,26 +5096,26 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D103" s="2" t="n">
-        <v>616</v>
+        <v>1055</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F103" s="2" t="n">
-        <v>-6</v>
+        <v>157</v>
       </c>
       <c r="G103" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H103" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J103" s="3" t="inlineStr">
         <is>
@@ -5131,7 +5131,7 @@
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
         <is>
-          <t>23-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B104" s="2" t="inlineStr">
@@ -5141,17 +5141,17 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-694</t>
         </is>
       </c>
       <c r="D104" s="2" t="n">
-        <v>833</v>
+        <v>1055</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F104" s="2" t="n">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="G104" s="2" t="n">
         <v>46</v>
@@ -5176,7 +5176,7 @@
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
         <is>
-          <t>27-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B105" s="2" t="inlineStr">
@@ -5186,26 +5186,26 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>flyadeal F3-771</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D105" s="2" t="n">
-        <v>616</v>
+        <v>1055</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F105" s="2" t="n">
-        <v>-6</v>
+        <v>157</v>
       </c>
       <c r="G105" s="2" t="n">
-        <v>30</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>0</v>
+        <v>-16</v>
       </c>
       <c r="J105" s="3" t="inlineStr">
         <is>
@@ -5221,7 +5221,7 @@
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
         <is>
-          <t>28-JUL-26</t>
+          <t>23-SEP-26</t>
         </is>
       </c>
       <c r="B106" s="2" t="inlineStr">
@@ -5231,17 +5231,17 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D106" s="2" t="n">
-        <v>833</v>
+        <v>1112</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F106" s="2" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G106" s="2" t="n">
         <v>46</v>
@@ -5266,7 +5266,7 @@
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
         <is>
-          <t>29-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B107" s="2" t="inlineStr">
@@ -5276,30 +5276,30 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flynas XY-793</t>
         </is>
       </c>
       <c r="D107" s="2" t="n">
-        <v>833</v>
+        <v>429</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F107" s="2" t="n">
-        <v>211</v>
+        <v>-469</v>
       </c>
       <c r="G107" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H107" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J107" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J107" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K107" s="2" t="inlineStr">
@@ -5311,7 +5311,7 @@
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B108" s="2" t="inlineStr">
@@ -5321,30 +5321,30 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Saudia SV-381</t>
+          <t>flynas XY-576</t>
         </is>
       </c>
       <c r="D108" s="2" t="n">
-        <v>800</v>
+        <v>429</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F108" s="2" t="n">
-        <v>178</v>
+        <v>-469</v>
       </c>
       <c r="G108" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H108" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J108" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J108" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K108" s="2" t="inlineStr">
@@ -5356,7 +5356,7 @@
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B109" s="2" t="inlineStr">
@@ -5366,30 +5366,30 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>flyadeal F3-775</t>
         </is>
       </c>
       <c r="D109" s="2" t="n">
-        <v>833</v>
+        <v>439</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F109" s="2" t="n">
-        <v>211</v>
+        <v>-459</v>
       </c>
       <c r="G109" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H109" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J109" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J109" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K109" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
         <is>
-          <t>30-JUL-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B110" s="2" t="inlineStr">
@@ -5411,30 +5411,30 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>flyadeal F3-771</t>
         </is>
       </c>
       <c r="D110" s="2" t="n">
-        <v>833</v>
+        <v>439</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F110" s="2" t="n">
-        <v>211</v>
+        <v>-459</v>
       </c>
       <c r="G110" s="2" t="n">
-        <v>46</v>
+        <v>15</v>
       </c>
       <c r="H110" s="2" t="n">
         <v>30</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J110" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>15</v>
+      </c>
+      <c r="J110" s="5" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="K110" s="2" t="inlineStr">
@@ -5446,7 +5446,7 @@
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B111" s="2" t="inlineStr">
@@ -5456,17 +5456,17 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-640</t>
         </is>
       </c>
       <c r="D111" s="2" t="n">
-        <v>833</v>
+        <v>1055</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F111" s="2" t="n">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="G111" s="2" t="n">
         <v>46</v>
@@ -5491,7 +5491,7 @@
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
         <is>
-          <t>04-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B112" s="2" t="inlineStr">
@@ -5505,13 +5505,13 @@
         </is>
       </c>
       <c r="D112" s="2" t="n">
-        <v>833</v>
+        <v>1055</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F112" s="2" t="n">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="G112" s="2" t="n">
         <v>46</v>
@@ -5536,7 +5536,7 @@
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
         <is>
-          <t>10-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B113" s="2" t="inlineStr">
@@ -5546,17 +5546,17 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-694</t>
+          <t>EgyptAir MS-696</t>
         </is>
       </c>
       <c r="D113" s="2" t="n">
-        <v>833</v>
+        <v>1055</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F113" s="2" t="n">
-        <v>211</v>
+        <v>157</v>
       </c>
       <c r="G113" s="2" t="n">
         <v>46</v>
@@ -5581,7 +5581,7 @@
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
         <is>
-          <t>11-AUG-26</t>
+          <t>24-SEP-26</t>
         </is>
       </c>
       <c r="B114" s="2" t="inlineStr">
@@ -5591,17 +5591,17 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>EgyptAir MS-676</t>
+          <t>EgyptAir MS-678</t>
         </is>
       </c>
       <c r="D114" s="2" t="n">
-        <v>833</v>
+        <v>1112</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>622</v>
+        <v>898</v>
       </c>
       <c r="F114" s="2" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="G114" s="2" t="n">
         <v>46</v>
@@ -5618,1311 +5618,6 @@
         </is>
       </c>
       <c r="K114" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="n">
-        <v>616</v>
-      </c>
-      <c r="E115" s="2" t="n">
-        <v>622</v>
-      </c>
-      <c r="F115" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G115" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H115" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I115" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K115" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="n">
-        <v>616</v>
-      </c>
-      <c r="E116" s="2" t="n">
-        <v>622</v>
-      </c>
-      <c r="F116" s="2" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G116" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="H116" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I116" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="J116" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K116" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-793</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="n">
-        <v>619</v>
-      </c>
-      <c r="E117" s="2" t="n">
-        <v>622</v>
-      </c>
-      <c r="F117" s="2" t="n">
-        <v>-3</v>
-      </c>
-      <c r="G117" s="2" t="n">
-        <v>40</v>
-      </c>
-      <c r="H117" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I117" s="2" t="n">
-        <v>-10</v>
-      </c>
-      <c r="J117" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K117" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
-        <is>
-          <t>13-AUG-26</t>
-        </is>
-      </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="n">
-        <v>753</v>
-      </c>
-      <c r="E118" s="2" t="n">
-        <v>622</v>
-      </c>
-      <c r="F118" s="2" t="n">
-        <v>131</v>
-      </c>
-      <c r="G118" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H118" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I118" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J118" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K118" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E119" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F119" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G119" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H119" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I119" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J119" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K119" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E120" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F120" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G120" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H120" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I120" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J120" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K120" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E121" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F121" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G121" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H121" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I121" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J121" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K121" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E122" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F122" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G122" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H122" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I122" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J122" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K122" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E123" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F123" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G123" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H123" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I123" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J123" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K123" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E124" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F124" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G124" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H124" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I124" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J124" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K124" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E125" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F125" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G125" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H125" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I125" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J125" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K125" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
-        <is>
-          <t>22-SEP-26</t>
-        </is>
-      </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E126" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F126" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G126" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H126" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I126" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J126" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K126" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E127" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F127" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G127" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H127" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I127" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J127" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K127" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E128" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F128" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G128" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H128" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I128" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J128" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K128" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E129" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F129" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G129" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H129" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I129" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J129" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K129" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E130" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F130" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G130" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H130" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I130" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J130" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K130" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E131" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F131" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G131" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H131" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I131" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J131" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K131" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E132" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F132" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G132" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H132" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I132" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J132" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K132" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E133" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F133" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G133" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H133" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I133" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J133" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K133" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>23-SEP-26</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E134" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F134" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G134" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H134" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I134" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J134" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K134" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-793</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E135" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F135" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G135" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H135" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I135" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J135" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K135" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>flynas XY-576</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="n">
-        <v>429</v>
-      </c>
-      <c r="E136" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F136" s="2" t="n">
-        <v>-469</v>
-      </c>
-      <c r="G136" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H136" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I136" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J136" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K136" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-775</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E137" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F137" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G137" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H137" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I137" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J137" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K137" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>flyadeal F3-771</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="n">
-        <v>439</v>
-      </c>
-      <c r="E138" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F138" s="2" t="n">
-        <v>-459</v>
-      </c>
-      <c r="G138" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="H138" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I138" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="J138" s="5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="K138" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-694</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E139" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F139" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G139" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H139" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I139" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J139" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K139" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-696</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E140" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F140" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G140" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H140" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I140" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J140" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K140" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-640</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="n">
-        <v>1018</v>
-      </c>
-      <c r="E141" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F141" s="2" t="n">
-        <v>120</v>
-      </c>
-      <c r="G141" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H141" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I141" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J141" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K141" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-678</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="n">
-        <v>1075</v>
-      </c>
-      <c r="E142" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F142" s="2" t="n">
-        <v>177</v>
-      </c>
-      <c r="G142" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H142" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I142" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J142" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K142" s="2" t="inlineStr">
-        <is>
-          <t>SAR</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
-        <is>
-          <t>24-SEP-26</t>
-        </is>
-      </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>SM-494</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>EgyptAir MS-676</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="n">
-        <v>1113</v>
-      </c>
-      <c r="E143" s="2" t="n">
-        <v>898</v>
-      </c>
-      <c r="F143" s="2" t="n">
-        <v>215</v>
-      </c>
-      <c r="G143" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="H143" s="2" t="n">
-        <v>30</v>
-      </c>
-      <c r="I143" s="2" t="n">
-        <v>-16</v>
-      </c>
-      <c r="J143" s="3" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="K143" s="2" t="inlineStr">
         <is>
           <t>SAR</t>
         </is>
